--- a/storage/app/Titik Ori Grafik.xlsx
+++ b/storage/app/Titik Ori Grafik.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P18"/>
+  <dimension ref="A1:AL20"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -448,6 +448,72 @@
       <c r="P1" t="str">
         <v>TFL Y</v>
       </c>
+      <c r="Q1" t="str">
+        <v>VEI X</v>
+      </c>
+      <c r="R1" t="str">
+        <v>VEI Y</v>
+      </c>
+      <c r="S1" t="str">
+        <v>VER X</v>
+      </c>
+      <c r="T1" t="str">
+        <v>VER Y</v>
+      </c>
+      <c r="U1" t="str">
+        <v>OSI X</v>
+      </c>
+      <c r="V1" t="str">
+        <v>OSI Y</v>
+      </c>
+      <c r="W1" t="str">
+        <v>OEM X</v>
+      </c>
+      <c r="X1" t="str">
+        <v>OEM Y</v>
+      </c>
+      <c r="Y1" t="str">
+        <v>BAU X</v>
+      </c>
+      <c r="Z1" t="str">
+        <v>BAU Y</v>
+      </c>
+      <c r="AA1" t="str">
+        <v>BKU X</v>
+      </c>
+      <c r="AB1" t="str">
+        <v>BKU Y</v>
+      </c>
+      <c r="AC1" t="str">
+        <v>BSA X</v>
+      </c>
+      <c r="AD1" t="str">
+        <v>BSA Y</v>
+      </c>
+      <c r="AE1" t="str">
+        <v>BGI X</v>
+      </c>
+      <c r="AF1" t="str">
+        <v>BGI Y</v>
+      </c>
+      <c r="AG1" t="str">
+        <v>PAH X</v>
+      </c>
+      <c r="AH1" t="str">
+        <v>PAH Y</v>
+      </c>
+      <c r="AI1" t="str">
+        <v>PST X</v>
+      </c>
+      <c r="AJ1" t="str">
+        <v>PST Y</v>
+      </c>
+      <c r="AK1" t="str">
+        <v>PRA X</v>
+      </c>
+      <c r="AL1" t="str">
+        <v>PRA Y</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -498,6 +564,72 @@
       <c r="P2" t="str">
         <v>274.91</v>
       </c>
+      <c r="Q2" t="str">
+        <v>5630</v>
+      </c>
+      <c r="R2" t="str">
+        <v>129.3</v>
+      </c>
+      <c r="S2" t="str">
+        <v>6900</v>
+      </c>
+      <c r="T2" t="str">
+        <v>127.5</v>
+      </c>
+      <c r="U2" t="str">
+        <v>4850</v>
+      </c>
+      <c r="V2" t="str">
+        <v>126</v>
+      </c>
+      <c r="W2" t="str">
+        <v>4850</v>
+      </c>
+      <c r="X2" t="str">
+        <v>126</v>
+      </c>
+      <c r="Y2" t="str">
+        <v>115.83</v>
+      </c>
+      <c r="Z2" t="str">
+        <v>307.67</v>
+      </c>
+      <c r="AA2" t="str">
+        <v>115.83</v>
+      </c>
+      <c r="AB2" t="str">
+        <v>307.67</v>
+      </c>
+      <c r="AC2" t="str">
+        <v>115.83</v>
+      </c>
+      <c r="AD2" t="str">
+        <v>307.67</v>
+      </c>
+      <c r="AE2" t="str">
+        <v>115.83</v>
+      </c>
+      <c r="AF2" t="str">
+        <v>307.67</v>
+      </c>
+      <c r="AG2" t="str">
+        <v>448.66</v>
+      </c>
+      <c r="AH2" t="str">
+        <v>240</v>
+      </c>
+      <c r="AI2" t="str">
+        <v>508.4</v>
+      </c>
+      <c r="AJ2" t="str">
+        <v>240</v>
+      </c>
+      <c r="AK2" t="str">
+        <v>508.4</v>
+      </c>
+      <c r="AL2" t="str">
+        <v>240</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -548,6 +680,72 @@
       <c r="P3" t="str">
         <v>266.18</v>
       </c>
+      <c r="Q3" t="str">
+        <v>5750</v>
+      </c>
+      <c r="R3" t="str">
+        <v>129.3</v>
+      </c>
+      <c r="S3" t="str">
+        <v>7300</v>
+      </c>
+      <c r="T3" t="str">
+        <v>127</v>
+      </c>
+      <c r="U3" t="str">
+        <v>5150</v>
+      </c>
+      <c r="V3" t="str">
+        <v>125</v>
+      </c>
+      <c r="W3" t="str">
+        <v>5150</v>
+      </c>
+      <c r="X3" t="str">
+        <v>125</v>
+      </c>
+      <c r="Y3" t="str">
+        <v>150</v>
+      </c>
+      <c r="Z3" t="str">
+        <v>278.33</v>
+      </c>
+      <c r="AA3" t="str">
+        <v>150</v>
+      </c>
+      <c r="AB3" t="str">
+        <v>278.33</v>
+      </c>
+      <c r="AC3" t="str">
+        <v>150</v>
+      </c>
+      <c r="AD3" t="str">
+        <v>278.33</v>
+      </c>
+      <c r="AE3" t="str">
+        <v>150</v>
+      </c>
+      <c r="AF3" t="str">
+        <v>278.33</v>
+      </c>
+      <c r="AG3" t="str">
+        <v>529.5</v>
+      </c>
+      <c r="AH3" t="str">
+        <v>234</v>
+      </c>
+      <c r="AI3" t="str">
+        <v>600</v>
+      </c>
+      <c r="AJ3" t="str">
+        <v>234</v>
+      </c>
+      <c r="AK3" t="str">
+        <v>600</v>
+      </c>
+      <c r="AL3" t="str">
+        <v>234</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -598,6 +796,72 @@
       <c r="P4" t="str">
         <v>254.55</v>
       </c>
+      <c r="Q4" t="str">
+        <v>8920</v>
+      </c>
+      <c r="R4" t="str">
+        <v>126.5</v>
+      </c>
+      <c r="S4" t="str">
+        <v>7800</v>
+      </c>
+      <c r="T4" t="str">
+        <v>126.5</v>
+      </c>
+      <c r="U4" t="str">
+        <v>5550</v>
+      </c>
+      <c r="V4" t="str">
+        <v>124</v>
+      </c>
+      <c r="W4" t="str">
+        <v>5550</v>
+      </c>
+      <c r="X4" t="str">
+        <v>124</v>
+      </c>
+      <c r="Y4" t="str">
+        <v>200</v>
+      </c>
+      <c r="Z4" t="str">
+        <v>255</v>
+      </c>
+      <c r="AA4" t="str">
+        <v>200</v>
+      </c>
+      <c r="AB4" t="str">
+        <v>255</v>
+      </c>
+      <c r="AC4" t="str">
+        <v>200</v>
+      </c>
+      <c r="AD4" t="str">
+        <v>255</v>
+      </c>
+      <c r="AE4" t="str">
+        <v>200</v>
+      </c>
+      <c r="AF4" t="str">
+        <v>255</v>
+      </c>
+      <c r="AG4" t="str">
+        <v>706</v>
+      </c>
+      <c r="AH4" t="str">
+        <v>223.67</v>
+      </c>
+      <c r="AI4" t="str">
+        <v>800</v>
+      </c>
+      <c r="AJ4" t="str">
+        <v>223.67</v>
+      </c>
+      <c r="AK4" t="str">
+        <v>800</v>
+      </c>
+      <c r="AL4" t="str">
+        <v>223.67</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -648,6 +912,72 @@
       <c r="P5" t="str">
         <v>242.55</v>
       </c>
+      <c r="Q5" t="str">
+        <v>8980</v>
+      </c>
+      <c r="R5" t="str">
+        <v>126.2</v>
+      </c>
+      <c r="S5" t="str">
+        <v>8300</v>
+      </c>
+      <c r="T5" t="str">
+        <v>126</v>
+      </c>
+      <c r="U5" t="str">
+        <v>6050</v>
+      </c>
+      <c r="V5" t="str">
+        <v>123</v>
+      </c>
+      <c r="W5" t="str">
+        <v>6050</v>
+      </c>
+      <c r="X5" t="str">
+        <v>123</v>
+      </c>
+      <c r="Y5" t="str">
+        <v>250</v>
+      </c>
+      <c r="Z5" t="str">
+        <v>241.33</v>
+      </c>
+      <c r="AA5" t="str">
+        <v>250</v>
+      </c>
+      <c r="AB5" t="str">
+        <v>241.33</v>
+      </c>
+      <c r="AC5" t="str">
+        <v>250</v>
+      </c>
+      <c r="AD5" t="str">
+        <v>241.33</v>
+      </c>
+      <c r="AE5" t="str">
+        <v>250</v>
+      </c>
+      <c r="AF5" t="str">
+        <v>241.33</v>
+      </c>
+      <c r="AG5" t="str">
+        <v>882.5</v>
+      </c>
+      <c r="AH5" t="str">
+        <v>217</v>
+      </c>
+      <c r="AI5" t="str">
+        <v>1000</v>
+      </c>
+      <c r="AJ5" t="str">
+        <v>217</v>
+      </c>
+      <c r="AK5" t="str">
+        <v>1000</v>
+      </c>
+      <c r="AL5" t="str">
+        <v>217</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -698,6 +1028,72 @@
       <c r="P6" t="str">
         <v>232.73_x000d_</v>
       </c>
+      <c r="Q6" t="str">
+        <v>9480</v>
+      </c>
+      <c r="R6" t="str">
+        <v>126</v>
+      </c>
+      <c r="S6" t="str">
+        <v>8800</v>
+      </c>
+      <c r="T6" t="str">
+        <v>125.5</v>
+      </c>
+      <c r="U6" t="str">
+        <v>6800</v>
+      </c>
+      <c r="V6" t="str">
+        <v>122</v>
+      </c>
+      <c r="W6" t="str">
+        <v>6800</v>
+      </c>
+      <c r="X6" t="str">
+        <v>122</v>
+      </c>
+      <c r="Y6" t="str">
+        <v>300</v>
+      </c>
+      <c r="Z6" t="str">
+        <v>233</v>
+      </c>
+      <c r="AA6" t="str">
+        <v>300</v>
+      </c>
+      <c r="AB6" t="str">
+        <v>233</v>
+      </c>
+      <c r="AC6" t="str">
+        <v>300</v>
+      </c>
+      <c r="AD6" t="str">
+        <v>233</v>
+      </c>
+      <c r="AE6" t="str">
+        <v>300</v>
+      </c>
+      <c r="AF6" t="str">
+        <v>233</v>
+      </c>
+      <c r="AG6" t="str">
+        <v>1059</v>
+      </c>
+      <c r="AH6" t="str">
+        <v>211.67</v>
+      </c>
+      <c r="AI6" t="str">
+        <v>1200</v>
+      </c>
+      <c r="AJ6" t="str">
+        <v>211.67</v>
+      </c>
+      <c r="AK6" t="str">
+        <v>1200</v>
+      </c>
+      <c r="AL6" t="str">
+        <v>211.67</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -748,6 +1144,72 @@
       <c r="P7" t="str">
         <v>224.36_x000d_</v>
       </c>
+      <c r="Q7" t="str">
+        <v>9920</v>
+      </c>
+      <c r="R7" t="str">
+        <v>125.6</v>
+      </c>
+      <c r="S7" t="str">
+        <v>9300</v>
+      </c>
+      <c r="T7" t="str">
+        <v>125</v>
+      </c>
+      <c r="U7" t="str">
+        <v>7550</v>
+      </c>
+      <c r="V7" t="str">
+        <v>121</v>
+      </c>
+      <c r="W7" t="str">
+        <v>7550</v>
+      </c>
+      <c r="X7" t="str">
+        <v>121</v>
+      </c>
+      <c r="Y7" t="str">
+        <v>350</v>
+      </c>
+      <c r="Z7" t="str">
+        <v>226.33</v>
+      </c>
+      <c r="AA7" t="str">
+        <v>350</v>
+      </c>
+      <c r="AB7" t="str">
+        <v>226.33</v>
+      </c>
+      <c r="AC7" t="str">
+        <v>350</v>
+      </c>
+      <c r="AD7" t="str">
+        <v>226.33</v>
+      </c>
+      <c r="AE7" t="str">
+        <v>350</v>
+      </c>
+      <c r="AF7" t="str">
+        <v>226.33</v>
+      </c>
+      <c r="AG7" t="str">
+        <v>1235.5</v>
+      </c>
+      <c r="AH7" t="str">
+        <v>208.33</v>
+      </c>
+      <c r="AI7" t="str">
+        <v>1400</v>
+      </c>
+      <c r="AJ7" t="str">
+        <v>208.33</v>
+      </c>
+      <c r="AK7" t="str">
+        <v>1400</v>
+      </c>
+      <c r="AL7" t="str">
+        <v>208.33</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -798,6 +1260,72 @@
       <c r="P8" t="str">
         <v>218.18_x000d_</v>
       </c>
+      <c r="Q8" t="str">
+        <v>9960</v>
+      </c>
+      <c r="R8" t="str">
+        <v>125.1</v>
+      </c>
+      <c r="S8" t="str">
+        <v>9800</v>
+      </c>
+      <c r="T8" t="str">
+        <v>124.5</v>
+      </c>
+      <c r="U8" t="str">
+        <v>9300</v>
+      </c>
+      <c r="V8" t="str">
+        <v>122</v>
+      </c>
+      <c r="W8" t="str">
+        <v>9300</v>
+      </c>
+      <c r="X8" t="str">
+        <v>122</v>
+      </c>
+      <c r="Y8" t="str">
+        <v>400</v>
+      </c>
+      <c r="Z8" t="str">
+        <v>221.67</v>
+      </c>
+      <c r="AA8" t="str">
+        <v>400</v>
+      </c>
+      <c r="AB8" t="str">
+        <v>221.67</v>
+      </c>
+      <c r="AC8" t="str">
+        <v>400</v>
+      </c>
+      <c r="AD8" t="str">
+        <v>221.67</v>
+      </c>
+      <c r="AE8" t="str">
+        <v>400</v>
+      </c>
+      <c r="AF8" t="str">
+        <v>221.67</v>
+      </c>
+      <c r="AG8" t="str">
+        <v>1412</v>
+      </c>
+      <c r="AH8" t="str">
+        <v>206</v>
+      </c>
+      <c r="AI8" t="str">
+        <v>1600</v>
+      </c>
+      <c r="AJ8" t="str">
+        <v>206</v>
+      </c>
+      <c r="AK8" t="str">
+        <v>1600</v>
+      </c>
+      <c r="AL8" t="str">
+        <v>206</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -848,6 +1376,72 @@
       <c r="P9" t="str">
         <v>213.09_x000d_</v>
       </c>
+      <c r="Q9" t="str">
+        <v>11620</v>
+      </c>
+      <c r="R9" t="str">
+        <v>128</v>
+      </c>
+      <c r="S9" t="str">
+        <v>10600</v>
+      </c>
+      <c r="T9" t="str">
+        <v>124</v>
+      </c>
+      <c r="U9" t="str">
+        <v>9650</v>
+      </c>
+      <c r="V9" t="str">
+        <v>123</v>
+      </c>
+      <c r="W9" t="str">
+        <v>9650</v>
+      </c>
+      <c r="X9" t="str">
+        <v>123</v>
+      </c>
+      <c r="Y9" t="str">
+        <v>450</v>
+      </c>
+      <c r="Z9" t="str">
+        <v>218.33</v>
+      </c>
+      <c r="AA9" t="str">
+        <v>450</v>
+      </c>
+      <c r="AB9" t="str">
+        <v>218.33</v>
+      </c>
+      <c r="AC9" t="str">
+        <v>450</v>
+      </c>
+      <c r="AD9" t="str">
+        <v>218.33</v>
+      </c>
+      <c r="AE9" t="str">
+        <v>450</v>
+      </c>
+      <c r="AF9" t="str">
+        <v>218.33</v>
+      </c>
+      <c r="AG9" t="str">
+        <v>1588.5</v>
+      </c>
+      <c r="AH9" t="str">
+        <v>205.17</v>
+      </c>
+      <c r="AI9" t="str">
+        <v>1800</v>
+      </c>
+      <c r="AJ9" t="str">
+        <v>205.17</v>
+      </c>
+      <c r="AK9" t="str">
+        <v>1800</v>
+      </c>
+      <c r="AL9" t="str">
+        <v>205.17</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -898,6 +1492,60 @@
       <c r="P10" t="str">
         <v>209.82_x000d_</v>
       </c>
+      <c r="Q10" t="str">
+        <v>11640</v>
+      </c>
+      <c r="R10" t="str">
+        <v>127.6</v>
+      </c>
+      <c r="S10" t="str">
+        <v>11600</v>
+      </c>
+      <c r="T10" t="str">
+        <v>124</v>
+      </c>
+      <c r="Y10" t="str">
+        <v>500</v>
+      </c>
+      <c r="Z10" t="str">
+        <v>215.33</v>
+      </c>
+      <c r="AA10" t="str">
+        <v>500</v>
+      </c>
+      <c r="AB10" t="str">
+        <v>215.33</v>
+      </c>
+      <c r="AC10" t="str">
+        <v>500</v>
+      </c>
+      <c r="AD10" t="str">
+        <v>215.33</v>
+      </c>
+      <c r="AE10" t="str">
+        <v>500</v>
+      </c>
+      <c r="AF10" t="str">
+        <v>215.33</v>
+      </c>
+      <c r="AG10" t="str">
+        <v>1765</v>
+      </c>
+      <c r="AH10" t="str">
+        <v>204.67</v>
+      </c>
+      <c r="AI10" t="str">
+        <v>2000</v>
+      </c>
+      <c r="AJ10" t="str">
+        <v>204.67</v>
+      </c>
+      <c r="AK10" t="str">
+        <v>2000</v>
+      </c>
+      <c r="AL10" t="str">
+        <v>204.67</v>
+      </c>
     </row>
     <row r="11">
       <c r="C11" t="str">
@@ -942,6 +1590,54 @@
       <c r="P11" t="str">
         <v>208.36_x000d_</v>
       </c>
+      <c r="S11" t="str">
+        <v>12300</v>
+      </c>
+      <c r="T11" t="str">
+        <v>124.5</v>
+      </c>
+      <c r="Y11" t="str">
+        <v>550</v>
+      </c>
+      <c r="Z11" t="str">
+        <v>212.67</v>
+      </c>
+      <c r="AA11" t="str">
+        <v>550</v>
+      </c>
+      <c r="AB11" t="str">
+        <v>212.67</v>
+      </c>
+      <c r="AC11" t="str">
+        <v>550</v>
+      </c>
+      <c r="AD11" t="str">
+        <v>212.67</v>
+      </c>
+      <c r="AE11" t="str">
+        <v>550</v>
+      </c>
+      <c r="AF11" t="str">
+        <v>212.67</v>
+      </c>
+      <c r="AG11" t="str">
+        <v>1941.5</v>
+      </c>
+      <c r="AH11" t="str">
+        <v>205</v>
+      </c>
+      <c r="AI11" t="str">
+        <v>2200</v>
+      </c>
+      <c r="AJ11" t="str">
+        <v>205</v>
+      </c>
+      <c r="AK11" t="str">
+        <v>2200</v>
+      </c>
+      <c r="AL11" t="str">
+        <v>205</v>
+      </c>
     </row>
     <row r="12">
       <c r="C12" t="str">
@@ -986,6 +1682,36 @@
       <c r="P12" t="str">
         <v>209.45_x000d_</v>
       </c>
+      <c r="S12" t="str">
+        <v>12800</v>
+      </c>
+      <c r="T12" t="str">
+        <v>125</v>
+      </c>
+      <c r="Y12" t="str">
+        <v>600</v>
+      </c>
+      <c r="Z12" t="str">
+        <v>210.67</v>
+      </c>
+      <c r="AA12" t="str">
+        <v>600</v>
+      </c>
+      <c r="AB12" t="str">
+        <v>210.67</v>
+      </c>
+      <c r="AC12" t="str">
+        <v>600</v>
+      </c>
+      <c r="AD12" t="str">
+        <v>210.67</v>
+      </c>
+      <c r="AE12" t="str">
+        <v>600</v>
+      </c>
+      <c r="AF12" t="str">
+        <v>210.67</v>
+      </c>
     </row>
     <row r="13">
       <c r="C13" t="str">
@@ -1030,6 +1756,36 @@
       <c r="P13" t="str">
         <v>209.82_x000d_</v>
       </c>
+      <c r="S13" t="str">
+        <v>13300</v>
+      </c>
+      <c r="T13" t="str">
+        <v>125.5</v>
+      </c>
+      <c r="Y13" t="str">
+        <v>650</v>
+      </c>
+      <c r="Z13" t="str">
+        <v>209</v>
+      </c>
+      <c r="AA13" t="str">
+        <v>650</v>
+      </c>
+      <c r="AB13" t="str">
+        <v>209</v>
+      </c>
+      <c r="AC13" t="str">
+        <v>650</v>
+      </c>
+      <c r="AD13" t="str">
+        <v>209</v>
+      </c>
+      <c r="AE13" t="str">
+        <v>650</v>
+      </c>
+      <c r="AF13" t="str">
+        <v>209</v>
+      </c>
     </row>
     <row r="14">
       <c r="C14" t="str">
@@ -1074,6 +1830,36 @@
       <c r="P14" t="str">
         <v>210.18</v>
       </c>
+      <c r="S14" t="str">
+        <v>13600</v>
+      </c>
+      <c r="T14" t="str">
+        <v>126</v>
+      </c>
+      <c r="Y14" t="str">
+        <v>700</v>
+      </c>
+      <c r="Z14" t="str">
+        <v>208.33</v>
+      </c>
+      <c r="AA14" t="str">
+        <v>700</v>
+      </c>
+      <c r="AB14" t="str">
+        <v>208.33</v>
+      </c>
+      <c r="AC14" t="str">
+        <v>700</v>
+      </c>
+      <c r="AD14" t="str">
+        <v>208.33</v>
+      </c>
+      <c r="AE14" t="str">
+        <v>700</v>
+      </c>
+      <c r="AF14" t="str">
+        <v>208.33</v>
+      </c>
     </row>
     <row r="15">
       <c r="C15" t="str">
@@ -1082,6 +1868,36 @@
       <c r="D15" t="str">
         <v>126.5</v>
       </c>
+      <c r="S15" t="str">
+        <v>14000</v>
+      </c>
+      <c r="T15" t="str">
+        <v>126.5</v>
+      </c>
+      <c r="Y15" t="str">
+        <v>750</v>
+      </c>
+      <c r="Z15" t="str">
+        <v>208</v>
+      </c>
+      <c r="AA15" t="str">
+        <v>750</v>
+      </c>
+      <c r="AB15" t="str">
+        <v>208</v>
+      </c>
+      <c r="AC15" t="str">
+        <v>750</v>
+      </c>
+      <c r="AD15" t="str">
+        <v>208</v>
+      </c>
+      <c r="AE15" t="str">
+        <v>750</v>
+      </c>
+      <c r="AF15" t="str">
+        <v>208</v>
+      </c>
     </row>
     <row r="16">
       <c r="C16" t="str">
@@ -1090,6 +1906,36 @@
       <c r="D16" t="str">
         <v>127</v>
       </c>
+      <c r="S16" t="str">
+        <v>14300</v>
+      </c>
+      <c r="T16" t="str">
+        <v>127</v>
+      </c>
+      <c r="Y16" t="str">
+        <v>800</v>
+      </c>
+      <c r="Z16" t="str">
+        <v>208.67</v>
+      </c>
+      <c r="AA16" t="str">
+        <v>800</v>
+      </c>
+      <c r="AB16" t="str">
+        <v>208.67</v>
+      </c>
+      <c r="AC16" t="str">
+        <v>800</v>
+      </c>
+      <c r="AD16" t="str">
+        <v>208.67</v>
+      </c>
+      <c r="AE16" t="str">
+        <v>800</v>
+      </c>
+      <c r="AF16" t="str">
+        <v>208.67</v>
+      </c>
     </row>
     <row r="17">
       <c r="C17" t="str">
@@ -1098,6 +1944,36 @@
       <c r="D17" t="str">
         <v>127.5</v>
       </c>
+      <c r="S17" t="str">
+        <v>14700</v>
+      </c>
+      <c r="T17" t="str">
+        <v>127.5</v>
+      </c>
+      <c r="Y17" t="str">
+        <v>850</v>
+      </c>
+      <c r="Z17" t="str">
+        <v>209.33</v>
+      </c>
+      <c r="AA17" t="str">
+        <v>850</v>
+      </c>
+      <c r="AB17" t="str">
+        <v>209.33</v>
+      </c>
+      <c r="AC17" t="str">
+        <v>850</v>
+      </c>
+      <c r="AD17" t="str">
+        <v>209.33</v>
+      </c>
+      <c r="AE17" t="str">
+        <v>850</v>
+      </c>
+      <c r="AF17" t="str">
+        <v>209.33</v>
+      </c>
     </row>
     <row r="18">
       <c r="C18" t="str">
@@ -1106,10 +1982,92 @@
       <c r="D18" t="str">
         <v>128</v>
       </c>
+      <c r="S18" t="str">
+        <v>15000</v>
+      </c>
+      <c r="T18" t="str">
+        <v>128</v>
+      </c>
+      <c r="Y18" t="str">
+        <v>900</v>
+      </c>
+      <c r="Z18" t="str">
+        <v>210.33</v>
+      </c>
+      <c r="AA18" t="str">
+        <v>900</v>
+      </c>
+      <c r="AB18" t="str">
+        <v>210.33</v>
+      </c>
+      <c r="AC18" t="str">
+        <v>900</v>
+      </c>
+      <c r="AD18" t="str">
+        <v>210.33</v>
+      </c>
+      <c r="AE18" t="str">
+        <v>900</v>
+      </c>
+      <c r="AF18" t="str">
+        <v>210.33</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="Y19" t="str">
+        <v>950</v>
+      </c>
+      <c r="Z19" t="str">
+        <v>212</v>
+      </c>
+      <c r="AA19" t="str">
+        <v>950</v>
+      </c>
+      <c r="AB19" t="str">
+        <v>212</v>
+      </c>
+      <c r="AC19" t="str">
+        <v>950</v>
+      </c>
+      <c r="AD19" t="str">
+        <v>212</v>
+      </c>
+      <c r="AE19" t="str">
+        <v>950</v>
+      </c>
+      <c r="AF19" t="str">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="Y20" t="str">
+        <v>1000</v>
+      </c>
+      <c r="Z20" t="str">
+        <v>213.67</v>
+      </c>
+      <c r="AA20" t="str">
+        <v>1000</v>
+      </c>
+      <c r="AB20" t="str">
+        <v>213.67</v>
+      </c>
+      <c r="AC20" t="str">
+        <v>1000</v>
+      </c>
+      <c r="AD20" t="str">
+        <v>213.67</v>
+      </c>
+      <c r="AE20" t="str">
+        <v>1000</v>
+      </c>
+      <c r="AF20" t="str">
+        <v>213.67</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P18"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AL20"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/storage/app/Titik Ori Grafik.xlsx
+++ b/storage/app/Titik Ori Grafik.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AL20"/>
+  <dimension ref="A1:AT20"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -514,6 +514,30 @@
       <c r="AL1" t="str">
         <v>PRA Y</v>
       </c>
+      <c r="AM1" t="str">
+        <v>HAN X</v>
+      </c>
+      <c r="AN1" t="str">
+        <v>HAN Y</v>
+      </c>
+      <c r="AO1" t="str">
+        <v>HAP X</v>
+      </c>
+      <c r="AP1" t="str">
+        <v>HAP Y</v>
+      </c>
+      <c r="AQ1" t="str">
+        <v>HAS X</v>
+      </c>
+      <c r="AR1" t="str">
+        <v>HAS Y</v>
+      </c>
+      <c r="AS1" t="str">
+        <v>HAY X</v>
+      </c>
+      <c r="AT1" t="str">
+        <v>HAY Y</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -630,6 +654,30 @@
       <c r="AL2" t="str">
         <v>240</v>
       </c>
+      <c r="AM2" t="str">
+        <v>1914</v>
+      </c>
+      <c r="AN2" t="str">
+        <v>175</v>
+      </c>
+      <c r="AO2" t="str">
+        <v>1914</v>
+      </c>
+      <c r="AP2" t="str">
+        <v>175</v>
+      </c>
+      <c r="AQ2" t="str">
+        <v>1914</v>
+      </c>
+      <c r="AR2" t="str">
+        <v>175</v>
+      </c>
+      <c r="AS2" t="str">
+        <v>1914</v>
+      </c>
+      <c r="AT2" t="str">
+        <v>175</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -746,6 +794,30 @@
       <c r="AL3" t="str">
         <v>234</v>
       </c>
+      <c r="AM3" t="str">
+        <v>2168</v>
+      </c>
+      <c r="AN3" t="str">
+        <v>174.2</v>
+      </c>
+      <c r="AO3" t="str">
+        <v>2168</v>
+      </c>
+      <c r="AP3" t="str">
+        <v>174.2</v>
+      </c>
+      <c r="AQ3" t="str">
+        <v>2168</v>
+      </c>
+      <c r="AR3" t="str">
+        <v>174.2</v>
+      </c>
+      <c r="AS3" t="str">
+        <v>2168</v>
+      </c>
+      <c r="AT3" t="str">
+        <v>174.2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -862,6 +934,30 @@
       <c r="AL4" t="str">
         <v>223.67</v>
       </c>
+      <c r="AM4" t="str">
+        <v>2562</v>
+      </c>
+      <c r="AN4" t="str">
+        <v>171.1</v>
+      </c>
+      <c r="AO4" t="str">
+        <v>2562</v>
+      </c>
+      <c r="AP4" t="str">
+        <v>171.1</v>
+      </c>
+      <c r="AQ4" t="str">
+        <v>2562</v>
+      </c>
+      <c r="AR4" t="str">
+        <v>171.1</v>
+      </c>
+      <c r="AS4" t="str">
+        <v>2562</v>
+      </c>
+      <c r="AT4" t="str">
+        <v>171.1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -2067,7 +2163,7 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AL20"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AT20"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/storage/app/Titik Ori Grafik.xlsx
+++ b/storage/app/Titik Ori Grafik.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BX31"/>
+  <dimension ref="A1:CL31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -623,9 +623,51 @@
         <v>PSM Y</v>
       </c>
       <c r="BW1" t="str">
+        <v>RAT X</v>
+      </c>
+      <c r="BX1" t="str">
+        <v>RAT Y</v>
+      </c>
+      <c r="BY1" t="str">
+        <v>RUM X</v>
+      </c>
+      <c r="BZ1" t="str">
+        <v>RUM Y</v>
+      </c>
+      <c r="CA1" t="str">
+        <v>OPA X</v>
+      </c>
+      <c r="CB1" t="str">
+        <v>OPA Y</v>
+      </c>
+      <c r="CC1" t="str">
+        <v>OSA X</v>
+      </c>
+      <c r="CD1" t="str">
+        <v>OSA Y</v>
+      </c>
+      <c r="CE1" t="str">
+        <v>ASN X</v>
+      </c>
+      <c r="CF1" t="str">
+        <v>ASN Y</v>
+      </c>
+      <c r="CG1" t="str">
+        <v>ASG X</v>
+      </c>
+      <c r="CH1" t="str">
+        <v>ASG Y</v>
+      </c>
+      <c r="CI1" t="str">
+        <v>ASR X</v>
+      </c>
+      <c r="CJ1" t="str">
+        <v>ASR Y</v>
+      </c>
+      <c r="CK1" t="str">
         <v>PNN X</v>
       </c>
-      <c r="BX1" t="str">
+      <c r="CL1" t="str">
         <v>PNN Y</v>
       </c>
     </row>
@@ -853,9 +895,51 @@
         <v>209.3</v>
       </c>
       <c r="BW2" t="str">
+        <v>638</v>
+      </c>
+      <c r="BX2" t="str">
+        <v>215.7</v>
+      </c>
+      <c r="BY2" t="str">
+        <v>638</v>
+      </c>
+      <c r="BZ2" t="str">
+        <v>215.7</v>
+      </c>
+      <c r="CA2" t="str">
+        <v>827</v>
+      </c>
+      <c r="CB2" t="str">
+        <v>204_x000d_</v>
+      </c>
+      <c r="CC2" t="str">
+        <v>827</v>
+      </c>
+      <c r="CD2" t="str">
+        <v>204_x000d_</v>
+      </c>
+      <c r="CE2" t="str">
+        <v>2220</v>
+      </c>
+      <c r="CF2" t="str">
+        <v>213.6</v>
+      </c>
+      <c r="CG2" t="str">
+        <v>2220</v>
+      </c>
+      <c r="CH2" t="str">
+        <v>213.6</v>
+      </c>
+      <c r="CI2" t="str">
+        <v>2220</v>
+      </c>
+      <c r="CJ2" t="str">
+        <v>213.6</v>
+      </c>
+      <c r="CK2" t="str">
         <v>163.64</v>
       </c>
-      <c r="BX2" t="str">
+      <c r="CL2" t="str">
         <v>275.27</v>
       </c>
     </row>
@@ -1083,9 +1167,51 @@
         <v>214.3</v>
       </c>
       <c r="BW3" t="str">
+        <v>1270</v>
+      </c>
+      <c r="BX3" t="str">
+        <v>202.2</v>
+      </c>
+      <c r="BY3" t="str">
+        <v>1270</v>
+      </c>
+      <c r="BZ3" t="str">
+        <v>202.2</v>
+      </c>
+      <c r="CA3" t="str">
+        <v>1655</v>
+      </c>
+      <c r="CB3" t="str">
+        <v>197_x000d_</v>
+      </c>
+      <c r="CC3" t="str">
+        <v>1655</v>
+      </c>
+      <c r="CD3" t="str">
+        <v>197_x000d_</v>
+      </c>
+      <c r="CE3" t="str">
+        <v>3330</v>
+      </c>
+      <c r="CF3" t="str">
+        <v>210.4</v>
+      </c>
+      <c r="CG3" t="str">
+        <v>3330</v>
+      </c>
+      <c r="CH3" t="str">
+        <v>210.4</v>
+      </c>
+      <c r="CI3" t="str">
+        <v>3330</v>
+      </c>
+      <c r="CJ3" t="str">
+        <v>210.4</v>
+      </c>
+      <c r="CK3" t="str">
         <v>218.18</v>
       </c>
-      <c r="BX3" t="str">
+      <c r="CL3" t="str">
         <v>266.55</v>
       </c>
     </row>
@@ -1301,9 +1427,51 @@
         <v>128.4</v>
       </c>
       <c r="BW4" t="str">
+        <v>1920</v>
+      </c>
+      <c r="BX4" t="str">
+        <v>198.6</v>
+      </c>
+      <c r="BY4" t="str">
+        <v>1920</v>
+      </c>
+      <c r="BZ4" t="str">
+        <v>198.6</v>
+      </c>
+      <c r="CA4" t="str">
+        <v>2482</v>
+      </c>
+      <c r="CB4" t="str">
+        <v>192_x000d_</v>
+      </c>
+      <c r="CC4" t="str">
+        <v>2482</v>
+      </c>
+      <c r="CD4" t="str">
+        <v>192_x000d_</v>
+      </c>
+      <c r="CE4" t="str">
+        <v>4440</v>
+      </c>
+      <c r="CF4" t="str">
+        <v>206.5</v>
+      </c>
+      <c r="CG4" t="str">
+        <v>4440</v>
+      </c>
+      <c r="CH4" t="str">
+        <v>206.5</v>
+      </c>
+      <c r="CI4" t="str">
+        <v>4440</v>
+      </c>
+      <c r="CJ4" t="str">
+        <v>206.5</v>
+      </c>
+      <c r="CK4" t="str">
         <v>358.18</v>
       </c>
-      <c r="BX4" t="str">
+      <c r="CL4" t="str">
         <v>254.36</v>
       </c>
     </row>
@@ -1495,9 +1663,33 @@
         <v>131.6</v>
       </c>
       <c r="BW5" t="str">
+        <v>2300</v>
+      </c>
+      <c r="BX5" t="str">
+        <v>199.8</v>
+      </c>
+      <c r="BY5" t="str">
+        <v>2300</v>
+      </c>
+      <c r="BZ5" t="str">
+        <v>199.8</v>
+      </c>
+      <c r="CA5" t="str">
+        <v>2979</v>
+      </c>
+      <c r="CB5" t="str">
+        <v>194_x000d_</v>
+      </c>
+      <c r="CC5" t="str">
+        <v>2979</v>
+      </c>
+      <c r="CD5" t="str">
+        <v>194_x000d_</v>
+      </c>
+      <c r="CK5" t="str">
         <v>467.27</v>
       </c>
-      <c r="BX5" t="str">
+      <c r="CL5" t="str">
         <v>242.36</v>
       </c>
     </row>
@@ -1689,9 +1881,33 @@
         <v>131.3</v>
       </c>
       <c r="BW6" t="str">
+        <v>2574</v>
+      </c>
+      <c r="BX6" t="str">
+        <v>200.3</v>
+      </c>
+      <c r="BY6" t="str">
+        <v>2574</v>
+      </c>
+      <c r="BZ6" t="str">
+        <v>200.3</v>
+      </c>
+      <c r="CA6" t="str">
+        <v>3310</v>
+      </c>
+      <c r="CB6" t="str">
+        <v>197_x000d_</v>
+      </c>
+      <c r="CC6" t="str">
+        <v>3310</v>
+      </c>
+      <c r="CD6" t="str">
+        <v>197_x000d_</v>
+      </c>
+      <c r="CK6" t="str">
         <v>614.55</v>
       </c>
-      <c r="BX6" t="str">
+      <c r="CL6" t="str">
         <v>232.36</v>
       </c>
     </row>
@@ -1883,9 +2099,33 @@
         <v>133.5</v>
       </c>
       <c r="BW7" t="str">
+        <v>2840</v>
+      </c>
+      <c r="BX7" t="str">
+        <v>206.2</v>
+      </c>
+      <c r="BY7" t="str">
+        <v>2840</v>
+      </c>
+      <c r="BZ7" t="str">
+        <v>206.2</v>
+      </c>
+      <c r="CA7" t="str">
+        <v>3641</v>
+      </c>
+      <c r="CB7" t="str">
+        <v>201</v>
+      </c>
+      <c r="CC7" t="str">
+        <v>3641</v>
+      </c>
+      <c r="CD7" t="str">
+        <v>201</v>
+      </c>
+      <c r="CK7" t="str">
         <v>796.36</v>
       </c>
-      <c r="BX7" t="str">
+      <c r="CL7" t="str">
         <v>224</v>
       </c>
     </row>
@@ -2064,10 +2304,10 @@
       <c r="BR8" t="str">
         <v>130.5</v>
       </c>
-      <c r="BW8" t="str">
+      <c r="CK8" t="str">
         <v>1010.91</v>
       </c>
-      <c r="BX8" t="str">
+      <c r="CL8" t="str">
         <v>218</v>
       </c>
     </row>
@@ -2246,10 +2486,10 @@
       <c r="BR9" t="str">
         <v>130</v>
       </c>
-      <c r="BW9" t="str">
+      <c r="CK9" t="str">
         <v>1265.45</v>
       </c>
-      <c r="BX9" t="str">
+      <c r="CL9" t="str">
         <v>213.09</v>
       </c>
     </row>
@@ -2416,10 +2656,10 @@
       <c r="BR10" t="str">
         <v>129.5</v>
       </c>
-      <c r="BW10" t="str">
+      <c r="CK10" t="str">
         <v>1567.27</v>
       </c>
-      <c r="BX10" t="str">
+      <c r="CL10" t="str">
         <v>209.45</v>
       </c>
     </row>
@@ -2574,10 +2814,10 @@
       <c r="BR11" t="str">
         <v>129</v>
       </c>
-      <c r="BW11" t="str">
+      <c r="CK11" t="str">
         <v>1909.09</v>
       </c>
-      <c r="BX11" t="str">
+      <c r="CL11" t="str">
         <v>208.18</v>
       </c>
     </row>
@@ -2684,10 +2924,10 @@
       <c r="BR12" t="str">
         <v>128.5</v>
       </c>
-      <c r="BW12" t="str">
+      <c r="CK12" t="str">
         <v>2309.09</v>
       </c>
-      <c r="BX12" t="str">
+      <c r="CL12" t="str">
         <v>209.64</v>
       </c>
     </row>
@@ -2782,10 +3022,10 @@
       <c r="BR13" t="str">
         <v>128</v>
       </c>
-      <c r="BW13" t="str">
+      <c r="CK13" t="str">
         <v>2421.05</v>
       </c>
-      <c r="BX13" t="str">
+      <c r="CL13" t="str">
         <v>210.36</v>
       </c>
     </row>
@@ -3181,7 +3421,7 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:BX31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:CL31"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/storage/app/Titik Ori Grafik.xlsx
+++ b/storage/app/Titik Ori Grafik.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CL31"/>
+  <dimension ref="A1:CP131"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -578,7 +578,7 @@
         <v>ORU X</v>
       </c>
       <c r="BH1" t="str">
-        <v>ORU Y</v>
+        <v>ORU Y_x000d_</v>
       </c>
       <c r="BI1" t="str">
         <v>REN X</v>
@@ -587,87 +587,99 @@
         <v>REN Y</v>
       </c>
       <c r="BK1" t="str">
+        <v>RET X</v>
+      </c>
+      <c r="BL1" t="str">
+        <v>RET Y</v>
+      </c>
+      <c r="BM1" t="str">
+        <v>RAH X</v>
+      </c>
+      <c r="BN1" t="str">
+        <v>RAH Y</v>
+      </c>
+      <c r="BO1" t="str">
         <v xml:space="preserve"> PBE X</v>
       </c>
-      <c r="BL1" t="str">
+      <c r="BP1" t="str">
         <v>PBE Y</v>
       </c>
-      <c r="BM1" t="str">
+      <c r="BQ1" t="str">
         <v>OGA X</v>
       </c>
-      <c r="BN1" t="str">
+      <c r="BR1" t="str">
         <v>OGA Y</v>
       </c>
-      <c r="BO1" t="str">
+      <c r="BS1" t="str">
         <v>LUZ X</v>
       </c>
-      <c r="BP1" t="str">
+      <c r="BT1" t="str">
         <v>LUZ Y</v>
       </c>
-      <c r="BQ1" t="str">
+      <c r="BU1" t="str">
         <v>HJE X</v>
       </c>
-      <c r="BR1" t="str">
+      <c r="BV1" t="str">
         <v>HJE Y</v>
       </c>
-      <c r="BS1" t="str">
+      <c r="BW1" t="str">
         <v>HSJ X</v>
       </c>
-      <c r="BT1" t="str">
+      <c r="BX1" t="str">
         <v>HSJ Y</v>
       </c>
-      <c r="BU1" t="str">
+      <c r="BY1" t="str">
         <v>PSM X</v>
       </c>
-      <c r="BV1" t="str">
+      <c r="BZ1" t="str">
         <v>PSM Y</v>
       </c>
-      <c r="BW1" t="str">
+      <c r="CA1" t="str">
         <v>RAT X</v>
       </c>
-      <c r="BX1" t="str">
+      <c r="CB1" t="str">
         <v>RAT Y</v>
       </c>
-      <c r="BY1" t="str">
+      <c r="CC1" t="str">
         <v>RUM X</v>
       </c>
-      <c r="BZ1" t="str">
+      <c r="CD1" t="str">
         <v>RUM Y</v>
       </c>
-      <c r="CA1" t="str">
+      <c r="CE1" t="str">
         <v>OPA X</v>
       </c>
-      <c r="CB1" t="str">
+      <c r="CF1" t="str">
         <v>OPA Y</v>
       </c>
-      <c r="CC1" t="str">
+      <c r="CG1" t="str">
         <v>OSA X</v>
       </c>
-      <c r="CD1" t="str">
+      <c r="CH1" t="str">
         <v>OSA Y</v>
       </c>
-      <c r="CE1" t="str">
+      <c r="CI1" t="str">
         <v>ASN X</v>
       </c>
-      <c r="CF1" t="str">
+      <c r="CJ1" t="str">
         <v>ASN Y</v>
       </c>
-      <c r="CG1" t="str">
+      <c r="CK1" t="str">
         <v>ASG X</v>
       </c>
-      <c r="CH1" t="str">
+      <c r="CL1" t="str">
         <v>ASG Y</v>
       </c>
-      <c r="CI1" t="str">
+      <c r="CM1" t="str">
         <v>ASR X</v>
       </c>
-      <c r="CJ1" t="str">
+      <c r="CN1" t="str">
         <v>ASR Y</v>
       </c>
-      <c r="CK1" t="str">
+      <c r="CO1" t="str">
         <v>PNN X</v>
       </c>
-      <c r="CL1" t="str">
+      <c r="CP1" t="str">
         <v>PNN Y</v>
       </c>
     </row>
@@ -841,16 +853,16 @@
         <v>240</v>
       </c>
       <c r="BE2" t="str">
-        <v>1170</v>
+        <v>5500</v>
       </c>
       <c r="BF2" t="str">
-        <v>171.4</v>
+        <v>175.5</v>
       </c>
       <c r="BG2" t="str">
-        <v>1170</v>
+        <v>5500</v>
       </c>
       <c r="BH2" t="str">
-        <v>171.4</v>
+        <v>175.5_x000d_</v>
       </c>
       <c r="BI2" t="str">
         <v>163.64</v>
@@ -859,76 +871,76 @@
         <v>275.27</v>
       </c>
       <c r="BK2" t="str">
+        <v>163.64</v>
+      </c>
+      <c r="BL2" t="str">
+        <v>275.27</v>
+      </c>
+      <c r="BM2" t="str">
+        <v>163.64</v>
+      </c>
+      <c r="BN2" t="str">
+        <v>275.27_x000d_</v>
+      </c>
+      <c r="BO2" t="str">
         <v>739</v>
       </c>
-      <c r="BL2" t="str">
+      <c r="BP2" t="str">
         <v>209.3</v>
       </c>
-      <c r="BM2" t="str">
+      <c r="BQ2" t="str">
         <v>6900</v>
       </c>
-      <c r="BN2" t="str">
+      <c r="BR2" t="str">
         <v>124.5</v>
       </c>
-      <c r="BO2" t="str">
+      <c r="BS2" t="str">
         <v>2714</v>
       </c>
-      <c r="BP2" t="str">
+      <c r="BT2" t="str">
         <v>190.65</v>
       </c>
-      <c r="BQ2" t="str">
+      <c r="BU2" t="str">
         <v>4350</v>
       </c>
-      <c r="BR2" t="str">
+      <c r="BV2" t="str">
         <v>133.5</v>
       </c>
-      <c r="BS2" t="str">
+      <c r="BW2" t="str">
         <v>2442</v>
       </c>
-      <c r="BT2" t="str">
+      <c r="BX2" t="str">
         <v>135.3</v>
       </c>
-      <c r="BU2" t="str">
+      <c r="BY2" t="str">
         <v>739</v>
       </c>
-      <c r="BV2" t="str">
+      <c r="BZ2" t="str">
         <v>209.3</v>
       </c>
-      <c r="BW2" t="str">
+      <c r="CA2" t="str">
         <v>638</v>
       </c>
-      <c r="BX2" t="str">
+      <c r="CB2" t="str">
         <v>215.7</v>
       </c>
-      <c r="BY2" t="str">
+      <c r="CC2" t="str">
         <v>638</v>
       </c>
-      <c r="BZ2" t="str">
+      <c r="CD2" t="str">
         <v>215.7</v>
       </c>
-      <c r="CA2" t="str">
+      <c r="CE2" t="str">
         <v>827</v>
       </c>
-      <c r="CB2" t="str">
+      <c r="CF2" t="str">
         <v>204_x000d_</v>
       </c>
-      <c r="CC2" t="str">
+      <c r="CG2" t="str">
         <v>827</v>
       </c>
-      <c r="CD2" t="str">
+      <c r="CH2" t="str">
         <v>204_x000d_</v>
-      </c>
-      <c r="CE2" t="str">
-        <v>2220</v>
-      </c>
-      <c r="CF2" t="str">
-        <v>213.6</v>
-      </c>
-      <c r="CG2" t="str">
-        <v>2220</v>
-      </c>
-      <c r="CH2" t="str">
-        <v>213.6</v>
       </c>
       <c r="CI2" t="str">
         <v>2220</v>
@@ -937,9 +949,21 @@
         <v>213.6</v>
       </c>
       <c r="CK2" t="str">
+        <v>2220</v>
+      </c>
+      <c r="CL2" t="str">
+        <v>213.6</v>
+      </c>
+      <c r="CM2" t="str">
+        <v>2220</v>
+      </c>
+      <c r="CN2" t="str">
+        <v>213.6</v>
+      </c>
+      <c r="CO2" t="str">
         <v>163.64</v>
       </c>
-      <c r="CL2" t="str">
+      <c r="CP2" t="str">
         <v>275.27</v>
       </c>
     </row>
@@ -1113,16 +1137,16 @@
         <v>234.35</v>
       </c>
       <c r="BE3" t="str">
-        <v>1287</v>
+        <v>6000</v>
       </c>
       <c r="BF3" t="str">
-        <v>170.27</v>
+        <v>174.5</v>
       </c>
       <c r="BG3" t="str">
-        <v>1287</v>
+        <v>6000</v>
       </c>
       <c r="BH3" t="str">
-        <v>170.27</v>
+        <v>174.5_x000d_</v>
       </c>
       <c r="BI3" t="str">
         <v>218.18</v>
@@ -1131,76 +1155,76 @@
         <v>266.55</v>
       </c>
       <c r="BK3" t="str">
+        <v>218.18</v>
+      </c>
+      <c r="BL3" t="str">
+        <v>266.55</v>
+      </c>
+      <c r="BM3" t="str">
+        <v>218.18</v>
+      </c>
+      <c r="BN3" t="str">
+        <v>266.55_x000d_</v>
+      </c>
+      <c r="BO3" t="str">
         <v>821</v>
       </c>
-      <c r="BL3" t="str">
+      <c r="BP3" t="str">
         <v>214.3</v>
       </c>
-      <c r="BM3" t="str">
+      <c r="BQ3" t="str">
         <v>7450</v>
       </c>
-      <c r="BN3" t="str">
+      <c r="BR3" t="str">
         <v>124</v>
       </c>
-      <c r="BO3" t="str">
+      <c r="BS3" t="str">
         <v>5421</v>
       </c>
-      <c r="BP3" t="str">
+      <c r="BT3" t="str">
         <v>181.22</v>
       </c>
-      <c r="BQ3" t="str">
+      <c r="BU3" t="str">
         <v>4450</v>
       </c>
-      <c r="BR3" t="str">
+      <c r="BV3" t="str">
         <v>133</v>
       </c>
-      <c r="BS3" t="str">
+      <c r="BW3" t="str">
         <v>4877</v>
       </c>
-      <c r="BT3" t="str">
+      <c r="BX3" t="str">
         <v>129.5</v>
       </c>
-      <c r="BU3" t="str">
+      <c r="BY3" t="str">
         <v>821</v>
       </c>
-      <c r="BV3" t="str">
+      <c r="BZ3" t="str">
         <v>214.3</v>
       </c>
-      <c r="BW3" t="str">
+      <c r="CA3" t="str">
         <v>1270</v>
       </c>
-      <c r="BX3" t="str">
+      <c r="CB3" t="str">
         <v>202.2</v>
       </c>
-      <c r="BY3" t="str">
+      <c r="CC3" t="str">
         <v>1270</v>
       </c>
-      <c r="BZ3" t="str">
+      <c r="CD3" t="str">
         <v>202.2</v>
       </c>
-      <c r="CA3" t="str">
+      <c r="CE3" t="str">
         <v>1655</v>
       </c>
-      <c r="CB3" t="str">
+      <c r="CF3" t="str">
         <v>197_x000d_</v>
       </c>
-      <c r="CC3" t="str">
+      <c r="CG3" t="str">
         <v>1655</v>
       </c>
-      <c r="CD3" t="str">
+      <c r="CH3" t="str">
         <v>197_x000d_</v>
-      </c>
-      <c r="CE3" t="str">
-        <v>3330</v>
-      </c>
-      <c r="CF3" t="str">
-        <v>210.4</v>
-      </c>
-      <c r="CG3" t="str">
-        <v>3330</v>
-      </c>
-      <c r="CH3" t="str">
-        <v>210.4</v>
       </c>
       <c r="CI3" t="str">
         <v>3330</v>
@@ -1209,9 +1233,21 @@
         <v>210.4</v>
       </c>
       <c r="CK3" t="str">
+        <v>3330</v>
+      </c>
+      <c r="CL3" t="str">
+        <v>210.4</v>
+      </c>
+      <c r="CM3" t="str">
+        <v>3330</v>
+      </c>
+      <c r="CN3" t="str">
+        <v>210.4</v>
+      </c>
+      <c r="CO3" t="str">
         <v>218.18</v>
       </c>
-      <c r="CL3" t="str">
+      <c r="CP3" t="str">
         <v>266.55</v>
       </c>
     </row>
@@ -1385,16 +1421,16 @@
         <v>223.91</v>
       </c>
       <c r="BE4" t="str">
-        <v>1404</v>
+        <v>6500</v>
       </c>
       <c r="BF4" t="str">
-        <v>169.53</v>
+        <v>173.5</v>
       </c>
       <c r="BG4" t="str">
-        <v>1404</v>
+        <v>6500</v>
       </c>
       <c r="BH4" t="str">
-        <v>169.53</v>
+        <v>173.5_x000d_</v>
       </c>
       <c r="BI4" t="str">
         <v>358.18</v>
@@ -1402,65 +1438,65 @@
       <c r="BJ4" t="str">
         <v>254.36</v>
       </c>
+      <c r="BK4" t="str">
+        <v>358.18</v>
+      </c>
+      <c r="BL4" t="str">
+        <v>254.36</v>
+      </c>
       <c r="BM4" t="str">
+        <v>358.18</v>
+      </c>
+      <c r="BN4" t="str">
+        <v>254.36_x000d_</v>
+      </c>
+      <c r="BQ4" t="str">
         <v>8100</v>
       </c>
-      <c r="BN4" t="str">
+      <c r="BR4" t="str">
         <v>123.5</v>
       </c>
-      <c r="BO4" t="str">
+      <c r="BS4" t="str">
         <v>8261</v>
       </c>
-      <c r="BP4" t="str">
+      <c r="BT4" t="str">
         <v>175.06</v>
       </c>
-      <c r="BQ4" t="str">
+      <c r="BU4" t="str">
         <v>4600</v>
       </c>
-      <c r="BR4" t="str">
+      <c r="BV4" t="str">
         <v>132.5</v>
       </c>
-      <c r="BS4" t="str">
+      <c r="BW4" t="str">
         <v>7329</v>
       </c>
-      <c r="BT4" t="str">
+      <c r="BX4" t="str">
         <v>128.4</v>
       </c>
-      <c r="BW4" t="str">
+      <c r="CA4" t="str">
         <v>1920</v>
       </c>
-      <c r="BX4" t="str">
+      <c r="CB4" t="str">
         <v>198.6</v>
       </c>
-      <c r="BY4" t="str">
+      <c r="CC4" t="str">
         <v>1920</v>
       </c>
-      <c r="BZ4" t="str">
+      <c r="CD4" t="str">
         <v>198.6</v>
       </c>
-      <c r="CA4" t="str">
+      <c r="CE4" t="str">
         <v>2482</v>
       </c>
-      <c r="CB4" t="str">
+      <c r="CF4" t="str">
         <v>192_x000d_</v>
       </c>
-      <c r="CC4" t="str">
+      <c r="CG4" t="str">
         <v>2482</v>
       </c>
-      <c r="CD4" t="str">
+      <c r="CH4" t="str">
         <v>192_x000d_</v>
-      </c>
-      <c r="CE4" t="str">
-        <v>4440</v>
-      </c>
-      <c r="CF4" t="str">
-        <v>206.5</v>
-      </c>
-      <c r="CG4" t="str">
-        <v>4440</v>
-      </c>
-      <c r="CH4" t="str">
-        <v>206.5</v>
       </c>
       <c r="CI4" t="str">
         <v>4440</v>
@@ -1469,9 +1505,21 @@
         <v>206.5</v>
       </c>
       <c r="CK4" t="str">
+        <v>4440</v>
+      </c>
+      <c r="CL4" t="str">
+        <v>206.5</v>
+      </c>
+      <c r="CM4" t="str">
+        <v>4440</v>
+      </c>
+      <c r="CN4" t="str">
+        <v>206.5</v>
+      </c>
+      <c r="CO4" t="str">
         <v>358.18</v>
       </c>
-      <c r="CL4" t="str">
+      <c r="CP4" t="str">
         <v>254.36</v>
       </c>
     </row>
@@ -1621,16 +1669,16 @@
         <v>217.61</v>
       </c>
       <c r="BE5" t="str">
-        <v>1521</v>
+        <v>7000</v>
       </c>
       <c r="BF5" t="str">
-        <v>168.8</v>
+        <v>172.5</v>
       </c>
       <c r="BG5" t="str">
-        <v>1521</v>
+        <v>7000</v>
       </c>
       <c r="BH5" t="str">
-        <v>168.8</v>
+        <v>172.5_x000d_</v>
       </c>
       <c r="BI5" t="str">
         <v>467.27</v>
@@ -1638,58 +1686,70 @@
       <c r="BJ5" t="str">
         <v>242.36</v>
       </c>
+      <c r="BK5" t="str">
+        <v>467.27</v>
+      </c>
+      <c r="BL5" t="str">
+        <v>242.36</v>
+      </c>
       <c r="BM5" t="str">
+        <v>467.27</v>
+      </c>
+      <c r="BN5" t="str">
+        <v>242.36_x000d_</v>
+      </c>
+      <c r="BQ5" t="str">
         <v>8900</v>
       </c>
-      <c r="BN5" t="str">
+      <c r="BR5" t="str">
         <v>123</v>
       </c>
-      <c r="BO5" t="str">
+      <c r="BS5" t="str">
         <v>9808</v>
       </c>
-      <c r="BP5" t="str">
+      <c r="BT5" t="str">
         <v>175.36</v>
       </c>
-      <c r="BQ5" t="str">
+      <c r="BU5" t="str">
         <v>4700</v>
       </c>
-      <c r="BR5" t="str">
+      <c r="BV5" t="str">
         <v>132</v>
       </c>
-      <c r="BS5" t="str">
+      <c r="BW5" t="str">
         <v>9759</v>
       </c>
-      <c r="BT5" t="str">
+      <c r="BX5" t="str">
         <v>131.6</v>
       </c>
-      <c r="BW5" t="str">
+      <c r="CA5" t="str">
         <v>2300</v>
       </c>
-      <c r="BX5" t="str">
+      <c r="CB5" t="str">
         <v>199.8</v>
       </c>
-      <c r="BY5" t="str">
+      <c r="CC5" t="str">
         <v>2300</v>
       </c>
-      <c r="BZ5" t="str">
+      <c r="CD5" t="str">
         <v>199.8</v>
       </c>
-      <c r="CA5" t="str">
+      <c r="CE5" t="str">
         <v>2979</v>
       </c>
-      <c r="CB5" t="str">
+      <c r="CF5" t="str">
         <v>194_x000d_</v>
       </c>
-      <c r="CC5" t="str">
+      <c r="CG5" t="str">
         <v>2979</v>
       </c>
-      <c r="CD5" t="str">
+      <c r="CH5" t="str">
         <v>194_x000d_</v>
       </c>
-      <c r="CK5" t="str">
+      <c r="CO5" t="str">
         <v>467.27</v>
       </c>
-      <c r="CL5" t="str">
+      <c r="CP5" t="str">
         <v>242.36</v>
       </c>
     </row>
@@ -1839,16 +1899,16 @@
         <v>211.96</v>
       </c>
       <c r="BE6" t="str">
-        <v>1638</v>
+        <v>7500</v>
       </c>
       <c r="BF6" t="str">
-        <v>168.33</v>
+        <v>171.5</v>
       </c>
       <c r="BG6" t="str">
-        <v>1638</v>
+        <v>7500</v>
       </c>
       <c r="BH6" t="str">
-        <v>168.33</v>
+        <v>171.5_x000d_</v>
       </c>
       <c r="BI6" t="str">
         <v>614.55</v>
@@ -1856,58 +1916,70 @@
       <c r="BJ6" t="str">
         <v>232.36</v>
       </c>
+      <c r="BK6" t="str">
+        <v>614.55</v>
+      </c>
+      <c r="BL6" t="str">
+        <v>232.36</v>
+      </c>
       <c r="BM6" t="str">
+        <v>614.55</v>
+      </c>
+      <c r="BN6" t="str">
+        <v>232.36_x000d_</v>
+      </c>
+      <c r="BQ6" t="str">
         <v>9650</v>
       </c>
-      <c r="BN6" t="str">
+      <c r="BR6" t="str">
         <v>122.5</v>
       </c>
-      <c r="BO6" t="str">
+      <c r="BS6" t="str">
         <v>10913</v>
       </c>
-      <c r="BP6" t="str">
+      <c r="BT6" t="str">
         <v>177.19</v>
       </c>
-      <c r="BQ6" t="str">
+      <c r="BU6" t="str">
         <v>4900</v>
       </c>
-      <c r="BR6" t="str">
+      <c r="BV6" t="str">
         <v>131.5</v>
       </c>
-      <c r="BS6" t="str">
+      <c r="BW6" t="str">
         <v>9775</v>
       </c>
-      <c r="BT6" t="str">
+      <c r="BX6" t="str">
         <v>131.3</v>
       </c>
-      <c r="BW6" t="str">
+      <c r="CA6" t="str">
         <v>2574</v>
       </c>
-      <c r="BX6" t="str">
+      <c r="CB6" t="str">
         <v>200.3</v>
       </c>
-      <c r="BY6" t="str">
+      <c r="CC6" t="str">
         <v>2574</v>
       </c>
-      <c r="BZ6" t="str">
+      <c r="CD6" t="str">
         <v>200.3</v>
       </c>
-      <c r="CA6" t="str">
+      <c r="CE6" t="str">
         <v>3310</v>
       </c>
-      <c r="CB6" t="str">
+      <c r="CF6" t="str">
         <v>197_x000d_</v>
       </c>
-      <c r="CC6" t="str">
+      <c r="CG6" t="str">
         <v>3310</v>
       </c>
-      <c r="CD6" t="str">
+      <c r="CH6" t="str">
         <v>197_x000d_</v>
       </c>
-      <c r="CK6" t="str">
+      <c r="CO6" t="str">
         <v>614.55</v>
       </c>
-      <c r="CL6" t="str">
+      <c r="CP6" t="str">
         <v>232.36</v>
       </c>
     </row>
@@ -2057,16 +2129,16 @@
         <v>208.7</v>
       </c>
       <c r="BE7" t="str">
-        <v>1755</v>
+        <v>8000</v>
       </c>
       <c r="BF7" t="str">
-        <v>168.13</v>
+        <v>170.5</v>
       </c>
       <c r="BG7" t="str">
-        <v>1755</v>
+        <v>8000</v>
       </c>
       <c r="BH7" t="str">
-        <v>168.13</v>
+        <v>170.5_x000d_</v>
       </c>
       <c r="BI7" t="str">
         <v>796.36</v>
@@ -2074,58 +2146,70 @@
       <c r="BJ7" t="str">
         <v>224</v>
       </c>
+      <c r="BK7" t="str">
+        <v>796.36</v>
+      </c>
+      <c r="BL7" t="str">
+        <v>224</v>
+      </c>
       <c r="BM7" t="str">
+        <v>796.36</v>
+      </c>
+      <c r="BN7" t="str">
+        <v>224_x000d_</v>
+      </c>
+      <c r="BQ7" t="str">
         <v>10500</v>
       </c>
-      <c r="BN7" t="str">
+      <c r="BR7" t="str">
         <v>122</v>
       </c>
-      <c r="BO7" t="str">
+      <c r="BS7" t="str">
         <v>11927</v>
       </c>
-      <c r="BP7" t="str">
+      <c r="BT7" t="str">
         <v>180.2</v>
       </c>
-      <c r="BQ7" t="str">
+      <c r="BU7" t="str">
         <v>5050</v>
       </c>
-      <c r="BR7" t="str">
+      <c r="BV7" t="str">
         <v>131</v>
       </c>
-      <c r="BS7" t="str">
+      <c r="BW7" t="str">
         <v>10740</v>
       </c>
-      <c r="BT7" t="str">
+      <c r="BX7" t="str">
         <v>133.5</v>
       </c>
-      <c r="BW7" t="str">
+      <c r="CA7" t="str">
         <v>2840</v>
       </c>
-      <c r="BX7" t="str">
+      <c r="CB7" t="str">
         <v>206.2</v>
       </c>
-      <c r="BY7" t="str">
+      <c r="CC7" t="str">
         <v>2840</v>
       </c>
-      <c r="BZ7" t="str">
+      <c r="CD7" t="str">
         <v>206.2</v>
       </c>
-      <c r="CA7" t="str">
+      <c r="CE7" t="str">
         <v>3641</v>
       </c>
-      <c r="CB7" t="str">
+      <c r="CF7" t="str">
         <v>201</v>
       </c>
-      <c r="CC7" t="str">
+      <c r="CG7" t="str">
         <v>3641</v>
       </c>
-      <c r="CD7" t="str">
+      <c r="CH7" t="str">
         <v>201</v>
       </c>
-      <c r="CK7" t="str">
+      <c r="CO7" t="str">
         <v>796.36</v>
       </c>
-      <c r="CL7" t="str">
+      <c r="CP7" t="str">
         <v>224</v>
       </c>
     </row>
@@ -2275,16 +2359,16 @@
         <v>206.3</v>
       </c>
       <c r="BE8" t="str">
-        <v>1872</v>
+        <v>8500</v>
       </c>
       <c r="BF8" t="str">
-        <v>168.13</v>
+        <v>170</v>
       </c>
       <c r="BG8" t="str">
-        <v>1872</v>
+        <v>8500</v>
       </c>
       <c r="BH8" t="str">
-        <v>168.13</v>
+        <v>170_x000d_</v>
       </c>
       <c r="BI8" t="str">
         <v>1010.91</v>
@@ -2292,22 +2376,34 @@
       <c r="BJ8" t="str">
         <v>218</v>
       </c>
+      <c r="BK8" t="str">
+        <v>1010.91</v>
+      </c>
+      <c r="BL8" t="str">
+        <v>218</v>
+      </c>
       <c r="BM8" t="str">
+        <v>1010.91</v>
+      </c>
+      <c r="BN8" t="str">
+        <v>218_x000d_</v>
+      </c>
+      <c r="BQ8" t="str">
         <v>11600</v>
       </c>
-      <c r="BN8" t="str">
+      <c r="BR8" t="str">
         <v>121.5</v>
       </c>
-      <c r="BQ8" t="str">
+      <c r="BU8" t="str">
         <v>5200</v>
       </c>
-      <c r="BR8" t="str">
+      <c r="BV8" t="str">
         <v>130.5</v>
       </c>
-      <c r="CK8" t="str">
+      <c r="CO8" t="str">
         <v>1010.91</v>
       </c>
-      <c r="CL8" t="str">
+      <c r="CP8" t="str">
         <v>218</v>
       </c>
     </row>
@@ -2457,16 +2553,16 @@
         <v>204.78</v>
       </c>
       <c r="BE9" t="str">
-        <v>1989</v>
+        <v>9000</v>
       </c>
       <c r="BF9" t="str">
-        <v>168.4</v>
+        <v>169.5</v>
       </c>
       <c r="BG9" t="str">
-        <v>1989</v>
+        <v>9000</v>
       </c>
       <c r="BH9" t="str">
-        <v>168.4</v>
+        <v>169.5_x000d_</v>
       </c>
       <c r="BI9" t="str">
         <v>1265.45</v>
@@ -2474,22 +2570,34 @@
       <c r="BJ9" t="str">
         <v>213.09</v>
       </c>
+      <c r="BK9" t="str">
+        <v>1265.45</v>
+      </c>
+      <c r="BL9" t="str">
+        <v>213.09</v>
+      </c>
       <c r="BM9" t="str">
+        <v>1265.45</v>
+      </c>
+      <c r="BN9" t="str">
+        <v>213.09_x000d_</v>
+      </c>
+      <c r="BQ9" t="str">
         <v>12600</v>
       </c>
-      <c r="BN9" t="str">
+      <c r="BR9" t="str">
         <v>121.25</v>
       </c>
-      <c r="BQ9" t="str">
+      <c r="BU9" t="str">
         <v>5325</v>
       </c>
-      <c r="BR9" t="str">
+      <c r="BV9" t="str">
         <v>130</v>
       </c>
-      <c r="CK9" t="str">
+      <c r="CO9" t="str">
         <v>1265.45</v>
       </c>
-      <c r="CL9" t="str">
+      <c r="CP9" t="str">
         <v>213.09</v>
       </c>
     </row>
@@ -2627,16 +2735,16 @@
         <v>204.35</v>
       </c>
       <c r="BE10" t="str">
-        <v>2106</v>
+        <v>9500</v>
       </c>
       <c r="BF10" t="str">
-        <v>168.93</v>
+        <v>169</v>
       </c>
       <c r="BG10" t="str">
-        <v>2106</v>
+        <v>9500</v>
       </c>
       <c r="BH10" t="str">
-        <v>168.93</v>
+        <v>169_x000d_</v>
       </c>
       <c r="BI10" t="str">
         <v>1567.27</v>
@@ -2644,22 +2752,34 @@
       <c r="BJ10" t="str">
         <v>209.45</v>
       </c>
+      <c r="BK10" t="str">
+        <v>1567.27</v>
+      </c>
+      <c r="BL10" t="str">
+        <v>209.45</v>
+      </c>
       <c r="BM10" t="str">
+        <v>1567.27</v>
+      </c>
+      <c r="BN10" t="str">
+        <v>209.45_x000d_</v>
+      </c>
+      <c r="BQ10" t="str">
         <v>12800</v>
       </c>
-      <c r="BN10" t="str">
+      <c r="BR10" t="str">
         <v>121.25</v>
       </c>
-      <c r="BQ10" t="str">
+      <c r="BU10" t="str">
         <v>5500</v>
       </c>
-      <c r="BR10" t="str">
+      <c r="BV10" t="str">
         <v>129.5</v>
       </c>
-      <c r="CK10" t="str">
+      <c r="CO10" t="str">
         <v>1567.27</v>
       </c>
-      <c r="CL10" t="str">
+      <c r="CP10" t="str">
         <v>209.45</v>
       </c>
     </row>
@@ -2785,16 +2905,16 @@
         <v>204.78</v>
       </c>
       <c r="BE11" t="str">
-        <v>2223</v>
+        <v>10000</v>
       </c>
       <c r="BF11" t="str">
-        <v>169.8</v>
+        <v>168.5_x000d_</v>
       </c>
       <c r="BG11" t="str">
-        <v>2223</v>
+        <v>10000</v>
       </c>
       <c r="BH11" t="str">
-        <v>169.8</v>
+        <v>168.5_x000d_</v>
       </c>
       <c r="BI11" t="str">
         <v>1909.09</v>
@@ -2802,22 +2922,34 @@
       <c r="BJ11" t="str">
         <v>208.18</v>
       </c>
+      <c r="BK11" t="str">
+        <v>1909.09</v>
+      </c>
+      <c r="BL11" t="str">
+        <v>208.18</v>
+      </c>
       <c r="BM11" t="str">
+        <v>1909.09</v>
+      </c>
+      <c r="BN11" t="str">
+        <v>208.18_x000d_</v>
+      </c>
+      <c r="BQ11" t="str">
         <v>14300</v>
       </c>
-      <c r="BN11" t="str">
+      <c r="BR11" t="str">
         <v>121.5</v>
       </c>
-      <c r="BQ11" t="str">
+      <c r="BU11" t="str">
         <v>5700</v>
       </c>
-      <c r="BR11" t="str">
+      <c r="BV11" t="str">
         <v>129</v>
       </c>
-      <c r="CK11" t="str">
+      <c r="CO11" t="str">
         <v>1909.09</v>
       </c>
-      <c r="CL11" t="str">
+      <c r="CP11" t="str">
         <v>208.18</v>
       </c>
     </row>
@@ -2895,16 +3027,16 @@
         <v>210.67</v>
       </c>
       <c r="BE12" t="str">
-        <v>2340</v>
+        <v>10500</v>
       </c>
       <c r="BF12" t="str">
-        <v>171.4</v>
+        <v>168.5_x000d_</v>
       </c>
       <c r="BG12" t="str">
-        <v>2340</v>
+        <v>10500</v>
       </c>
       <c r="BH12" t="str">
-        <v>171.4</v>
+        <v>168.5_x000d_</v>
       </c>
       <c r="BI12" t="str">
         <v>2309.09</v>
@@ -2912,22 +3044,34 @@
       <c r="BJ12" t="str">
         <v>209.64</v>
       </c>
+      <c r="BK12" t="str">
+        <v>2309.09</v>
+      </c>
+      <c r="BL12" t="str">
+        <v>209.64</v>
+      </c>
       <c r="BM12" t="str">
+        <v>2309.09</v>
+      </c>
+      <c r="BN12" t="str">
+        <v>209.64_x000d_</v>
+      </c>
+      <c r="BQ12" t="str">
         <v>15100</v>
       </c>
-      <c r="BN12" t="str">
+      <c r="BR12" t="str">
         <v>122</v>
       </c>
-      <c r="BQ12" t="str">
+      <c r="BU12" t="str">
         <v>5900</v>
       </c>
-      <c r="BR12" t="str">
+      <c r="BV12" t="str">
         <v>128.5</v>
       </c>
-      <c r="CK12" t="str">
+      <c r="CO12" t="str">
         <v>2309.09</v>
       </c>
-      <c r="CL12" t="str">
+      <c r="CP12" t="str">
         <v>209.64</v>
       </c>
     </row>
@@ -3004,28 +3148,52 @@
       <c r="AF13" t="str">
         <v>209</v>
       </c>
+      <c r="BE13" t="str">
+        <v>11000</v>
+      </c>
+      <c r="BF13" t="str">
+        <v>169_x000d_</v>
+      </c>
+      <c r="BG13" t="str">
+        <v>11000</v>
+      </c>
+      <c r="BH13" t="str">
+        <v>169_x000d_</v>
+      </c>
       <c r="BI13" t="str">
         <v>2421.05</v>
       </c>
       <c r="BJ13" t="str">
         <v>210.36</v>
       </c>
+      <c r="BK13" t="str">
+        <v>2421.05</v>
+      </c>
+      <c r="BL13" t="str">
+        <v>210.36</v>
+      </c>
       <c r="BM13" t="str">
+        <v>2421.05</v>
+      </c>
+      <c r="BN13" t="str">
+        <v>210.36_x000d_</v>
+      </c>
+      <c r="BQ13" t="str">
         <v>15700</v>
       </c>
-      <c r="BN13" t="str">
+      <c r="BR13" t="str">
         <v>122.5</v>
       </c>
-      <c r="BQ13" t="str">
+      <c r="BU13" t="str">
         <v>6100</v>
       </c>
-      <c r="BR13" t="str">
+      <c r="BV13" t="str">
         <v>128</v>
       </c>
-      <c r="CK13" t="str">
+      <c r="CO13" t="str">
         <v>2421.05</v>
       </c>
-      <c r="CL13" t="str">
+      <c r="CP13" t="str">
         <v>210.36</v>
       </c>
     </row>
@@ -3066,16 +3234,34 @@
       <c r="AF14" t="str">
         <v>208.33</v>
       </c>
+      <c r="BE14" t="str">
+        <v>11500</v>
+      </c>
+      <c r="BF14" t="str">
+        <v>169.5_x000d_</v>
+      </c>
+      <c r="BG14" t="str">
+        <v>11500</v>
+      </c>
+      <c r="BH14" t="str">
+        <v>169.5_x000d_</v>
+      </c>
       <c r="BM14" t="str">
+        <v/>
+      </c>
+      <c r="BN14" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BQ14" t="str">
         <v>16200</v>
       </c>
-      <c r="BN14" t="str">
+      <c r="BR14" t="str">
         <v>123</v>
       </c>
-      <c r="BQ14" t="str">
+      <c r="BU14" t="str">
         <v>6300</v>
       </c>
-      <c r="BR14" t="str">
+      <c r="BV14" t="str">
         <v>127.5</v>
       </c>
     </row>
@@ -3116,16 +3302,34 @@
       <c r="AF15" t="str">
         <v>208</v>
       </c>
+      <c r="BE15" t="str">
+        <v>12000</v>
+      </c>
+      <c r="BF15" t="str">
+        <v>169.9</v>
+      </c>
+      <c r="BG15" t="str">
+        <v>12000</v>
+      </c>
+      <c r="BH15" t="str">
+        <v>169.9_x000d_</v>
+      </c>
       <c r="BM15" t="str">
+        <v/>
+      </c>
+      <c r="BN15" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BQ15" t="str">
         <v>16650</v>
       </c>
-      <c r="BN15" t="str">
+      <c r="BR15" t="str">
         <v>123.5</v>
       </c>
-      <c r="BQ15" t="str">
+      <c r="BU15" t="str">
         <v>6550</v>
       </c>
-      <c r="BR15" t="str">
+      <c r="BV15" t="str">
         <v>127</v>
       </c>
     </row>
@@ -3166,16 +3370,34 @@
       <c r="AF16" t="str">
         <v>208.67</v>
       </c>
+      <c r="BE16" t="str">
+        <v>12500</v>
+      </c>
+      <c r="BF16" t="str">
+        <v>170.5</v>
+      </c>
+      <c r="BG16" t="str">
+        <v>12500</v>
+      </c>
+      <c r="BH16" t="str">
+        <v>170.5_x000d_</v>
+      </c>
       <c r="BM16" t="str">
+        <v/>
+      </c>
+      <c r="BN16" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BQ16" t="str">
         <v>17000</v>
       </c>
-      <c r="BN16" t="str">
+      <c r="BR16" t="str">
         <v>124</v>
       </c>
-      <c r="BQ16" t="str">
+      <c r="BU16" t="str">
         <v>6800</v>
       </c>
-      <c r="BR16" t="str">
+      <c r="BV16" t="str">
         <v>126.5</v>
       </c>
     </row>
@@ -3216,10 +3438,28 @@
       <c r="AF17" t="str">
         <v>209.33</v>
       </c>
-      <c r="BQ17" t="str">
+      <c r="BE17" t="str">
+        <v/>
+      </c>
+      <c r="BF17" t="str">
+        <v/>
+      </c>
+      <c r="BG17" t="str">
+        <v/>
+      </c>
+      <c r="BH17" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM17" t="str">
+        <v/>
+      </c>
+      <c r="BN17" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BU17" t="str">
         <v>7100</v>
       </c>
-      <c r="BR17" t="str">
+      <c r="BV17" t="str">
         <v>126</v>
       </c>
     </row>
@@ -3260,10 +3500,28 @@
       <c r="AF18" t="str">
         <v>210.33</v>
       </c>
-      <c r="BQ18" t="str">
+      <c r="BE18" t="str">
+        <v/>
+      </c>
+      <c r="BF18" t="str">
+        <v/>
+      </c>
+      <c r="BG18" t="str">
+        <v/>
+      </c>
+      <c r="BH18" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM18" t="str">
+        <v/>
+      </c>
+      <c r="BN18" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BU18" t="str">
         <v>7500</v>
       </c>
-      <c r="BR18" t="str">
+      <c r="BV18" t="str">
         <v>125.5</v>
       </c>
     </row>
@@ -3292,10 +3550,28 @@
       <c r="AF19" t="str">
         <v>212</v>
       </c>
-      <c r="BQ19" t="str">
+      <c r="BE19" t="str">
+        <v/>
+      </c>
+      <c r="BF19" t="str">
+        <v/>
+      </c>
+      <c r="BG19" t="str">
+        <v/>
+      </c>
+      <c r="BH19" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM19" t="str">
+        <v/>
+      </c>
+      <c r="BN19" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BU19" t="str">
         <v>8100</v>
       </c>
-      <c r="BR19" t="str">
+      <c r="BV19" t="str">
         <v>125</v>
       </c>
     </row>
@@ -3324,104 +3600,1720 @@
       <c r="AF20" t="str">
         <v>213.67</v>
       </c>
-      <c r="BQ20" t="str">
+      <c r="BE20" t="str">
+        <v/>
+      </c>
+      <c r="BF20" t="str">
+        <v/>
+      </c>
+      <c r="BG20" t="str">
+        <v/>
+      </c>
+      <c r="BH20" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM20" t="str">
+        <v/>
+      </c>
+      <c r="BN20" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BU20" t="str">
         <v>8800</v>
       </c>
-      <c r="BR20" t="str">
+      <c r="BV20" t="str">
         <v>124.75</v>
       </c>
     </row>
     <row r="21">
-      <c r="BQ21" t="str">
+      <c r="BE21" t="str">
+        <v/>
+      </c>
+      <c r="BF21" t="str">
+        <v/>
+      </c>
+      <c r="BG21" t="str">
+        <v/>
+      </c>
+      <c r="BH21" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM21" t="str">
+        <v/>
+      </c>
+      <c r="BN21" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BU21" t="str">
         <v>8900</v>
       </c>
-      <c r="BR21" t="str">
+      <c r="BV21" t="str">
         <v>124.75</v>
       </c>
     </row>
     <row r="22">
-      <c r="BQ22" t="str">
+      <c r="BE22" t="str">
+        <v/>
+      </c>
+      <c r="BF22" t="str">
+        <v/>
+      </c>
+      <c r="BG22" t="str">
+        <v/>
+      </c>
+      <c r="BH22" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM22" t="str">
+        <v/>
+      </c>
+      <c r="BN22" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BU22" t="str">
         <v>9500</v>
       </c>
-      <c r="BR22" t="str">
+      <c r="BV22" t="str">
         <v>125</v>
       </c>
     </row>
     <row r="23">
-      <c r="BQ23" t="str">
+      <c r="BE23" t="str">
+        <v/>
+      </c>
+      <c r="BF23" t="str">
+        <v/>
+      </c>
+      <c r="BG23" t="str">
+        <v/>
+      </c>
+      <c r="BH23" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM23" t="str">
+        <v/>
+      </c>
+      <c r="BN23" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BU23" t="str">
         <v>10050</v>
       </c>
-      <c r="BR23" t="str">
+      <c r="BV23" t="str">
         <v>125.5</v>
       </c>
     </row>
     <row r="24">
-      <c r="BQ24" t="str">
+      <c r="BE24" t="str">
+        <v/>
+      </c>
+      <c r="BF24" t="str">
+        <v/>
+      </c>
+      <c r="BG24" t="str">
+        <v/>
+      </c>
+      <c r="BH24" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM24" t="str">
+        <v/>
+      </c>
+      <c r="BN24" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BU24" t="str">
         <v>10450</v>
       </c>
-      <c r="BR24" t="str">
+      <c r="BV24" t="str">
         <v>126</v>
       </c>
     </row>
     <row r="25">
-      <c r="BQ25" t="str">
+      <c r="BE25" t="str">
+        <v/>
+      </c>
+      <c r="BF25" t="str">
+        <v/>
+      </c>
+      <c r="BG25" t="str">
+        <v/>
+      </c>
+      <c r="BH25" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM25" t="str">
+        <v/>
+      </c>
+      <c r="BN25" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BU25" t="str">
         <v>10750</v>
       </c>
-      <c r="BR25" t="str">
+      <c r="BV25" t="str">
         <v>126.5</v>
       </c>
     </row>
     <row r="26">
-      <c r="BQ26" t="str">
+      <c r="BE26" t="str">
+        <v/>
+      </c>
+      <c r="BF26" t="str">
+        <v/>
+      </c>
+      <c r="BG26" t="str">
+        <v/>
+      </c>
+      <c r="BH26" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM26" t="str">
+        <v/>
+      </c>
+      <c r="BN26" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BU26" t="str">
         <v>11000</v>
       </c>
-      <c r="BR26" t="str">
+      <c r="BV26" t="str">
         <v>127</v>
       </c>
     </row>
     <row r="27">
-      <c r="BQ27" t="str">
+      <c r="BE27" t="str">
+        <v/>
+      </c>
+      <c r="BF27" t="str">
+        <v/>
+      </c>
+      <c r="BG27" t="str">
+        <v/>
+      </c>
+      <c r="BH27" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM27" t="str">
+        <v/>
+      </c>
+      <c r="BN27" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BU27" t="str">
         <v>11300</v>
       </c>
-      <c r="BR27" t="str">
+      <c r="BV27" t="str">
         <v>127.5</v>
       </c>
     </row>
     <row r="28">
-      <c r="BQ28" t="str">
+      <c r="BE28" t="str">
+        <v/>
+      </c>
+      <c r="BF28" t="str">
+        <v/>
+      </c>
+      <c r="BG28" t="str">
+        <v/>
+      </c>
+      <c r="BH28" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM28" t="str">
+        <v/>
+      </c>
+      <c r="BN28" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BU28" t="str">
         <v>11450</v>
       </c>
-      <c r="BR28" t="str">
+      <c r="BV28" t="str">
         <v>128</v>
       </c>
     </row>
     <row r="29">
-      <c r="BQ29" t="str">
+      <c r="BE29" t="str">
+        <v/>
+      </c>
+      <c r="BF29" t="str">
+        <v/>
+      </c>
+      <c r="BG29" t="str">
+        <v/>
+      </c>
+      <c r="BH29" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM29" t="str">
+        <v/>
+      </c>
+      <c r="BN29" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BU29" t="str">
         <v>11650</v>
       </c>
-      <c r="BR29" t="str">
+      <c r="BV29" t="str">
         <v>128.5</v>
       </c>
     </row>
     <row r="30">
-      <c r="BQ30" t="str">
+      <c r="BE30" t="str">
+        <v/>
+      </c>
+      <c r="BF30" t="str">
+        <v/>
+      </c>
+      <c r="BG30" t="str">
+        <v/>
+      </c>
+      <c r="BH30" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM30" t="str">
+        <v/>
+      </c>
+      <c r="BN30" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BU30" t="str">
         <v>11850</v>
       </c>
-      <c r="BR30" t="str">
+      <c r="BV30" t="str">
         <v>129</v>
       </c>
     </row>
     <row r="31">
-      <c r="BQ31" t="str">
+      <c r="BE31" t="str">
+        <v/>
+      </c>
+      <c r="BF31" t="str">
+        <v/>
+      </c>
+      <c r="BG31" t="str">
+        <v/>
+      </c>
+      <c r="BH31" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM31" t="str">
+        <v/>
+      </c>
+      <c r="BN31" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BU31" t="str">
         <v>11950</v>
       </c>
-      <c r="BR31" t="str">
+      <c r="BV31" t="str">
         <v>129.5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="BE32" t="str">
+        <v/>
+      </c>
+      <c r="BF32" t="str">
+        <v/>
+      </c>
+      <c r="BG32" t="str">
+        <v/>
+      </c>
+      <c r="BH32" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM32" t="str">
+        <v/>
+      </c>
+      <c r="BN32" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="BE33" t="str">
+        <v/>
+      </c>
+      <c r="BF33" t="str">
+        <v/>
+      </c>
+      <c r="BG33" t="str">
+        <v/>
+      </c>
+      <c r="BH33" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM33" t="str">
+        <v/>
+      </c>
+      <c r="BN33" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="BE34" t="str">
+        <v/>
+      </c>
+      <c r="BF34" t="str">
+        <v/>
+      </c>
+      <c r="BG34" t="str">
+        <v/>
+      </c>
+      <c r="BH34" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM34" t="str">
+        <v/>
+      </c>
+      <c r="BN34" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="BE35" t="str">
+        <v/>
+      </c>
+      <c r="BF35" t="str">
+        <v/>
+      </c>
+      <c r="BG35" t="str">
+        <v/>
+      </c>
+      <c r="BH35" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM35" t="str">
+        <v/>
+      </c>
+      <c r="BN35" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="BE36" t="str">
+        <v/>
+      </c>
+      <c r="BF36" t="str">
+        <v/>
+      </c>
+      <c r="BG36" t="str">
+        <v/>
+      </c>
+      <c r="BH36" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM36" t="str">
+        <v/>
+      </c>
+      <c r="BN36" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="BE37" t="str">
+        <v/>
+      </c>
+      <c r="BF37" t="str">
+        <v/>
+      </c>
+      <c r="BG37" t="str">
+        <v/>
+      </c>
+      <c r="BH37" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM37" t="str">
+        <v/>
+      </c>
+      <c r="BN37" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="BE38" t="str">
+        <v/>
+      </c>
+      <c r="BF38" t="str">
+        <v/>
+      </c>
+      <c r="BG38" t="str">
+        <v/>
+      </c>
+      <c r="BH38" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM38" t="str">
+        <v/>
+      </c>
+      <c r="BN38" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="BE39" t="str">
+        <v/>
+      </c>
+      <c r="BF39" t="str">
+        <v/>
+      </c>
+      <c r="BG39" t="str">
+        <v/>
+      </c>
+      <c r="BH39" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM39" t="str">
+        <v/>
+      </c>
+      <c r="BN39" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="BE40" t="str">
+        <v/>
+      </c>
+      <c r="BF40" t="str">
+        <v/>
+      </c>
+      <c r="BG40" t="str">
+        <v/>
+      </c>
+      <c r="BH40" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM40" t="str">
+        <v/>
+      </c>
+      <c r="BN40" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="BE41" t="str">
+        <v/>
+      </c>
+      <c r="BF41" t="str">
+        <v/>
+      </c>
+      <c r="BG41" t="str">
+        <v/>
+      </c>
+      <c r="BH41" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM41" t="str">
+        <v/>
+      </c>
+      <c r="BN41" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="BE42" t="str">
+        <v/>
+      </c>
+      <c r="BF42" t="str">
+        <v/>
+      </c>
+      <c r="BG42" t="str">
+        <v/>
+      </c>
+      <c r="BH42" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM42" t="str">
+        <v/>
+      </c>
+      <c r="BN42" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="BE43" t="str">
+        <v/>
+      </c>
+      <c r="BF43" t="str">
+        <v/>
+      </c>
+      <c r="BG43" t="str">
+        <v/>
+      </c>
+      <c r="BH43" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM43" t="str">
+        <v/>
+      </c>
+      <c r="BN43" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="BE44" t="str">
+        <v/>
+      </c>
+      <c r="BF44" t="str">
+        <v/>
+      </c>
+      <c r="BG44" t="str">
+        <v/>
+      </c>
+      <c r="BH44" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM44" t="str">
+        <v/>
+      </c>
+      <c r="BN44" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="BE45" t="str">
+        <v/>
+      </c>
+      <c r="BF45" t="str">
+        <v/>
+      </c>
+      <c r="BG45" t="str">
+        <v/>
+      </c>
+      <c r="BH45" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM45" t="str">
+        <v/>
+      </c>
+      <c r="BN45" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="BE46" t="str">
+        <v/>
+      </c>
+      <c r="BF46" t="str">
+        <v/>
+      </c>
+      <c r="BG46" t="str">
+        <v/>
+      </c>
+      <c r="BH46" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM46" t="str">
+        <v/>
+      </c>
+      <c r="BN46" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="BE47" t="str">
+        <v/>
+      </c>
+      <c r="BF47" t="str">
+        <v/>
+      </c>
+      <c r="BG47" t="str">
+        <v/>
+      </c>
+      <c r="BH47" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM47" t="str">
+        <v/>
+      </c>
+      <c r="BN47" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="BE48" t="str">
+        <v/>
+      </c>
+      <c r="BF48" t="str">
+        <v/>
+      </c>
+      <c r="BG48" t="str">
+        <v/>
+      </c>
+      <c r="BH48" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM48" t="str">
+        <v/>
+      </c>
+      <c r="BN48" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="BE49" t="str">
+        <v/>
+      </c>
+      <c r="BF49" t="str">
+        <v/>
+      </c>
+      <c r="BG49" t="str">
+        <v/>
+      </c>
+      <c r="BH49" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM49" t="str">
+        <v/>
+      </c>
+      <c r="BN49" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="BE50" t="str">
+        <v/>
+      </c>
+      <c r="BF50" t="str">
+        <v/>
+      </c>
+      <c r="BG50" t="str">
+        <v/>
+      </c>
+      <c r="BH50" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM50" t="str">
+        <v/>
+      </c>
+      <c r="BN50" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="BE51" t="str">
+        <v/>
+      </c>
+      <c r="BF51" t="str">
+        <v/>
+      </c>
+      <c r="BG51" t="str">
+        <v/>
+      </c>
+      <c r="BH51" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM51" t="str">
+        <v/>
+      </c>
+      <c r="BN51" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="BE52" t="str">
+        <v/>
+      </c>
+      <c r="BF52" t="str">
+        <v/>
+      </c>
+      <c r="BG52" t="str">
+        <v/>
+      </c>
+      <c r="BH52" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM52" t="str">
+        <v/>
+      </c>
+      <c r="BN52" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="BE53" t="str">
+        <v/>
+      </c>
+      <c r="BF53" t="str">
+        <v/>
+      </c>
+      <c r="BG53" t="str">
+        <v/>
+      </c>
+      <c r="BH53" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM53" t="str">
+        <v/>
+      </c>
+      <c r="BN53" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="BE54" t="str">
+        <v/>
+      </c>
+      <c r="BF54" t="str">
+        <v/>
+      </c>
+      <c r="BG54" t="str">
+        <v/>
+      </c>
+      <c r="BH54" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM54" t="str">
+        <v/>
+      </c>
+      <c r="BN54" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="BE55" t="str">
+        <v/>
+      </c>
+      <c r="BF55" t="str">
+        <v/>
+      </c>
+      <c r="BG55" t="str">
+        <v/>
+      </c>
+      <c r="BH55" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM55" t="str">
+        <v/>
+      </c>
+      <c r="BN55" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="BE56" t="str">
+        <v/>
+      </c>
+      <c r="BF56" t="str">
+        <v/>
+      </c>
+      <c r="BG56" t="str">
+        <v/>
+      </c>
+      <c r="BH56" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM56" t="str">
+        <v/>
+      </c>
+      <c r="BN56" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="BE57" t="str">
+        <v/>
+      </c>
+      <c r="BF57" t="str">
+        <v/>
+      </c>
+      <c r="BG57" t="str">
+        <v/>
+      </c>
+      <c r="BH57" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM57" t="str">
+        <v/>
+      </c>
+      <c r="BN57" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="BE58" t="str">
+        <v/>
+      </c>
+      <c r="BF58" t="str">
+        <v/>
+      </c>
+      <c r="BG58" t="str">
+        <v/>
+      </c>
+      <c r="BH58" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM58" t="str">
+        <v/>
+      </c>
+      <c r="BN58" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="BE59" t="str">
+        <v/>
+      </c>
+      <c r="BF59" t="str">
+        <v/>
+      </c>
+      <c r="BG59" t="str">
+        <v/>
+      </c>
+      <c r="BH59" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM59" t="str">
+        <v/>
+      </c>
+      <c r="BN59" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="BE60" t="str">
+        <v/>
+      </c>
+      <c r="BF60" t="str">
+        <v/>
+      </c>
+      <c r="BG60" t="str">
+        <v/>
+      </c>
+      <c r="BH60" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM60" t="str">
+        <v/>
+      </c>
+      <c r="BN60" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="BE61" t="str">
+        <v/>
+      </c>
+      <c r="BF61" t="str">
+        <v/>
+      </c>
+      <c r="BG61" t="str">
+        <v/>
+      </c>
+      <c r="BH61" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM61" t="str">
+        <v/>
+      </c>
+      <c r="BN61" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="BE62" t="str">
+        <v/>
+      </c>
+      <c r="BF62" t="str">
+        <v/>
+      </c>
+      <c r="BG62" t="str">
+        <v/>
+      </c>
+      <c r="BH62" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM62" t="str">
+        <v/>
+      </c>
+      <c r="BN62" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="BE63" t="str">
+        <v/>
+      </c>
+      <c r="BF63" t="str">
+        <v/>
+      </c>
+      <c r="BG63" t="str">
+        <v/>
+      </c>
+      <c r="BH63" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM63" t="str">
+        <v/>
+      </c>
+      <c r="BN63" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="BE64" t="str">
+        <v/>
+      </c>
+      <c r="BF64" t="str">
+        <v/>
+      </c>
+      <c r="BG64" t="str">
+        <v/>
+      </c>
+      <c r="BH64" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM64" t="str">
+        <v/>
+      </c>
+      <c r="BN64" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="BE65" t="str">
+        <v/>
+      </c>
+      <c r="BF65" t="str">
+        <v/>
+      </c>
+      <c r="BG65" t="str">
+        <v/>
+      </c>
+      <c r="BH65" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM65" t="str">
+        <v/>
+      </c>
+      <c r="BN65" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="BE66" t="str">
+        <v/>
+      </c>
+      <c r="BF66" t="str">
+        <v/>
+      </c>
+      <c r="BG66" t="str">
+        <v/>
+      </c>
+      <c r="BH66" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM66" t="str">
+        <v/>
+      </c>
+      <c r="BN66" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="BE67" t="str">
+        <v/>
+      </c>
+      <c r="BF67" t="str">
+        <v/>
+      </c>
+      <c r="BG67" t="str">
+        <v/>
+      </c>
+      <c r="BH67" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM67" t="str">
+        <v/>
+      </c>
+      <c r="BN67" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="BE68" t="str">
+        <v/>
+      </c>
+      <c r="BF68" t="str">
+        <v/>
+      </c>
+      <c r="BG68" t="str">
+        <v/>
+      </c>
+      <c r="BH68" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM68" t="str">
+        <v/>
+      </c>
+      <c r="BN68" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="BE69" t="str">
+        <v/>
+      </c>
+      <c r="BF69" t="str">
+        <v/>
+      </c>
+      <c r="BG69" t="str">
+        <v/>
+      </c>
+      <c r="BH69" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM69" t="str">
+        <v/>
+      </c>
+      <c r="BN69" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="BE70" t="str">
+        <v/>
+      </c>
+      <c r="BF70" t="str">
+        <v/>
+      </c>
+      <c r="BG70" t="str">
+        <v/>
+      </c>
+      <c r="BH70" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM70" t="str">
+        <v/>
+      </c>
+      <c r="BN70" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="BE71" t="str">
+        <v/>
+      </c>
+      <c r="BF71" t="str">
+        <v/>
+      </c>
+      <c r="BG71" t="str">
+        <v/>
+      </c>
+      <c r="BH71" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM71" t="str">
+        <v/>
+      </c>
+      <c r="BN71" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="BE72" t="str">
+        <v/>
+      </c>
+      <c r="BF72" t="str">
+        <v/>
+      </c>
+      <c r="BG72" t="str">
+        <v/>
+      </c>
+      <c r="BH72" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM72" t="str">
+        <v/>
+      </c>
+      <c r="BN72" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="BE73" t="str">
+        <v/>
+      </c>
+      <c r="BF73" t="str">
+        <v/>
+      </c>
+      <c r="BG73" t="str">
+        <v/>
+      </c>
+      <c r="BH73" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM73" t="str">
+        <v/>
+      </c>
+      <c r="BN73" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="BE74" t="str">
+        <v/>
+      </c>
+      <c r="BF74" t="str">
+        <v/>
+      </c>
+      <c r="BG74" t="str">
+        <v/>
+      </c>
+      <c r="BH74" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM74" t="str">
+        <v/>
+      </c>
+      <c r="BN74" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="BE75" t="str">
+        <v/>
+      </c>
+      <c r="BF75" t="str">
+        <v/>
+      </c>
+      <c r="BG75" t="str">
+        <v/>
+      </c>
+      <c r="BH75" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM75" t="str">
+        <v/>
+      </c>
+      <c r="BN75" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="BE76" t="str">
+        <v/>
+      </c>
+      <c r="BF76" t="str">
+        <v/>
+      </c>
+      <c r="BG76" t="str">
+        <v/>
+      </c>
+      <c r="BH76" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM76" t="str">
+        <v/>
+      </c>
+      <c r="BN76" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="BE77" t="str">
+        <v/>
+      </c>
+      <c r="BF77" t="str">
+        <v/>
+      </c>
+      <c r="BG77" t="str">
+        <v/>
+      </c>
+      <c r="BH77" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM77" t="str">
+        <v/>
+      </c>
+      <c r="BN77" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="BE78" t="str">
+        <v/>
+      </c>
+      <c r="BF78" t="str">
+        <v/>
+      </c>
+      <c r="BG78" t="str">
+        <v/>
+      </c>
+      <c r="BH78" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM78" t="str">
+        <v/>
+      </c>
+      <c r="BN78" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="BE79" t="str">
+        <v/>
+      </c>
+      <c r="BF79" t="str">
+        <v/>
+      </c>
+      <c r="BG79" t="str">
+        <v/>
+      </c>
+      <c r="BH79" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM79" t="str">
+        <v/>
+      </c>
+      <c r="BN79" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="BE80" t="str">
+        <v/>
+      </c>
+      <c r="BF80" t="str">
+        <v/>
+      </c>
+      <c r="BG80" t="str">
+        <v/>
+      </c>
+      <c r="BH80" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="BM80" t="str">
+        <v/>
+      </c>
+      <c r="BN80" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="BE81" t="str">
+        <v/>
+      </c>
+      <c r="BF81" t="str">
+        <v/>
+      </c>
+      <c r="BG81" t="str">
+        <v/>
+      </c>
+      <c r="BH81" t="str">
+        <v/>
+      </c>
+      <c r="BM81" t="str">
+        <v/>
+      </c>
+      <c r="BN81" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="BM82" t="str">
+        <v/>
+      </c>
+      <c r="BN82" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="BM83" t="str">
+        <v/>
+      </c>
+      <c r="BN83" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="BM84" t="str">
+        <v/>
+      </c>
+      <c r="BN84" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="BM85" t="str">
+        <v/>
+      </c>
+      <c r="BN85" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="BM86" t="str">
+        <v/>
+      </c>
+      <c r="BN86" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="BM87" t="str">
+        <v/>
+      </c>
+      <c r="BN87" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="BM88" t="str">
+        <v/>
+      </c>
+      <c r="BN88" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="BM89" t="str">
+        <v/>
+      </c>
+      <c r="BN89" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="BM90" t="str">
+        <v/>
+      </c>
+      <c r="BN90" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="BM91" t="str">
+        <v/>
+      </c>
+      <c r="BN91" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="BM92" t="str">
+        <v/>
+      </c>
+      <c r="BN92" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="BM93" t="str">
+        <v/>
+      </c>
+      <c r="BN93" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="BM94" t="str">
+        <v/>
+      </c>
+      <c r="BN94" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="BM95" t="str">
+        <v/>
+      </c>
+      <c r="BN95" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="BM96" t="str">
+        <v/>
+      </c>
+      <c r="BN96" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="BM97" t="str">
+        <v/>
+      </c>
+      <c r="BN97" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="BM98" t="str">
+        <v/>
+      </c>
+      <c r="BN98" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="BM99" t="str">
+        <v/>
+      </c>
+      <c r="BN99" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="BM100" t="str">
+        <v/>
+      </c>
+      <c r="BN100" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="BM101" t="str">
+        <v/>
+      </c>
+      <c r="BN101" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="BM102" t="str">
+        <v/>
+      </c>
+      <c r="BN102" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="BM103" t="str">
+        <v/>
+      </c>
+      <c r="BN103" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="BM104" t="str">
+        <v/>
+      </c>
+      <c r="BN104" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="BM105" t="str">
+        <v/>
+      </c>
+      <c r="BN105" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="BM106" t="str">
+        <v/>
+      </c>
+      <c r="BN106" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="BM107" t="str">
+        <v/>
+      </c>
+      <c r="BN107" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="BM108" t="str">
+        <v/>
+      </c>
+      <c r="BN108" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="BM109" t="str">
+        <v/>
+      </c>
+      <c r="BN109" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="BM110" t="str">
+        <v/>
+      </c>
+      <c r="BN110" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="BM111" t="str">
+        <v/>
+      </c>
+      <c r="BN111" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="BM112" t="str">
+        <v/>
+      </c>
+      <c r="BN112" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="BM113" t="str">
+        <v/>
+      </c>
+      <c r="BN113" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="BM114" t="str">
+        <v/>
+      </c>
+      <c r="BN114" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="BM115" t="str">
+        <v/>
+      </c>
+      <c r="BN115" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="BM116" t="str">
+        <v/>
+      </c>
+      <c r="BN116" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="BM117" t="str">
+        <v/>
+      </c>
+      <c r="BN117" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="BM118" t="str">
+        <v/>
+      </c>
+      <c r="BN118" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="BM119" t="str">
+        <v/>
+      </c>
+      <c r="BN119" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="BM120" t="str">
+        <v/>
+      </c>
+      <c r="BN120" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="BM121" t="str">
+        <v/>
+      </c>
+      <c r="BN121" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="BM122" t="str">
+        <v/>
+      </c>
+      <c r="BN122" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="BM123" t="str">
+        <v/>
+      </c>
+      <c r="BN123" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="BM124" t="str">
+        <v/>
+      </c>
+      <c r="BN124" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="BM125" t="str">
+        <v/>
+      </c>
+      <c r="BN125" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="BM126" t="str">
+        <v/>
+      </c>
+      <c r="BN126" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="BM127" t="str">
+        <v/>
+      </c>
+      <c r="BN127" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="BM128" t="str">
+        <v/>
+      </c>
+      <c r="BN128" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="BM129" t="str">
+        <v/>
+      </c>
+      <c r="BN129" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="BM130" t="str">
+        <v/>
+      </c>
+      <c r="BN130" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="BM131" t="str">
+        <v/>
+      </c>
+      <c r="BN131" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:CL31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:CP131"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/storage/app/Titik Ori Grafik.xlsx
+++ b/storage/app/Titik Ori Grafik.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CP131"/>
+  <dimension ref="A1:CR181"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -677,9 +677,15 @@
         <v>ASR Y</v>
       </c>
       <c r="CO1" t="str">
+        <v>TIT X</v>
+      </c>
+      <c r="CP1" t="str">
+        <v>TIT Y</v>
+      </c>
+      <c r="CQ1" t="str">
         <v>PNN X</v>
       </c>
-      <c r="CP1" t="str">
+      <c r="CR1" t="str">
         <v>PNN Y</v>
       </c>
     </row>
@@ -961,9 +967,15 @@
         <v>213.6</v>
       </c>
       <c r="CO2" t="str">
+        <v>6900</v>
+      </c>
+      <c r="CP2" t="str">
+        <v>127.5_x000d_</v>
+      </c>
+      <c r="CQ2" t="str">
         <v>163.64</v>
       </c>
-      <c r="CP2" t="str">
+      <c r="CR2" t="str">
         <v>275.27</v>
       </c>
     </row>
@@ -1245,9 +1257,15 @@
         <v>210.4</v>
       </c>
       <c r="CO3" t="str">
+        <v>7300</v>
+      </c>
+      <c r="CP3" t="str">
+        <v>127_x000d_</v>
+      </c>
+      <c r="CQ3" t="str">
         <v>218.18</v>
       </c>
-      <c r="CP3" t="str">
+      <c r="CR3" t="str">
         <v>266.55</v>
       </c>
     </row>
@@ -1517,9 +1535,15 @@
         <v>206.5</v>
       </c>
       <c r="CO4" t="str">
+        <v>7800</v>
+      </c>
+      <c r="CP4" t="str">
+        <v>126.5_x000d_</v>
+      </c>
+      <c r="CQ4" t="str">
         <v>358.18</v>
       </c>
-      <c r="CP4" t="str">
+      <c r="CR4" t="str">
         <v>254.36</v>
       </c>
     </row>
@@ -1747,9 +1771,15 @@
         <v>194_x000d_</v>
       </c>
       <c r="CO5" t="str">
+        <v>8300</v>
+      </c>
+      <c r="CP5" t="str">
+        <v>126_x000d_</v>
+      </c>
+      <c r="CQ5" t="str">
         <v>467.27</v>
       </c>
-      <c r="CP5" t="str">
+      <c r="CR5" t="str">
         <v>242.36</v>
       </c>
     </row>
@@ -1977,9 +2007,15 @@
         <v>197_x000d_</v>
       </c>
       <c r="CO6" t="str">
+        <v>8800</v>
+      </c>
+      <c r="CP6" t="str">
+        <v>125.5_x000d_</v>
+      </c>
+      <c r="CQ6" t="str">
         <v>614.55</v>
       </c>
-      <c r="CP6" t="str">
+      <c r="CR6" t="str">
         <v>232.36</v>
       </c>
     </row>
@@ -2207,9 +2243,15 @@
         <v>201</v>
       </c>
       <c r="CO7" t="str">
+        <v>9300</v>
+      </c>
+      <c r="CP7" t="str">
+        <v>125_x000d_</v>
+      </c>
+      <c r="CQ7" t="str">
         <v>796.36</v>
       </c>
-      <c r="CP7" t="str">
+      <c r="CR7" t="str">
         <v>224</v>
       </c>
     </row>
@@ -2401,9 +2443,15 @@
         <v>130.5</v>
       </c>
       <c r="CO8" t="str">
+        <v>9800</v>
+      </c>
+      <c r="CP8" t="str">
+        <v>124.5_x000d_</v>
+      </c>
+      <c r="CQ8" t="str">
         <v>1010.91</v>
       </c>
-      <c r="CP8" t="str">
+      <c r="CR8" t="str">
         <v>218</v>
       </c>
     </row>
@@ -2595,9 +2643,15 @@
         <v>130</v>
       </c>
       <c r="CO9" t="str">
+        <v>10600</v>
+      </c>
+      <c r="CP9" t="str">
+        <v>124_x000d_</v>
+      </c>
+      <c r="CQ9" t="str">
         <v>1265.45</v>
       </c>
-      <c r="CP9" t="str">
+      <c r="CR9" t="str">
         <v>213.09</v>
       </c>
     </row>
@@ -2777,9 +2831,15 @@
         <v>129.5</v>
       </c>
       <c r="CO10" t="str">
+        <v>11600</v>
+      </c>
+      <c r="CP10" t="str">
+        <v>124_x000d_</v>
+      </c>
+      <c r="CQ10" t="str">
         <v>1567.27</v>
       </c>
-      <c r="CP10" t="str">
+      <c r="CR10" t="str">
         <v>209.45</v>
       </c>
     </row>
@@ -2947,9 +3007,15 @@
         <v>129</v>
       </c>
       <c r="CO11" t="str">
+        <v>12300</v>
+      </c>
+      <c r="CP11" t="str">
+        <v>124.5_x000d_</v>
+      </c>
+      <c r="CQ11" t="str">
         <v>1909.09</v>
       </c>
-      <c r="CP11" t="str">
+      <c r="CR11" t="str">
         <v>208.18</v>
       </c>
     </row>
@@ -3069,9 +3135,15 @@
         <v>128.5</v>
       </c>
       <c r="CO12" t="str">
+        <v>12800</v>
+      </c>
+      <c r="CP12" t="str">
+        <v>125_x000d_</v>
+      </c>
+      <c r="CQ12" t="str">
         <v>2309.09</v>
       </c>
-      <c r="CP12" t="str">
+      <c r="CR12" t="str">
         <v>209.64</v>
       </c>
     </row>
@@ -3191,9 +3263,15 @@
         <v>128</v>
       </c>
       <c r="CO13" t="str">
+        <v>13300</v>
+      </c>
+      <c r="CP13" t="str">
+        <v>125.5_x000d_</v>
+      </c>
+      <c r="CQ13" t="str">
         <v>2421.05</v>
       </c>
-      <c r="CP13" t="str">
+      <c r="CR13" t="str">
         <v>210.36</v>
       </c>
     </row>
@@ -3264,6 +3342,12 @@
       <c r="BV14" t="str">
         <v>127.5</v>
       </c>
+      <c r="CO14" t="str">
+        <v>13600</v>
+      </c>
+      <c r="CP14" t="str">
+        <v>126_x000d_</v>
+      </c>
     </row>
     <row r="15">
       <c r="C15" t="str">
@@ -3332,6 +3416,12 @@
       <c r="BV15" t="str">
         <v>127</v>
       </c>
+      <c r="CO15" t="str">
+        <v>14000</v>
+      </c>
+      <c r="CP15" t="str">
+        <v>126.5_x000d_</v>
+      </c>
     </row>
     <row r="16">
       <c r="C16" t="str">
@@ -3400,6 +3490,12 @@
       <c r="BV16" t="str">
         <v>126.5</v>
       </c>
+      <c r="CO16" t="str">
+        <v>14300</v>
+      </c>
+      <c r="CP16" t="str">
+        <v>127_x000d_</v>
+      </c>
     </row>
     <row r="17">
       <c r="C17" t="str">
@@ -3462,6 +3558,12 @@
       <c r="BV17" t="str">
         <v>126</v>
       </c>
+      <c r="CO17" t="str">
+        <v>14700</v>
+      </c>
+      <c r="CP17" t="str">
+        <v>127.5_x000d_</v>
+      </c>
     </row>
     <row r="18">
       <c r="C18" t="str">
@@ -3524,6 +3626,12 @@
       <c r="BV18" t="str">
         <v>125.5</v>
       </c>
+      <c r="CO18" t="str">
+        <v>15000</v>
+      </c>
+      <c r="CP18" t="str">
+        <v>128_x000d_</v>
+      </c>
     </row>
     <row r="19">
       <c r="Y19" t="str">
@@ -3574,6 +3682,12 @@
       <c r="BV19" t="str">
         <v>125</v>
       </c>
+      <c r="CO19" t="str">
+        <v/>
+      </c>
+      <c r="CP19" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="20">
       <c r="Y20" t="str">
@@ -3624,6 +3738,12 @@
       <c r="BV20" t="str">
         <v>124.75</v>
       </c>
+      <c r="CO20" t="str">
+        <v/>
+      </c>
+      <c r="CP20" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="21">
       <c r="BE21" t="str">
@@ -3650,6 +3770,12 @@
       <c r="BV21" t="str">
         <v>124.75</v>
       </c>
+      <c r="CO21" t="str">
+        <v/>
+      </c>
+      <c r="CP21" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="22">
       <c r="BE22" t="str">
@@ -3676,6 +3802,12 @@
       <c r="BV22" t="str">
         <v>125</v>
       </c>
+      <c r="CO22" t="str">
+        <v/>
+      </c>
+      <c r="CP22" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="23">
       <c r="BE23" t="str">
@@ -3702,6 +3834,12 @@
       <c r="BV23" t="str">
         <v>125.5</v>
       </c>
+      <c r="CO23" t="str">
+        <v/>
+      </c>
+      <c r="CP23" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="24">
       <c r="BE24" t="str">
@@ -3728,6 +3866,12 @@
       <c r="BV24" t="str">
         <v>126</v>
       </c>
+      <c r="CO24" t="str">
+        <v/>
+      </c>
+      <c r="CP24" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="25">
       <c r="BE25" t="str">
@@ -3754,6 +3898,12 @@
       <c r="BV25" t="str">
         <v>126.5</v>
       </c>
+      <c r="CO25" t="str">
+        <v/>
+      </c>
+      <c r="CP25" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="26">
       <c r="BE26" t="str">
@@ -3780,6 +3930,12 @@
       <c r="BV26" t="str">
         <v>127</v>
       </c>
+      <c r="CO26" t="str">
+        <v/>
+      </c>
+      <c r="CP26" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="27">
       <c r="BE27" t="str">
@@ -3806,6 +3962,12 @@
       <c r="BV27" t="str">
         <v>127.5</v>
       </c>
+      <c r="CO27" t="str">
+        <v/>
+      </c>
+      <c r="CP27" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="28">
       <c r="BE28" t="str">
@@ -3832,6 +3994,12 @@
       <c r="BV28" t="str">
         <v>128</v>
       </c>
+      <c r="CO28" t="str">
+        <v/>
+      </c>
+      <c r="CP28" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="29">
       <c r="BE29" t="str">
@@ -3858,6 +4026,12 @@
       <c r="BV29" t="str">
         <v>128.5</v>
       </c>
+      <c r="CO29" t="str">
+        <v/>
+      </c>
+      <c r="CP29" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="30">
       <c r="BE30" t="str">
@@ -3884,6 +4058,12 @@
       <c r="BV30" t="str">
         <v>129</v>
       </c>
+      <c r="CO30" t="str">
+        <v/>
+      </c>
+      <c r="CP30" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="31">
       <c r="BE31" t="str">
@@ -3910,6 +4090,12 @@
       <c r="BV31" t="str">
         <v>129.5</v>
       </c>
+      <c r="CO31" t="str">
+        <v/>
+      </c>
+      <c r="CP31" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="32">
       <c r="BE32" t="str">
@@ -3930,6 +4116,12 @@
       <c r="BN32" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO32" t="str">
+        <v/>
+      </c>
+      <c r="CP32" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="33">
       <c r="BE33" t="str">
@@ -3950,6 +4142,12 @@
       <c r="BN33" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO33" t="str">
+        <v/>
+      </c>
+      <c r="CP33" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="34">
       <c r="BE34" t="str">
@@ -3970,6 +4168,12 @@
       <c r="BN34" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO34" t="str">
+        <v/>
+      </c>
+      <c r="CP34" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="35">
       <c r="BE35" t="str">
@@ -3990,6 +4194,12 @@
       <c r="BN35" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO35" t="str">
+        <v/>
+      </c>
+      <c r="CP35" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="36">
       <c r="BE36" t="str">
@@ -4010,6 +4220,12 @@
       <c r="BN36" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO36" t="str">
+        <v/>
+      </c>
+      <c r="CP36" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="37">
       <c r="BE37" t="str">
@@ -4030,6 +4246,12 @@
       <c r="BN37" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO37" t="str">
+        <v/>
+      </c>
+      <c r="CP37" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="38">
       <c r="BE38" t="str">
@@ -4050,6 +4272,12 @@
       <c r="BN38" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO38" t="str">
+        <v/>
+      </c>
+      <c r="CP38" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="39">
       <c r="BE39" t="str">
@@ -4070,6 +4298,12 @@
       <c r="BN39" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO39" t="str">
+        <v/>
+      </c>
+      <c r="CP39" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="40">
       <c r="BE40" t="str">
@@ -4090,6 +4324,12 @@
       <c r="BN40" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO40" t="str">
+        <v/>
+      </c>
+      <c r="CP40" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="41">
       <c r="BE41" t="str">
@@ -4110,6 +4350,12 @@
       <c r="BN41" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO41" t="str">
+        <v/>
+      </c>
+      <c r="CP41" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="42">
       <c r="BE42" t="str">
@@ -4130,6 +4376,12 @@
       <c r="BN42" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO42" t="str">
+        <v/>
+      </c>
+      <c r="CP42" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="43">
       <c r="BE43" t="str">
@@ -4150,6 +4402,12 @@
       <c r="BN43" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO43" t="str">
+        <v/>
+      </c>
+      <c r="CP43" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="44">
       <c r="BE44" t="str">
@@ -4170,6 +4428,12 @@
       <c r="BN44" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO44" t="str">
+        <v/>
+      </c>
+      <c r="CP44" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="45">
       <c r="BE45" t="str">
@@ -4190,6 +4454,12 @@
       <c r="BN45" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO45" t="str">
+        <v/>
+      </c>
+      <c r="CP45" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="46">
       <c r="BE46" t="str">
@@ -4210,6 +4480,12 @@
       <c r="BN46" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO46" t="str">
+        <v/>
+      </c>
+      <c r="CP46" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="47">
       <c r="BE47" t="str">
@@ -4230,6 +4506,12 @@
       <c r="BN47" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO47" t="str">
+        <v/>
+      </c>
+      <c r="CP47" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="48">
       <c r="BE48" t="str">
@@ -4250,6 +4532,12 @@
       <c r="BN48" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO48" t="str">
+        <v/>
+      </c>
+      <c r="CP48" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="49">
       <c r="BE49" t="str">
@@ -4270,6 +4558,12 @@
       <c r="BN49" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO49" t="str">
+        <v/>
+      </c>
+      <c r="CP49" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="50">
       <c r="BE50" t="str">
@@ -4290,6 +4584,12 @@
       <c r="BN50" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO50" t="str">
+        <v/>
+      </c>
+      <c r="CP50" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="51">
       <c r="BE51" t="str">
@@ -4310,6 +4610,12 @@
       <c r="BN51" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO51" t="str">
+        <v/>
+      </c>
+      <c r="CP51" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="52">
       <c r="BE52" t="str">
@@ -4330,6 +4636,12 @@
       <c r="BN52" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO52" t="str">
+        <v/>
+      </c>
+      <c r="CP52" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="53">
       <c r="BE53" t="str">
@@ -4350,6 +4662,12 @@
       <c r="BN53" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO53" t="str">
+        <v/>
+      </c>
+      <c r="CP53" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="54">
       <c r="BE54" t="str">
@@ -4370,6 +4688,12 @@
       <c r="BN54" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO54" t="str">
+        <v/>
+      </c>
+      <c r="CP54" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="55">
       <c r="BE55" t="str">
@@ -4390,6 +4714,12 @@
       <c r="BN55" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO55" t="str">
+        <v/>
+      </c>
+      <c r="CP55" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="56">
       <c r="BE56" t="str">
@@ -4410,6 +4740,12 @@
       <c r="BN56" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO56" t="str">
+        <v/>
+      </c>
+      <c r="CP56" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="57">
       <c r="BE57" t="str">
@@ -4430,6 +4766,12 @@
       <c r="BN57" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO57" t="str">
+        <v/>
+      </c>
+      <c r="CP57" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="58">
       <c r="BE58" t="str">
@@ -4450,6 +4792,12 @@
       <c r="BN58" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO58" t="str">
+        <v/>
+      </c>
+      <c r="CP58" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="59">
       <c r="BE59" t="str">
@@ -4470,6 +4818,12 @@
       <c r="BN59" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO59" t="str">
+        <v/>
+      </c>
+      <c r="CP59" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="60">
       <c r="BE60" t="str">
@@ -4490,6 +4844,12 @@
       <c r="BN60" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO60" t="str">
+        <v/>
+      </c>
+      <c r="CP60" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="61">
       <c r="BE61" t="str">
@@ -4510,6 +4870,12 @@
       <c r="BN61" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO61" t="str">
+        <v/>
+      </c>
+      <c r="CP61" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="62">
       <c r="BE62" t="str">
@@ -4530,6 +4896,12 @@
       <c r="BN62" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO62" t="str">
+        <v/>
+      </c>
+      <c r="CP62" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="63">
       <c r="BE63" t="str">
@@ -4550,6 +4922,12 @@
       <c r="BN63" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO63" t="str">
+        <v/>
+      </c>
+      <c r="CP63" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="64">
       <c r="BE64" t="str">
@@ -4570,6 +4948,12 @@
       <c r="BN64" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO64" t="str">
+        <v/>
+      </c>
+      <c r="CP64" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="65">
       <c r="BE65" t="str">
@@ -4590,6 +4974,12 @@
       <c r="BN65" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO65" t="str">
+        <v/>
+      </c>
+      <c r="CP65" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="66">
       <c r="BE66" t="str">
@@ -4610,6 +5000,12 @@
       <c r="BN66" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO66" t="str">
+        <v/>
+      </c>
+      <c r="CP66" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="67">
       <c r="BE67" t="str">
@@ -4630,6 +5026,12 @@
       <c r="BN67" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO67" t="str">
+        <v/>
+      </c>
+      <c r="CP67" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="68">
       <c r="BE68" t="str">
@@ -4650,6 +5052,12 @@
       <c r="BN68" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO68" t="str">
+        <v/>
+      </c>
+      <c r="CP68" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="69">
       <c r="BE69" t="str">
@@ -4670,6 +5078,12 @@
       <c r="BN69" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO69" t="str">
+        <v/>
+      </c>
+      <c r="CP69" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="70">
       <c r="BE70" t="str">
@@ -4690,6 +5104,12 @@
       <c r="BN70" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO70" t="str">
+        <v/>
+      </c>
+      <c r="CP70" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="71">
       <c r="BE71" t="str">
@@ -4710,6 +5130,12 @@
       <c r="BN71" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO71" t="str">
+        <v/>
+      </c>
+      <c r="CP71" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="72">
       <c r="BE72" t="str">
@@ -4730,6 +5156,12 @@
       <c r="BN72" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO72" t="str">
+        <v/>
+      </c>
+      <c r="CP72" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="73">
       <c r="BE73" t="str">
@@ -4750,6 +5182,12 @@
       <c r="BN73" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO73" t="str">
+        <v/>
+      </c>
+      <c r="CP73" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="74">
       <c r="BE74" t="str">
@@ -4770,6 +5208,12 @@
       <c r="BN74" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO74" t="str">
+        <v/>
+      </c>
+      <c r="CP74" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="75">
       <c r="BE75" t="str">
@@ -4790,6 +5234,12 @@
       <c r="BN75" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO75" t="str">
+        <v/>
+      </c>
+      <c r="CP75" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="76">
       <c r="BE76" t="str">
@@ -4810,6 +5260,12 @@
       <c r="BN76" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO76" t="str">
+        <v/>
+      </c>
+      <c r="CP76" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="77">
       <c r="BE77" t="str">
@@ -4830,6 +5286,12 @@
       <c r="BN77" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO77" t="str">
+        <v/>
+      </c>
+      <c r="CP77" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="78">
       <c r="BE78" t="str">
@@ -4850,6 +5312,12 @@
       <c r="BN78" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO78" t="str">
+        <v/>
+      </c>
+      <c r="CP78" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="79">
       <c r="BE79" t="str">
@@ -4870,6 +5338,12 @@
       <c r="BN79" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO79" t="str">
+        <v/>
+      </c>
+      <c r="CP79" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="80">
       <c r="BE80" t="str">
@@ -4890,6 +5364,12 @@
       <c r="BN80" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO80" t="str">
+        <v/>
+      </c>
+      <c r="CP80" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="81">
       <c r="BE81" t="str">
@@ -4910,6 +5390,12 @@
       <c r="BN81" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO81" t="str">
+        <v/>
+      </c>
+      <c r="CP81" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="82">
       <c r="BM82" t="str">
@@ -4918,6 +5404,12 @@
       <c r="BN82" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO82" t="str">
+        <v/>
+      </c>
+      <c r="CP82" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="83">
       <c r="BM83" t="str">
@@ -4926,6 +5418,12 @@
       <c r="BN83" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO83" t="str">
+        <v/>
+      </c>
+      <c r="CP83" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="84">
       <c r="BM84" t="str">
@@ -4934,6 +5432,12 @@
       <c r="BN84" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO84" t="str">
+        <v/>
+      </c>
+      <c r="CP84" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="85">
       <c r="BM85" t="str">
@@ -4942,6 +5446,12 @@
       <c r="BN85" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO85" t="str">
+        <v/>
+      </c>
+      <c r="CP85" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="86">
       <c r="BM86" t="str">
@@ -4950,6 +5460,12 @@
       <c r="BN86" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO86" t="str">
+        <v/>
+      </c>
+      <c r="CP86" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="87">
       <c r="BM87" t="str">
@@ -4958,6 +5474,12 @@
       <c r="BN87" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO87" t="str">
+        <v/>
+      </c>
+      <c r="CP87" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="88">
       <c r="BM88" t="str">
@@ -4966,6 +5488,12 @@
       <c r="BN88" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO88" t="str">
+        <v/>
+      </c>
+      <c r="CP88" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="89">
       <c r="BM89" t="str">
@@ -4974,6 +5502,12 @@
       <c r="BN89" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO89" t="str">
+        <v/>
+      </c>
+      <c r="CP89" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="90">
       <c r="BM90" t="str">
@@ -4982,6 +5516,12 @@
       <c r="BN90" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO90" t="str">
+        <v/>
+      </c>
+      <c r="CP90" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="91">
       <c r="BM91" t="str">
@@ -4990,6 +5530,12 @@
       <c r="BN91" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO91" t="str">
+        <v/>
+      </c>
+      <c r="CP91" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="92">
       <c r="BM92" t="str">
@@ -4998,6 +5544,12 @@
       <c r="BN92" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO92" t="str">
+        <v/>
+      </c>
+      <c r="CP92" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="93">
       <c r="BM93" t="str">
@@ -5006,6 +5558,12 @@
       <c r="BN93" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO93" t="str">
+        <v/>
+      </c>
+      <c r="CP93" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="94">
       <c r="BM94" t="str">
@@ -5014,6 +5572,12 @@
       <c r="BN94" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO94" t="str">
+        <v/>
+      </c>
+      <c r="CP94" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="95">
       <c r="BM95" t="str">
@@ -5022,6 +5586,12 @@
       <c r="BN95" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO95" t="str">
+        <v/>
+      </c>
+      <c r="CP95" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="96">
       <c r="BM96" t="str">
@@ -5030,6 +5600,12 @@
       <c r="BN96" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO96" t="str">
+        <v/>
+      </c>
+      <c r="CP96" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="97">
       <c r="BM97" t="str">
@@ -5038,6 +5614,12 @@
       <c r="BN97" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO97" t="str">
+        <v/>
+      </c>
+      <c r="CP97" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="98">
       <c r="BM98" t="str">
@@ -5046,6 +5628,12 @@
       <c r="BN98" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO98" t="str">
+        <v/>
+      </c>
+      <c r="CP98" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="99">
       <c r="BM99" t="str">
@@ -5054,6 +5642,12 @@
       <c r="BN99" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO99" t="str">
+        <v/>
+      </c>
+      <c r="CP99" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="100">
       <c r="BM100" t="str">
@@ -5062,6 +5656,12 @@
       <c r="BN100" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO100" t="str">
+        <v/>
+      </c>
+      <c r="CP100" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="101">
       <c r="BM101" t="str">
@@ -5070,6 +5670,12 @@
       <c r="BN101" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO101" t="str">
+        <v/>
+      </c>
+      <c r="CP101" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="102">
       <c r="BM102" t="str">
@@ -5078,6 +5684,12 @@
       <c r="BN102" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO102" t="str">
+        <v/>
+      </c>
+      <c r="CP102" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="103">
       <c r="BM103" t="str">
@@ -5086,6 +5698,12 @@
       <c r="BN103" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO103" t="str">
+        <v/>
+      </c>
+      <c r="CP103" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="104">
       <c r="BM104" t="str">
@@ -5094,6 +5712,12 @@
       <c r="BN104" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO104" t="str">
+        <v/>
+      </c>
+      <c r="CP104" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="105">
       <c r="BM105" t="str">
@@ -5102,6 +5726,12 @@
       <c r="BN105" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO105" t="str">
+        <v/>
+      </c>
+      <c r="CP105" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="106">
       <c r="BM106" t="str">
@@ -5110,6 +5740,12 @@
       <c r="BN106" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO106" t="str">
+        <v/>
+      </c>
+      <c r="CP106" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="107">
       <c r="BM107" t="str">
@@ -5118,6 +5754,12 @@
       <c r="BN107" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO107" t="str">
+        <v/>
+      </c>
+      <c r="CP107" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="108">
       <c r="BM108" t="str">
@@ -5126,6 +5768,12 @@
       <c r="BN108" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO108" t="str">
+        <v/>
+      </c>
+      <c r="CP108" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="109">
       <c r="BM109" t="str">
@@ -5134,6 +5782,12 @@
       <c r="BN109" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO109" t="str">
+        <v/>
+      </c>
+      <c r="CP109" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="110">
       <c r="BM110" t="str">
@@ -5142,6 +5796,12 @@
       <c r="BN110" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO110" t="str">
+        <v/>
+      </c>
+      <c r="CP110" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="111">
       <c r="BM111" t="str">
@@ -5150,6 +5810,12 @@
       <c r="BN111" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO111" t="str">
+        <v/>
+      </c>
+      <c r="CP111" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="112">
       <c r="BM112" t="str">
@@ -5158,6 +5824,12 @@
       <c r="BN112" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO112" t="str">
+        <v/>
+      </c>
+      <c r="CP112" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="113">
       <c r="BM113" t="str">
@@ -5166,6 +5838,12 @@
       <c r="BN113" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO113" t="str">
+        <v/>
+      </c>
+      <c r="CP113" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="114">
       <c r="BM114" t="str">
@@ -5174,6 +5852,12 @@
       <c r="BN114" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO114" t="str">
+        <v/>
+      </c>
+      <c r="CP114" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="115">
       <c r="BM115" t="str">
@@ -5182,6 +5866,12 @@
       <c r="BN115" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO115" t="str">
+        <v/>
+      </c>
+      <c r="CP115" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="116">
       <c r="BM116" t="str">
@@ -5190,6 +5880,12 @@
       <c r="BN116" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO116" t="str">
+        <v/>
+      </c>
+      <c r="CP116" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="117">
       <c r="BM117" t="str">
@@ -5198,6 +5894,12 @@
       <c r="BN117" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO117" t="str">
+        <v/>
+      </c>
+      <c r="CP117" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="118">
       <c r="BM118" t="str">
@@ -5206,6 +5908,12 @@
       <c r="BN118" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO118" t="str">
+        <v/>
+      </c>
+      <c r="CP118" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="119">
       <c r="BM119" t="str">
@@ -5214,6 +5922,12 @@
       <c r="BN119" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO119" t="str">
+        <v/>
+      </c>
+      <c r="CP119" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="120">
       <c r="BM120" t="str">
@@ -5222,6 +5936,12 @@
       <c r="BN120" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO120" t="str">
+        <v/>
+      </c>
+      <c r="CP120" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="121">
       <c r="BM121" t="str">
@@ -5230,6 +5950,12 @@
       <c r="BN121" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO121" t="str">
+        <v/>
+      </c>
+      <c r="CP121" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="122">
       <c r="BM122" t="str">
@@ -5238,6 +5964,12 @@
       <c r="BN122" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO122" t="str">
+        <v/>
+      </c>
+      <c r="CP122" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="123">
       <c r="BM123" t="str">
@@ -5246,6 +5978,12 @@
       <c r="BN123" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO123" t="str">
+        <v/>
+      </c>
+      <c r="CP123" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="124">
       <c r="BM124" t="str">
@@ -5254,6 +5992,12 @@
       <c r="BN124" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO124" t="str">
+        <v/>
+      </c>
+      <c r="CP124" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="125">
       <c r="BM125" t="str">
@@ -5262,6 +6006,12 @@
       <c r="BN125" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO125" t="str">
+        <v/>
+      </c>
+      <c r="CP125" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="126">
       <c r="BM126" t="str">
@@ -5270,6 +6020,12 @@
       <c r="BN126" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO126" t="str">
+        <v/>
+      </c>
+      <c r="CP126" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="127">
       <c r="BM127" t="str">
@@ -5278,6 +6034,12 @@
       <c r="BN127" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO127" t="str">
+        <v/>
+      </c>
+      <c r="CP127" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="128">
       <c r="BM128" t="str">
@@ -5286,6 +6048,12 @@
       <c r="BN128" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO128" t="str">
+        <v/>
+      </c>
+      <c r="CP128" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="129">
       <c r="BM129" t="str">
@@ -5294,6 +6062,12 @@
       <c r="BN129" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO129" t="str">
+        <v/>
+      </c>
+      <c r="CP129" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="130">
       <c r="BM130" t="str">
@@ -5302,6 +6076,12 @@
       <c r="BN130" t="str">
         <v>_x000d_</v>
       </c>
+      <c r="CO130" t="str">
+        <v/>
+      </c>
+      <c r="CP130" t="str">
+        <v>_x000d_</v>
+      </c>
     </row>
     <row r="131">
       <c r="BM131" t="str">
@@ -5310,10 +6090,416 @@
       <c r="BN131" t="str">
         <v/>
       </c>
+      <c r="CO131" t="str">
+        <v/>
+      </c>
+      <c r="CP131" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="CO132" t="str">
+        <v/>
+      </c>
+      <c r="CP132" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="CO133" t="str">
+        <v/>
+      </c>
+      <c r="CP133" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="CO134" t="str">
+        <v/>
+      </c>
+      <c r="CP134" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="CO135" t="str">
+        <v/>
+      </c>
+      <c r="CP135" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="CO136" t="str">
+        <v/>
+      </c>
+      <c r="CP136" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="CO137" t="str">
+        <v/>
+      </c>
+      <c r="CP137" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="CO138" t="str">
+        <v/>
+      </c>
+      <c r="CP138" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="CO139" t="str">
+        <v/>
+      </c>
+      <c r="CP139" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="CO140" t="str">
+        <v/>
+      </c>
+      <c r="CP140" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="CO141" t="str">
+        <v/>
+      </c>
+      <c r="CP141" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="CO142" t="str">
+        <v/>
+      </c>
+      <c r="CP142" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="CO143" t="str">
+        <v/>
+      </c>
+      <c r="CP143" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="CO144" t="str">
+        <v/>
+      </c>
+      <c r="CP144" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="CO145" t="str">
+        <v/>
+      </c>
+      <c r="CP145" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="CO146" t="str">
+        <v/>
+      </c>
+      <c r="CP146" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="CO147" t="str">
+        <v/>
+      </c>
+      <c r="CP147" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="CO148" t="str">
+        <v/>
+      </c>
+      <c r="CP148" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="CO149" t="str">
+        <v/>
+      </c>
+      <c r="CP149" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="CO150" t="str">
+        <v/>
+      </c>
+      <c r="CP150" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="CO151" t="str">
+        <v/>
+      </c>
+      <c r="CP151" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="CO152" t="str">
+        <v/>
+      </c>
+      <c r="CP152" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="CO153" t="str">
+        <v/>
+      </c>
+      <c r="CP153" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="CO154" t="str">
+        <v/>
+      </c>
+      <c r="CP154" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="CO155" t="str">
+        <v/>
+      </c>
+      <c r="CP155" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="CO156" t="str">
+        <v/>
+      </c>
+      <c r="CP156" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="CO157" t="str">
+        <v/>
+      </c>
+      <c r="CP157" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="CO158" t="str">
+        <v/>
+      </c>
+      <c r="CP158" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="CO159" t="str">
+        <v/>
+      </c>
+      <c r="CP159" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="CO160" t="str">
+        <v/>
+      </c>
+      <c r="CP160" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="CO161" t="str">
+        <v/>
+      </c>
+      <c r="CP161" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="CO162" t="str">
+        <v/>
+      </c>
+      <c r="CP162" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="CO163" t="str">
+        <v/>
+      </c>
+      <c r="CP163" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="CO164" t="str">
+        <v/>
+      </c>
+      <c r="CP164" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="CO165" t="str">
+        <v/>
+      </c>
+      <c r="CP165" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="CO166" t="str">
+        <v/>
+      </c>
+      <c r="CP166" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="CO167" t="str">
+        <v/>
+      </c>
+      <c r="CP167" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="CO168" t="str">
+        <v/>
+      </c>
+      <c r="CP168" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="CO169" t="str">
+        <v/>
+      </c>
+      <c r="CP169" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="CO170" t="str">
+        <v/>
+      </c>
+      <c r="CP170" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="CO171" t="str">
+        <v/>
+      </c>
+      <c r="CP171" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="CO172" t="str">
+        <v/>
+      </c>
+      <c r="CP172" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="CO173" t="str">
+        <v/>
+      </c>
+      <c r="CP173" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="CO174" t="str">
+        <v/>
+      </c>
+      <c r="CP174" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="CO175" t="str">
+        <v/>
+      </c>
+      <c r="CP175" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="CO176" t="str">
+        <v/>
+      </c>
+      <c r="CP176" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="CO177" t="str">
+        <v/>
+      </c>
+      <c r="CP177" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="CO178" t="str">
+        <v/>
+      </c>
+      <c r="CP178" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="CO179" t="str">
+        <v/>
+      </c>
+      <c r="CP179" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="CO180" t="str">
+        <v/>
+      </c>
+      <c r="CP180" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="CO181" t="str">
+        <v/>
+      </c>
+      <c r="CP181" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:CP131"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:CR181"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/storage/app/Titik Ori Grafik.xlsx
+++ b/storage/app/Titik Ori Grafik.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CR181"/>
+  <dimension ref="A1:CT231"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -629,63 +629,69 @@
         <v>HSJ Y</v>
       </c>
       <c r="BY1" t="str">
+        <v>HSG X</v>
+      </c>
+      <c r="BZ1" t="str">
+        <v>HSG Y</v>
+      </c>
+      <c r="CA1" t="str">
         <v>PSM X</v>
       </c>
-      <c r="BZ1" t="str">
+      <c r="CB1" t="str">
         <v>PSM Y</v>
       </c>
-      <c r="CA1" t="str">
+      <c r="CC1" t="str">
         <v>RAT X</v>
       </c>
-      <c r="CB1" t="str">
+      <c r="CD1" t="str">
         <v>RAT Y</v>
       </c>
-      <c r="CC1" t="str">
+      <c r="CE1" t="str">
         <v>RUM X</v>
       </c>
-      <c r="CD1" t="str">
+      <c r="CF1" t="str">
         <v>RUM Y</v>
       </c>
-      <c r="CE1" t="str">
+      <c r="CG1" t="str">
         <v>OPA X</v>
       </c>
-      <c r="CF1" t="str">
+      <c r="CH1" t="str">
         <v>OPA Y</v>
       </c>
-      <c r="CG1" t="str">
+      <c r="CI1" t="str">
         <v>OSA X</v>
       </c>
-      <c r="CH1" t="str">
+      <c r="CJ1" t="str">
         <v>OSA Y</v>
       </c>
-      <c r="CI1" t="str">
+      <c r="CK1" t="str">
         <v>ASN X</v>
       </c>
-      <c r="CJ1" t="str">
+      <c r="CL1" t="str">
         <v>ASN Y</v>
       </c>
-      <c r="CK1" t="str">
+      <c r="CM1" t="str">
         <v>ASG X</v>
       </c>
-      <c r="CL1" t="str">
+      <c r="CN1" t="str">
         <v>ASG Y</v>
       </c>
-      <c r="CM1" t="str">
+      <c r="CO1" t="str">
         <v>ASR X</v>
       </c>
-      <c r="CN1" t="str">
+      <c r="CP1" t="str">
         <v>ASR Y</v>
       </c>
-      <c r="CO1" t="str">
+      <c r="CQ1" t="str">
         <v>TIT X</v>
       </c>
-      <c r="CP1" t="str">
+      <c r="CR1" t="str">
         <v>TIT Y</v>
       </c>
-      <c r="CQ1" t="str">
+      <c r="CS1" t="str">
         <v>PNN X</v>
       </c>
-      <c r="CR1" t="str">
+      <c r="CT1" t="str">
         <v>PNN Y</v>
       </c>
     </row>
@@ -919,16 +925,16 @@
         <v>135.3</v>
       </c>
       <c r="BY2" t="str">
+        <v>2442</v>
+      </c>
+      <c r="BZ2" t="str">
+        <v>135.3_x000d_</v>
+      </c>
+      <c r="CA2" t="str">
         <v>739</v>
       </c>
-      <c r="BZ2" t="str">
+      <c r="CB2" t="str">
         <v>209.3</v>
-      </c>
-      <c r="CA2" t="str">
-        <v>638</v>
-      </c>
-      <c r="CB2" t="str">
-        <v>215.7</v>
       </c>
       <c r="CC2" t="str">
         <v>638</v>
@@ -937,10 +943,10 @@
         <v>215.7</v>
       </c>
       <c r="CE2" t="str">
-        <v>827</v>
+        <v>638</v>
       </c>
       <c r="CF2" t="str">
-        <v>204_x000d_</v>
+        <v>215.7</v>
       </c>
       <c r="CG2" t="str">
         <v>827</v>
@@ -949,10 +955,10 @@
         <v>204_x000d_</v>
       </c>
       <c r="CI2" t="str">
-        <v>2220</v>
+        <v>827</v>
       </c>
       <c r="CJ2" t="str">
-        <v>213.6</v>
+        <v>204_x000d_</v>
       </c>
       <c r="CK2" t="str">
         <v>2220</v>
@@ -967,15 +973,21 @@
         <v>213.6</v>
       </c>
       <c r="CO2" t="str">
+        <v>2220</v>
+      </c>
+      <c r="CP2" t="str">
+        <v>213.6</v>
+      </c>
+      <c r="CQ2" t="str">
         <v>6900</v>
       </c>
-      <c r="CP2" t="str">
+      <c r="CR2" t="str">
         <v>127.5_x000d_</v>
       </c>
-      <c r="CQ2" t="str">
+      <c r="CS2" t="str">
         <v>163.64</v>
       </c>
-      <c r="CR2" t="str">
+      <c r="CT2" t="str">
         <v>275.27</v>
       </c>
     </row>
@@ -1209,16 +1221,16 @@
         <v>129.5</v>
       </c>
       <c r="BY3" t="str">
+        <v>4877</v>
+      </c>
+      <c r="BZ3" t="str">
+        <v>129.5_x000d_</v>
+      </c>
+      <c r="CA3" t="str">
         <v>821</v>
       </c>
-      <c r="BZ3" t="str">
+      <c r="CB3" t="str">
         <v>214.3</v>
-      </c>
-      <c r="CA3" t="str">
-        <v>1270</v>
-      </c>
-      <c r="CB3" t="str">
-        <v>202.2</v>
       </c>
       <c r="CC3" t="str">
         <v>1270</v>
@@ -1227,10 +1239,10 @@
         <v>202.2</v>
       </c>
       <c r="CE3" t="str">
-        <v>1655</v>
+        <v>1270</v>
       </c>
       <c r="CF3" t="str">
-        <v>197_x000d_</v>
+        <v>202.2</v>
       </c>
       <c r="CG3" t="str">
         <v>1655</v>
@@ -1239,10 +1251,10 @@
         <v>197_x000d_</v>
       </c>
       <c r="CI3" t="str">
-        <v>3330</v>
+        <v>1655</v>
       </c>
       <c r="CJ3" t="str">
-        <v>210.4</v>
+        <v>197_x000d_</v>
       </c>
       <c r="CK3" t="str">
         <v>3330</v>
@@ -1257,15 +1269,21 @@
         <v>210.4</v>
       </c>
       <c r="CO3" t="str">
+        <v>3330</v>
+      </c>
+      <c r="CP3" t="str">
+        <v>210.4</v>
+      </c>
+      <c r="CQ3" t="str">
         <v>7300</v>
       </c>
-      <c r="CP3" t="str">
+      <c r="CR3" t="str">
         <v>127_x000d_</v>
       </c>
-      <c r="CQ3" t="str">
+      <c r="CS3" t="str">
         <v>218.18</v>
       </c>
-      <c r="CR3" t="str">
+      <c r="CT3" t="str">
         <v>266.55</v>
       </c>
     </row>
@@ -1492,11 +1510,11 @@
       <c r="BX4" t="str">
         <v>128.4</v>
       </c>
-      <c r="CA4" t="str">
-        <v>1920</v>
-      </c>
-      <c r="CB4" t="str">
-        <v>198.6</v>
+      <c r="BY4" t="str">
+        <v>7329</v>
+      </c>
+      <c r="BZ4" t="str">
+        <v>128.4_x000d_</v>
       </c>
       <c r="CC4" t="str">
         <v>1920</v>
@@ -1505,10 +1523,10 @@
         <v>198.6</v>
       </c>
       <c r="CE4" t="str">
-        <v>2482</v>
+        <v>1920</v>
       </c>
       <c r="CF4" t="str">
-        <v>192_x000d_</v>
+        <v>198.6</v>
       </c>
       <c r="CG4" t="str">
         <v>2482</v>
@@ -1517,10 +1535,10 @@
         <v>192_x000d_</v>
       </c>
       <c r="CI4" t="str">
-        <v>4440</v>
+        <v>2482</v>
       </c>
       <c r="CJ4" t="str">
-        <v>206.5</v>
+        <v>192_x000d_</v>
       </c>
       <c r="CK4" t="str">
         <v>4440</v>
@@ -1535,15 +1553,21 @@
         <v>206.5</v>
       </c>
       <c r="CO4" t="str">
+        <v>4440</v>
+      </c>
+      <c r="CP4" t="str">
+        <v>206.5</v>
+      </c>
+      <c r="CQ4" t="str">
         <v>7800</v>
       </c>
-      <c r="CP4" t="str">
+      <c r="CR4" t="str">
         <v>126.5_x000d_</v>
       </c>
-      <c r="CQ4" t="str">
+      <c r="CS4" t="str">
         <v>358.18</v>
       </c>
-      <c r="CR4" t="str">
+      <c r="CT4" t="str">
         <v>254.36</v>
       </c>
     </row>
@@ -1746,11 +1770,11 @@
       <c r="BX5" t="str">
         <v>131.6</v>
       </c>
-      <c r="CA5" t="str">
-        <v>2300</v>
-      </c>
-      <c r="CB5" t="str">
-        <v>199.8</v>
+      <c r="BY5" t="str">
+        <v>9759</v>
+      </c>
+      <c r="BZ5" t="str">
+        <v>131.6_x000d_</v>
       </c>
       <c r="CC5" t="str">
         <v>2300</v>
@@ -1759,10 +1783,10 @@
         <v>199.8</v>
       </c>
       <c r="CE5" t="str">
-        <v>2979</v>
+        <v>2300</v>
       </c>
       <c r="CF5" t="str">
-        <v>194_x000d_</v>
+        <v>199.8</v>
       </c>
       <c r="CG5" t="str">
         <v>2979</v>
@@ -1770,16 +1794,22 @@
       <c r="CH5" t="str">
         <v>194_x000d_</v>
       </c>
-      <c r="CO5" t="str">
+      <c r="CI5" t="str">
+        <v>2979</v>
+      </c>
+      <c r="CJ5" t="str">
+        <v>194_x000d_</v>
+      </c>
+      <c r="CQ5" t="str">
         <v>8300</v>
       </c>
-      <c r="CP5" t="str">
+      <c r="CR5" t="str">
         <v>126_x000d_</v>
       </c>
-      <c r="CQ5" t="str">
+      <c r="CS5" t="str">
         <v>467.27</v>
       </c>
-      <c r="CR5" t="str">
+      <c r="CT5" t="str">
         <v>242.36</v>
       </c>
     </row>
@@ -1982,11 +2012,11 @@
       <c r="BX6" t="str">
         <v>131.3</v>
       </c>
-      <c r="CA6" t="str">
-        <v>2574</v>
-      </c>
-      <c r="CB6" t="str">
-        <v>200.3</v>
+      <c r="BY6" t="str">
+        <v>9775</v>
+      </c>
+      <c r="BZ6" t="str">
+        <v>131.3_x000d_</v>
       </c>
       <c r="CC6" t="str">
         <v>2574</v>
@@ -1995,10 +2025,10 @@
         <v>200.3</v>
       </c>
       <c r="CE6" t="str">
-        <v>3310</v>
+        <v>2574</v>
       </c>
       <c r="CF6" t="str">
-        <v>197_x000d_</v>
+        <v>200.3</v>
       </c>
       <c r="CG6" t="str">
         <v>3310</v>
@@ -2006,16 +2036,22 @@
       <c r="CH6" t="str">
         <v>197_x000d_</v>
       </c>
-      <c r="CO6" t="str">
+      <c r="CI6" t="str">
+        <v>3310</v>
+      </c>
+      <c r="CJ6" t="str">
+        <v>197_x000d_</v>
+      </c>
+      <c r="CQ6" t="str">
         <v>8800</v>
       </c>
-      <c r="CP6" t="str">
+      <c r="CR6" t="str">
         <v>125.5_x000d_</v>
       </c>
-      <c r="CQ6" t="str">
+      <c r="CS6" t="str">
         <v>614.55</v>
       </c>
-      <c r="CR6" t="str">
+      <c r="CT6" t="str">
         <v>232.36</v>
       </c>
     </row>
@@ -2218,11 +2254,11 @@
       <c r="BX7" t="str">
         <v>133.5</v>
       </c>
-      <c r="CA7" t="str">
-        <v>2840</v>
-      </c>
-      <c r="CB7" t="str">
-        <v>206.2</v>
+      <c r="BY7" t="str">
+        <v>10740</v>
+      </c>
+      <c r="BZ7" t="str">
+        <v>133.5_x000d_</v>
       </c>
       <c r="CC7" t="str">
         <v>2840</v>
@@ -2231,10 +2267,10 @@
         <v>206.2</v>
       </c>
       <c r="CE7" t="str">
-        <v>3641</v>
+        <v>2840</v>
       </c>
       <c r="CF7" t="str">
-        <v>201</v>
+        <v>206.2</v>
       </c>
       <c r="CG7" t="str">
         <v>3641</v>
@@ -2242,16 +2278,22 @@
       <c r="CH7" t="str">
         <v>201</v>
       </c>
-      <c r="CO7" t="str">
+      <c r="CI7" t="str">
+        <v>3641</v>
+      </c>
+      <c r="CJ7" t="str">
+        <v>201</v>
+      </c>
+      <c r="CQ7" t="str">
         <v>9300</v>
       </c>
-      <c r="CP7" t="str">
+      <c r="CR7" t="str">
         <v>125_x000d_</v>
       </c>
-      <c r="CQ7" t="str">
+      <c r="CS7" t="str">
         <v>796.36</v>
       </c>
-      <c r="CR7" t="str">
+      <c r="CT7" t="str">
         <v>224</v>
       </c>
     </row>
@@ -2442,16 +2484,22 @@
       <c r="BV8" t="str">
         <v>130.5</v>
       </c>
-      <c r="CO8" t="str">
+      <c r="BY8" t="str">
+        <v/>
+      </c>
+      <c r="BZ8" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ8" t="str">
         <v>9800</v>
       </c>
-      <c r="CP8" t="str">
+      <c r="CR8" t="str">
         <v>124.5_x000d_</v>
       </c>
-      <c r="CQ8" t="str">
+      <c r="CS8" t="str">
         <v>1010.91</v>
       </c>
-      <c r="CR8" t="str">
+      <c r="CT8" t="str">
         <v>218</v>
       </c>
     </row>
@@ -2642,16 +2690,22 @@
       <c r="BV9" t="str">
         <v>130</v>
       </c>
-      <c r="CO9" t="str">
+      <c r="BY9" t="str">
+        <v/>
+      </c>
+      <c r="BZ9" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ9" t="str">
         <v>10600</v>
       </c>
-      <c r="CP9" t="str">
+      <c r="CR9" t="str">
         <v>124_x000d_</v>
       </c>
-      <c r="CQ9" t="str">
+      <c r="CS9" t="str">
         <v>1265.45</v>
       </c>
-      <c r="CR9" t="str">
+      <c r="CT9" t="str">
         <v>213.09</v>
       </c>
     </row>
@@ -2830,16 +2884,22 @@
       <c r="BV10" t="str">
         <v>129.5</v>
       </c>
-      <c r="CO10" t="str">
+      <c r="BY10" t="str">
+        <v/>
+      </c>
+      <c r="BZ10" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ10" t="str">
         <v>11600</v>
       </c>
-      <c r="CP10" t="str">
+      <c r="CR10" t="str">
         <v>124_x000d_</v>
       </c>
-      <c r="CQ10" t="str">
+      <c r="CS10" t="str">
         <v>1567.27</v>
       </c>
-      <c r="CR10" t="str">
+      <c r="CT10" t="str">
         <v>209.45</v>
       </c>
     </row>
@@ -3006,16 +3066,22 @@
       <c r="BV11" t="str">
         <v>129</v>
       </c>
-      <c r="CO11" t="str">
+      <c r="BY11" t="str">
+        <v/>
+      </c>
+      <c r="BZ11" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ11" t="str">
         <v>12300</v>
       </c>
-      <c r="CP11" t="str">
+      <c r="CR11" t="str">
         <v>124.5_x000d_</v>
       </c>
-      <c r="CQ11" t="str">
+      <c r="CS11" t="str">
         <v>1909.09</v>
       </c>
-      <c r="CR11" t="str">
+      <c r="CT11" t="str">
         <v>208.18</v>
       </c>
     </row>
@@ -3134,16 +3200,22 @@
       <c r="BV12" t="str">
         <v>128.5</v>
       </c>
-      <c r="CO12" t="str">
+      <c r="BY12" t="str">
+        <v/>
+      </c>
+      <c r="BZ12" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ12" t="str">
         <v>12800</v>
       </c>
-      <c r="CP12" t="str">
+      <c r="CR12" t="str">
         <v>125_x000d_</v>
       </c>
-      <c r="CQ12" t="str">
+      <c r="CS12" t="str">
         <v>2309.09</v>
       </c>
-      <c r="CR12" t="str">
+      <c r="CT12" t="str">
         <v>209.64</v>
       </c>
     </row>
@@ -3262,16 +3334,22 @@
       <c r="BV13" t="str">
         <v>128</v>
       </c>
-      <c r="CO13" t="str">
+      <c r="BY13" t="str">
+        <v/>
+      </c>
+      <c r="BZ13" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ13" t="str">
         <v>13300</v>
       </c>
-      <c r="CP13" t="str">
+      <c r="CR13" t="str">
         <v>125.5_x000d_</v>
       </c>
-      <c r="CQ13" t="str">
+      <c r="CS13" t="str">
         <v>2421.05</v>
       </c>
-      <c r="CR13" t="str">
+      <c r="CT13" t="str">
         <v>210.36</v>
       </c>
     </row>
@@ -3342,10 +3420,16 @@
       <c r="BV14" t="str">
         <v>127.5</v>
       </c>
-      <c r="CO14" t="str">
+      <c r="BY14" t="str">
+        <v/>
+      </c>
+      <c r="BZ14" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ14" t="str">
         <v>13600</v>
       </c>
-      <c r="CP14" t="str">
+      <c r="CR14" t="str">
         <v>126_x000d_</v>
       </c>
     </row>
@@ -3416,10 +3500,16 @@
       <c r="BV15" t="str">
         <v>127</v>
       </c>
-      <c r="CO15" t="str">
+      <c r="BY15" t="str">
+        <v/>
+      </c>
+      <c r="BZ15" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ15" t="str">
         <v>14000</v>
       </c>
-      <c r="CP15" t="str">
+      <c r="CR15" t="str">
         <v>126.5_x000d_</v>
       </c>
     </row>
@@ -3490,10 +3580,16 @@
       <c r="BV16" t="str">
         <v>126.5</v>
       </c>
-      <c r="CO16" t="str">
+      <c r="BY16" t="str">
+        <v/>
+      </c>
+      <c r="BZ16" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ16" t="str">
         <v>14300</v>
       </c>
-      <c r="CP16" t="str">
+      <c r="CR16" t="str">
         <v>127_x000d_</v>
       </c>
     </row>
@@ -3558,10 +3654,16 @@
       <c r="BV17" t="str">
         <v>126</v>
       </c>
-      <c r="CO17" t="str">
+      <c r="BY17" t="str">
+        <v/>
+      </c>
+      <c r="BZ17" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ17" t="str">
         <v>14700</v>
       </c>
-      <c r="CP17" t="str">
+      <c r="CR17" t="str">
         <v>127.5_x000d_</v>
       </c>
     </row>
@@ -3626,10 +3728,16 @@
       <c r="BV18" t="str">
         <v>125.5</v>
       </c>
-      <c r="CO18" t="str">
+      <c r="BY18" t="str">
+        <v/>
+      </c>
+      <c r="BZ18" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ18" t="str">
         <v>15000</v>
       </c>
-      <c r="CP18" t="str">
+      <c r="CR18" t="str">
         <v>128_x000d_</v>
       </c>
     </row>
@@ -3682,10 +3790,16 @@
       <c r="BV19" t="str">
         <v>125</v>
       </c>
-      <c r="CO19" t="str">
-        <v/>
-      </c>
-      <c r="CP19" t="str">
+      <c r="BY19" t="str">
+        <v/>
+      </c>
+      <c r="BZ19" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ19" t="str">
+        <v/>
+      </c>
+      <c r="CR19" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -3738,10 +3852,16 @@
       <c r="BV20" t="str">
         <v>124.75</v>
       </c>
-      <c r="CO20" t="str">
-        <v/>
-      </c>
-      <c r="CP20" t="str">
+      <c r="BY20" t="str">
+        <v/>
+      </c>
+      <c r="BZ20" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ20" t="str">
+        <v/>
+      </c>
+      <c r="CR20" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -3770,10 +3890,16 @@
       <c r="BV21" t="str">
         <v>124.75</v>
       </c>
-      <c r="CO21" t="str">
-        <v/>
-      </c>
-      <c r="CP21" t="str">
+      <c r="BY21" t="str">
+        <v/>
+      </c>
+      <c r="BZ21" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ21" t="str">
+        <v/>
+      </c>
+      <c r="CR21" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -3802,10 +3928,16 @@
       <c r="BV22" t="str">
         <v>125</v>
       </c>
-      <c r="CO22" t="str">
-        <v/>
-      </c>
-      <c r="CP22" t="str">
+      <c r="BY22" t="str">
+        <v/>
+      </c>
+      <c r="BZ22" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ22" t="str">
+        <v/>
+      </c>
+      <c r="CR22" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -3834,10 +3966,16 @@
       <c r="BV23" t="str">
         <v>125.5</v>
       </c>
-      <c r="CO23" t="str">
-        <v/>
-      </c>
-      <c r="CP23" t="str">
+      <c r="BY23" t="str">
+        <v/>
+      </c>
+      <c r="BZ23" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ23" t="str">
+        <v/>
+      </c>
+      <c r="CR23" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -3866,10 +4004,16 @@
       <c r="BV24" t="str">
         <v>126</v>
       </c>
-      <c r="CO24" t="str">
-        <v/>
-      </c>
-      <c r="CP24" t="str">
+      <c r="BY24" t="str">
+        <v/>
+      </c>
+      <c r="BZ24" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ24" t="str">
+        <v/>
+      </c>
+      <c r="CR24" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -3898,10 +4042,16 @@
       <c r="BV25" t="str">
         <v>126.5</v>
       </c>
-      <c r="CO25" t="str">
-        <v/>
-      </c>
-      <c r="CP25" t="str">
+      <c r="BY25" t="str">
+        <v/>
+      </c>
+      <c r="BZ25" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ25" t="str">
+        <v/>
+      </c>
+      <c r="CR25" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -3930,10 +4080,16 @@
       <c r="BV26" t="str">
         <v>127</v>
       </c>
-      <c r="CO26" t="str">
-        <v/>
-      </c>
-      <c r="CP26" t="str">
+      <c r="BY26" t="str">
+        <v/>
+      </c>
+      <c r="BZ26" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ26" t="str">
+        <v/>
+      </c>
+      <c r="CR26" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -3962,10 +4118,16 @@
       <c r="BV27" t="str">
         <v>127.5</v>
       </c>
-      <c r="CO27" t="str">
-        <v/>
-      </c>
-      <c r="CP27" t="str">
+      <c r="BY27" t="str">
+        <v/>
+      </c>
+      <c r="BZ27" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ27" t="str">
+        <v/>
+      </c>
+      <c r="CR27" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -3994,10 +4156,16 @@
       <c r="BV28" t="str">
         <v>128</v>
       </c>
-      <c r="CO28" t="str">
-        <v/>
-      </c>
-      <c r="CP28" t="str">
+      <c r="BY28" t="str">
+        <v/>
+      </c>
+      <c r="BZ28" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ28" t="str">
+        <v/>
+      </c>
+      <c r="CR28" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -4026,10 +4194,16 @@
       <c r="BV29" t="str">
         <v>128.5</v>
       </c>
-      <c r="CO29" t="str">
-        <v/>
-      </c>
-      <c r="CP29" t="str">
+      <c r="BY29" t="str">
+        <v/>
+      </c>
+      <c r="BZ29" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ29" t="str">
+        <v/>
+      </c>
+      <c r="CR29" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -4058,10 +4232,16 @@
       <c r="BV30" t="str">
         <v>129</v>
       </c>
-      <c r="CO30" t="str">
-        <v/>
-      </c>
-      <c r="CP30" t="str">
+      <c r="BY30" t="str">
+        <v/>
+      </c>
+      <c r="BZ30" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ30" t="str">
+        <v/>
+      </c>
+      <c r="CR30" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -4090,10 +4270,16 @@
       <c r="BV31" t="str">
         <v>129.5</v>
       </c>
-      <c r="CO31" t="str">
-        <v/>
-      </c>
-      <c r="CP31" t="str">
+      <c r="BY31" t="str">
+        <v/>
+      </c>
+      <c r="BZ31" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ31" t="str">
+        <v/>
+      </c>
+      <c r="CR31" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -4116,10 +4302,16 @@
       <c r="BN32" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO32" t="str">
-        <v/>
-      </c>
-      <c r="CP32" t="str">
+      <c r="BY32" t="str">
+        <v/>
+      </c>
+      <c r="BZ32" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ32" t="str">
+        <v/>
+      </c>
+      <c r="CR32" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -4142,10 +4334,16 @@
       <c r="BN33" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO33" t="str">
-        <v/>
-      </c>
-      <c r="CP33" t="str">
+      <c r="BY33" t="str">
+        <v/>
+      </c>
+      <c r="BZ33" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ33" t="str">
+        <v/>
+      </c>
+      <c r="CR33" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -4168,10 +4366,16 @@
       <c r="BN34" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO34" t="str">
-        <v/>
-      </c>
-      <c r="CP34" t="str">
+      <c r="BY34" t="str">
+        <v/>
+      </c>
+      <c r="BZ34" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ34" t="str">
+        <v/>
+      </c>
+      <c r="CR34" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -4194,10 +4398,16 @@
       <c r="BN35" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO35" t="str">
-        <v/>
-      </c>
-      <c r="CP35" t="str">
+      <c r="BY35" t="str">
+        <v/>
+      </c>
+      <c r="BZ35" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ35" t="str">
+        <v/>
+      </c>
+      <c r="CR35" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -4220,10 +4430,16 @@
       <c r="BN36" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO36" t="str">
-        <v/>
-      </c>
-      <c r="CP36" t="str">
+      <c r="BY36" t="str">
+        <v/>
+      </c>
+      <c r="BZ36" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ36" t="str">
+        <v/>
+      </c>
+      <c r="CR36" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -4246,10 +4462,16 @@
       <c r="BN37" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO37" t="str">
-        <v/>
-      </c>
-      <c r="CP37" t="str">
+      <c r="BY37" t="str">
+        <v/>
+      </c>
+      <c r="BZ37" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ37" t="str">
+        <v/>
+      </c>
+      <c r="CR37" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -4272,10 +4494,16 @@
       <c r="BN38" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO38" t="str">
-        <v/>
-      </c>
-      <c r="CP38" t="str">
+      <c r="BY38" t="str">
+        <v/>
+      </c>
+      <c r="BZ38" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ38" t="str">
+        <v/>
+      </c>
+      <c r="CR38" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -4298,10 +4526,16 @@
       <c r="BN39" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO39" t="str">
-        <v/>
-      </c>
-      <c r="CP39" t="str">
+      <c r="BY39" t="str">
+        <v/>
+      </c>
+      <c r="BZ39" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ39" t="str">
+        <v/>
+      </c>
+      <c r="CR39" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -4324,10 +4558,16 @@
       <c r="BN40" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO40" t="str">
-        <v/>
-      </c>
-      <c r="CP40" t="str">
+      <c r="BY40" t="str">
+        <v/>
+      </c>
+      <c r="BZ40" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ40" t="str">
+        <v/>
+      </c>
+      <c r="CR40" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -4350,10 +4590,16 @@
       <c r="BN41" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO41" t="str">
-        <v/>
-      </c>
-      <c r="CP41" t="str">
+      <c r="BY41" t="str">
+        <v/>
+      </c>
+      <c r="BZ41" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ41" t="str">
+        <v/>
+      </c>
+      <c r="CR41" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -4376,10 +4622,16 @@
       <c r="BN42" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO42" t="str">
-        <v/>
-      </c>
-      <c r="CP42" t="str">
+      <c r="BY42" t="str">
+        <v/>
+      </c>
+      <c r="BZ42" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ42" t="str">
+        <v/>
+      </c>
+      <c r="CR42" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -4402,10 +4654,16 @@
       <c r="BN43" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO43" t="str">
-        <v/>
-      </c>
-      <c r="CP43" t="str">
+      <c r="BY43" t="str">
+        <v/>
+      </c>
+      <c r="BZ43" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ43" t="str">
+        <v/>
+      </c>
+      <c r="CR43" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -4428,10 +4686,16 @@
       <c r="BN44" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO44" t="str">
-        <v/>
-      </c>
-      <c r="CP44" t="str">
+      <c r="BY44" t="str">
+        <v/>
+      </c>
+      <c r="BZ44" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ44" t="str">
+        <v/>
+      </c>
+      <c r="CR44" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -4454,10 +4718,16 @@
       <c r="BN45" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO45" t="str">
-        <v/>
-      </c>
-      <c r="CP45" t="str">
+      <c r="BY45" t="str">
+        <v/>
+      </c>
+      <c r="BZ45" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ45" t="str">
+        <v/>
+      </c>
+      <c r="CR45" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -4480,10 +4750,16 @@
       <c r="BN46" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO46" t="str">
-        <v/>
-      </c>
-      <c r="CP46" t="str">
+      <c r="BY46" t="str">
+        <v/>
+      </c>
+      <c r="BZ46" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ46" t="str">
+        <v/>
+      </c>
+      <c r="CR46" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -4506,10 +4782,16 @@
       <c r="BN47" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO47" t="str">
-        <v/>
-      </c>
-      <c r="CP47" t="str">
+      <c r="BY47" t="str">
+        <v/>
+      </c>
+      <c r="BZ47" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ47" t="str">
+        <v/>
+      </c>
+      <c r="CR47" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -4532,10 +4814,16 @@
       <c r="BN48" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO48" t="str">
-        <v/>
-      </c>
-      <c r="CP48" t="str">
+      <c r="BY48" t="str">
+        <v/>
+      </c>
+      <c r="BZ48" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ48" t="str">
+        <v/>
+      </c>
+      <c r="CR48" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -4558,10 +4846,16 @@
       <c r="BN49" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO49" t="str">
-        <v/>
-      </c>
-      <c r="CP49" t="str">
+      <c r="BY49" t="str">
+        <v/>
+      </c>
+      <c r="BZ49" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ49" t="str">
+        <v/>
+      </c>
+      <c r="CR49" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -4584,10 +4878,16 @@
       <c r="BN50" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO50" t="str">
-        <v/>
-      </c>
-      <c r="CP50" t="str">
+      <c r="BY50" t="str">
+        <v/>
+      </c>
+      <c r="BZ50" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ50" t="str">
+        <v/>
+      </c>
+      <c r="CR50" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -4610,10 +4910,16 @@
       <c r="BN51" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO51" t="str">
-        <v/>
-      </c>
-      <c r="CP51" t="str">
+      <c r="BY51" t="str">
+        <v/>
+      </c>
+      <c r="BZ51" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ51" t="str">
+        <v/>
+      </c>
+      <c r="CR51" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -4636,10 +4942,16 @@
       <c r="BN52" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO52" t="str">
-        <v/>
-      </c>
-      <c r="CP52" t="str">
+      <c r="BY52" t="str">
+        <v/>
+      </c>
+      <c r="BZ52" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ52" t="str">
+        <v/>
+      </c>
+      <c r="CR52" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -4662,10 +4974,16 @@
       <c r="BN53" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO53" t="str">
-        <v/>
-      </c>
-      <c r="CP53" t="str">
+      <c r="BY53" t="str">
+        <v/>
+      </c>
+      <c r="BZ53" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ53" t="str">
+        <v/>
+      </c>
+      <c r="CR53" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -4688,10 +5006,16 @@
       <c r="BN54" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO54" t="str">
-        <v/>
-      </c>
-      <c r="CP54" t="str">
+      <c r="BY54" t="str">
+        <v/>
+      </c>
+      <c r="BZ54" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ54" t="str">
+        <v/>
+      </c>
+      <c r="CR54" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -4714,10 +5038,16 @@
       <c r="BN55" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO55" t="str">
-        <v/>
-      </c>
-      <c r="CP55" t="str">
+      <c r="BY55" t="str">
+        <v/>
+      </c>
+      <c r="BZ55" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ55" t="str">
+        <v/>
+      </c>
+      <c r="CR55" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -4740,10 +5070,16 @@
       <c r="BN56" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO56" t="str">
-        <v/>
-      </c>
-      <c r="CP56" t="str">
+      <c r="BY56" t="str">
+        <v/>
+      </c>
+      <c r="BZ56" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ56" t="str">
+        <v/>
+      </c>
+      <c r="CR56" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -4766,10 +5102,16 @@
       <c r="BN57" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO57" t="str">
-        <v/>
-      </c>
-      <c r="CP57" t="str">
+      <c r="BY57" t="str">
+        <v/>
+      </c>
+      <c r="BZ57" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ57" t="str">
+        <v/>
+      </c>
+      <c r="CR57" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -4792,10 +5134,16 @@
       <c r="BN58" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO58" t="str">
-        <v/>
-      </c>
-      <c r="CP58" t="str">
+      <c r="BY58" t="str">
+        <v/>
+      </c>
+      <c r="BZ58" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ58" t="str">
+        <v/>
+      </c>
+      <c r="CR58" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -4818,10 +5166,16 @@
       <c r="BN59" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO59" t="str">
-        <v/>
-      </c>
-      <c r="CP59" t="str">
+      <c r="BY59" t="str">
+        <v/>
+      </c>
+      <c r="BZ59" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ59" t="str">
+        <v/>
+      </c>
+      <c r="CR59" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -4844,10 +5198,16 @@
       <c r="BN60" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO60" t="str">
-        <v/>
-      </c>
-      <c r="CP60" t="str">
+      <c r="BY60" t="str">
+        <v/>
+      </c>
+      <c r="BZ60" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ60" t="str">
+        <v/>
+      </c>
+      <c r="CR60" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -4870,10 +5230,16 @@
       <c r="BN61" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO61" t="str">
-        <v/>
-      </c>
-      <c r="CP61" t="str">
+      <c r="BY61" t="str">
+        <v/>
+      </c>
+      <c r="BZ61" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ61" t="str">
+        <v/>
+      </c>
+      <c r="CR61" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -4896,10 +5262,16 @@
       <c r="BN62" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO62" t="str">
-        <v/>
-      </c>
-      <c r="CP62" t="str">
+      <c r="BY62" t="str">
+        <v/>
+      </c>
+      <c r="BZ62" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ62" t="str">
+        <v/>
+      </c>
+      <c r="CR62" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -4922,10 +5294,16 @@
       <c r="BN63" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO63" t="str">
-        <v/>
-      </c>
-      <c r="CP63" t="str">
+      <c r="BY63" t="str">
+        <v/>
+      </c>
+      <c r="BZ63" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ63" t="str">
+        <v/>
+      </c>
+      <c r="CR63" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -4948,10 +5326,16 @@
       <c r="BN64" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO64" t="str">
-        <v/>
-      </c>
-      <c r="CP64" t="str">
+      <c r="BY64" t="str">
+        <v/>
+      </c>
+      <c r="BZ64" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ64" t="str">
+        <v/>
+      </c>
+      <c r="CR64" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -4974,10 +5358,16 @@
       <c r="BN65" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO65" t="str">
-        <v/>
-      </c>
-      <c r="CP65" t="str">
+      <c r="BY65" t="str">
+        <v/>
+      </c>
+      <c r="BZ65" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ65" t="str">
+        <v/>
+      </c>
+      <c r="CR65" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -5000,10 +5390,16 @@
       <c r="BN66" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO66" t="str">
-        <v/>
-      </c>
-      <c r="CP66" t="str">
+      <c r="BY66" t="str">
+        <v/>
+      </c>
+      <c r="BZ66" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ66" t="str">
+        <v/>
+      </c>
+      <c r="CR66" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -5026,10 +5422,16 @@
       <c r="BN67" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO67" t="str">
-        <v/>
-      </c>
-      <c r="CP67" t="str">
+      <c r="BY67" t="str">
+        <v/>
+      </c>
+      <c r="BZ67" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ67" t="str">
+        <v/>
+      </c>
+      <c r="CR67" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -5052,10 +5454,16 @@
       <c r="BN68" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO68" t="str">
-        <v/>
-      </c>
-      <c r="CP68" t="str">
+      <c r="BY68" t="str">
+        <v/>
+      </c>
+      <c r="BZ68" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ68" t="str">
+        <v/>
+      </c>
+      <c r="CR68" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -5078,10 +5486,16 @@
       <c r="BN69" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO69" t="str">
-        <v/>
-      </c>
-      <c r="CP69" t="str">
+      <c r="BY69" t="str">
+        <v/>
+      </c>
+      <c r="BZ69" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ69" t="str">
+        <v/>
+      </c>
+      <c r="CR69" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -5104,10 +5518,16 @@
       <c r="BN70" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO70" t="str">
-        <v/>
-      </c>
-      <c r="CP70" t="str">
+      <c r="BY70" t="str">
+        <v/>
+      </c>
+      <c r="BZ70" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ70" t="str">
+        <v/>
+      </c>
+      <c r="CR70" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -5130,10 +5550,16 @@
       <c r="BN71" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO71" t="str">
-        <v/>
-      </c>
-      <c r="CP71" t="str">
+      <c r="BY71" t="str">
+        <v/>
+      </c>
+      <c r="BZ71" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ71" t="str">
+        <v/>
+      </c>
+      <c r="CR71" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -5156,10 +5582,16 @@
       <c r="BN72" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO72" t="str">
-        <v/>
-      </c>
-      <c r="CP72" t="str">
+      <c r="BY72" t="str">
+        <v/>
+      </c>
+      <c r="BZ72" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ72" t="str">
+        <v/>
+      </c>
+      <c r="CR72" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -5182,10 +5614,16 @@
       <c r="BN73" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO73" t="str">
-        <v/>
-      </c>
-      <c r="CP73" t="str">
+      <c r="BY73" t="str">
+        <v/>
+      </c>
+      <c r="BZ73" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ73" t="str">
+        <v/>
+      </c>
+      <c r="CR73" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -5208,10 +5646,16 @@
       <c r="BN74" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO74" t="str">
-        <v/>
-      </c>
-      <c r="CP74" t="str">
+      <c r="BY74" t="str">
+        <v/>
+      </c>
+      <c r="BZ74" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ74" t="str">
+        <v/>
+      </c>
+      <c r="CR74" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -5234,10 +5678,16 @@
       <c r="BN75" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO75" t="str">
-        <v/>
-      </c>
-      <c r="CP75" t="str">
+      <c r="BY75" t="str">
+        <v/>
+      </c>
+      <c r="BZ75" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ75" t="str">
+        <v/>
+      </c>
+      <c r="CR75" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -5260,10 +5710,16 @@
       <c r="BN76" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO76" t="str">
-        <v/>
-      </c>
-      <c r="CP76" t="str">
+      <c r="BY76" t="str">
+        <v/>
+      </c>
+      <c r="BZ76" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ76" t="str">
+        <v/>
+      </c>
+      <c r="CR76" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -5286,10 +5742,16 @@
       <c r="BN77" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO77" t="str">
-        <v/>
-      </c>
-      <c r="CP77" t="str">
+      <c r="BY77" t="str">
+        <v/>
+      </c>
+      <c r="BZ77" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ77" t="str">
+        <v/>
+      </c>
+      <c r="CR77" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -5312,10 +5774,16 @@
       <c r="BN78" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO78" t="str">
-        <v/>
-      </c>
-      <c r="CP78" t="str">
+      <c r="BY78" t="str">
+        <v/>
+      </c>
+      <c r="BZ78" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ78" t="str">
+        <v/>
+      </c>
+      <c r="CR78" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -5338,10 +5806,16 @@
       <c r="BN79" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO79" t="str">
-        <v/>
-      </c>
-      <c r="CP79" t="str">
+      <c r="BY79" t="str">
+        <v/>
+      </c>
+      <c r="BZ79" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ79" t="str">
+        <v/>
+      </c>
+      <c r="CR79" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -5364,10 +5838,16 @@
       <c r="BN80" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO80" t="str">
-        <v/>
-      </c>
-      <c r="CP80" t="str">
+      <c r="BY80" t="str">
+        <v/>
+      </c>
+      <c r="BZ80" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ80" t="str">
+        <v/>
+      </c>
+      <c r="CR80" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -5390,10 +5870,16 @@
       <c r="BN81" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO81" t="str">
-        <v/>
-      </c>
-      <c r="CP81" t="str">
+      <c r="BY81" t="str">
+        <v/>
+      </c>
+      <c r="BZ81" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ81" t="str">
+        <v/>
+      </c>
+      <c r="CR81" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -5404,10 +5890,16 @@
       <c r="BN82" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO82" t="str">
-        <v/>
-      </c>
-      <c r="CP82" t="str">
+      <c r="BY82" t="str">
+        <v/>
+      </c>
+      <c r="BZ82" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ82" t="str">
+        <v/>
+      </c>
+      <c r="CR82" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -5418,10 +5910,16 @@
       <c r="BN83" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO83" t="str">
-        <v/>
-      </c>
-      <c r="CP83" t="str">
+      <c r="BY83" t="str">
+        <v/>
+      </c>
+      <c r="BZ83" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ83" t="str">
+        <v/>
+      </c>
+      <c r="CR83" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -5432,10 +5930,16 @@
       <c r="BN84" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO84" t="str">
-        <v/>
-      </c>
-      <c r="CP84" t="str">
+      <c r="BY84" t="str">
+        <v/>
+      </c>
+      <c r="BZ84" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ84" t="str">
+        <v/>
+      </c>
+      <c r="CR84" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -5446,10 +5950,16 @@
       <c r="BN85" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO85" t="str">
-        <v/>
-      </c>
-      <c r="CP85" t="str">
+      <c r="BY85" t="str">
+        <v/>
+      </c>
+      <c r="BZ85" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ85" t="str">
+        <v/>
+      </c>
+      <c r="CR85" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -5460,10 +5970,16 @@
       <c r="BN86" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO86" t="str">
-        <v/>
-      </c>
-      <c r="CP86" t="str">
+      <c r="BY86" t="str">
+        <v/>
+      </c>
+      <c r="BZ86" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ86" t="str">
+        <v/>
+      </c>
+      <c r="CR86" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -5474,10 +5990,16 @@
       <c r="BN87" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO87" t="str">
-        <v/>
-      </c>
-      <c r="CP87" t="str">
+      <c r="BY87" t="str">
+        <v/>
+      </c>
+      <c r="BZ87" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ87" t="str">
+        <v/>
+      </c>
+      <c r="CR87" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -5488,10 +6010,16 @@
       <c r="BN88" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO88" t="str">
-        <v/>
-      </c>
-      <c r="CP88" t="str">
+      <c r="BY88" t="str">
+        <v/>
+      </c>
+      <c r="BZ88" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ88" t="str">
+        <v/>
+      </c>
+      <c r="CR88" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -5502,10 +6030,16 @@
       <c r="BN89" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO89" t="str">
-        <v/>
-      </c>
-      <c r="CP89" t="str">
+      <c r="BY89" t="str">
+        <v/>
+      </c>
+      <c r="BZ89" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ89" t="str">
+        <v/>
+      </c>
+      <c r="CR89" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -5516,10 +6050,16 @@
       <c r="BN90" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO90" t="str">
-        <v/>
-      </c>
-      <c r="CP90" t="str">
+      <c r="BY90" t="str">
+        <v/>
+      </c>
+      <c r="BZ90" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ90" t="str">
+        <v/>
+      </c>
+      <c r="CR90" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -5530,10 +6070,16 @@
       <c r="BN91" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO91" t="str">
-        <v/>
-      </c>
-      <c r="CP91" t="str">
+      <c r="BY91" t="str">
+        <v/>
+      </c>
+      <c r="BZ91" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ91" t="str">
+        <v/>
+      </c>
+      <c r="CR91" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -5544,10 +6090,16 @@
       <c r="BN92" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO92" t="str">
-        <v/>
-      </c>
-      <c r="CP92" t="str">
+      <c r="BY92" t="str">
+        <v/>
+      </c>
+      <c r="BZ92" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ92" t="str">
+        <v/>
+      </c>
+      <c r="CR92" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -5558,10 +6110,16 @@
       <c r="BN93" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO93" t="str">
-        <v/>
-      </c>
-      <c r="CP93" t="str">
+      <c r="BY93" t="str">
+        <v/>
+      </c>
+      <c r="BZ93" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ93" t="str">
+        <v/>
+      </c>
+      <c r="CR93" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -5572,10 +6130,16 @@
       <c r="BN94" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO94" t="str">
-        <v/>
-      </c>
-      <c r="CP94" t="str">
+      <c r="BY94" t="str">
+        <v/>
+      </c>
+      <c r="BZ94" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ94" t="str">
+        <v/>
+      </c>
+      <c r="CR94" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -5586,10 +6150,16 @@
       <c r="BN95" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO95" t="str">
-        <v/>
-      </c>
-      <c r="CP95" t="str">
+      <c r="BY95" t="str">
+        <v/>
+      </c>
+      <c r="BZ95" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ95" t="str">
+        <v/>
+      </c>
+      <c r="CR95" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -5600,10 +6170,16 @@
       <c r="BN96" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO96" t="str">
-        <v/>
-      </c>
-      <c r="CP96" t="str">
+      <c r="BY96" t="str">
+        <v/>
+      </c>
+      <c r="BZ96" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ96" t="str">
+        <v/>
+      </c>
+      <c r="CR96" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -5614,10 +6190,16 @@
       <c r="BN97" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO97" t="str">
-        <v/>
-      </c>
-      <c r="CP97" t="str">
+      <c r="BY97" t="str">
+        <v/>
+      </c>
+      <c r="BZ97" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ97" t="str">
+        <v/>
+      </c>
+      <c r="CR97" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -5628,10 +6210,16 @@
       <c r="BN98" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO98" t="str">
-        <v/>
-      </c>
-      <c r="CP98" t="str">
+      <c r="BY98" t="str">
+        <v/>
+      </c>
+      <c r="BZ98" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ98" t="str">
+        <v/>
+      </c>
+      <c r="CR98" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -5642,10 +6230,16 @@
       <c r="BN99" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO99" t="str">
-        <v/>
-      </c>
-      <c r="CP99" t="str">
+      <c r="BY99" t="str">
+        <v/>
+      </c>
+      <c r="BZ99" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ99" t="str">
+        <v/>
+      </c>
+      <c r="CR99" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -5656,10 +6250,16 @@
       <c r="BN100" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO100" t="str">
-        <v/>
-      </c>
-      <c r="CP100" t="str">
+      <c r="BY100" t="str">
+        <v/>
+      </c>
+      <c r="BZ100" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ100" t="str">
+        <v/>
+      </c>
+      <c r="CR100" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -5670,10 +6270,16 @@
       <c r="BN101" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO101" t="str">
-        <v/>
-      </c>
-      <c r="CP101" t="str">
+      <c r="BY101" t="str">
+        <v/>
+      </c>
+      <c r="BZ101" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ101" t="str">
+        <v/>
+      </c>
+      <c r="CR101" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -5684,10 +6290,16 @@
       <c r="BN102" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO102" t="str">
-        <v/>
-      </c>
-      <c r="CP102" t="str">
+      <c r="BY102" t="str">
+        <v/>
+      </c>
+      <c r="BZ102" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ102" t="str">
+        <v/>
+      </c>
+      <c r="CR102" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -5698,10 +6310,16 @@
       <c r="BN103" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO103" t="str">
-        <v/>
-      </c>
-      <c r="CP103" t="str">
+      <c r="BY103" t="str">
+        <v/>
+      </c>
+      <c r="BZ103" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ103" t="str">
+        <v/>
+      </c>
+      <c r="CR103" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -5712,10 +6330,16 @@
       <c r="BN104" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO104" t="str">
-        <v/>
-      </c>
-      <c r="CP104" t="str">
+      <c r="BY104" t="str">
+        <v/>
+      </c>
+      <c r="BZ104" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ104" t="str">
+        <v/>
+      </c>
+      <c r="CR104" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -5726,10 +6350,16 @@
       <c r="BN105" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO105" t="str">
-        <v/>
-      </c>
-      <c r="CP105" t="str">
+      <c r="BY105" t="str">
+        <v/>
+      </c>
+      <c r="BZ105" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ105" t="str">
+        <v/>
+      </c>
+      <c r="CR105" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -5740,10 +6370,16 @@
       <c r="BN106" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO106" t="str">
-        <v/>
-      </c>
-      <c r="CP106" t="str">
+      <c r="BY106" t="str">
+        <v/>
+      </c>
+      <c r="BZ106" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ106" t="str">
+        <v/>
+      </c>
+      <c r="CR106" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -5754,10 +6390,16 @@
       <c r="BN107" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO107" t="str">
-        <v/>
-      </c>
-      <c r="CP107" t="str">
+      <c r="BY107" t="str">
+        <v/>
+      </c>
+      <c r="BZ107" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ107" t="str">
+        <v/>
+      </c>
+      <c r="CR107" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -5768,10 +6410,16 @@
       <c r="BN108" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO108" t="str">
-        <v/>
-      </c>
-      <c r="CP108" t="str">
+      <c r="BY108" t="str">
+        <v/>
+      </c>
+      <c r="BZ108" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ108" t="str">
+        <v/>
+      </c>
+      <c r="CR108" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -5782,10 +6430,16 @@
       <c r="BN109" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO109" t="str">
-        <v/>
-      </c>
-      <c r="CP109" t="str">
+      <c r="BY109" t="str">
+        <v/>
+      </c>
+      <c r="BZ109" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ109" t="str">
+        <v/>
+      </c>
+      <c r="CR109" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -5796,10 +6450,16 @@
       <c r="BN110" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO110" t="str">
-        <v/>
-      </c>
-      <c r="CP110" t="str">
+      <c r="BY110" t="str">
+        <v/>
+      </c>
+      <c r="BZ110" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ110" t="str">
+        <v/>
+      </c>
+      <c r="CR110" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -5810,10 +6470,16 @@
       <c r="BN111" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO111" t="str">
-        <v/>
-      </c>
-      <c r="CP111" t="str">
+      <c r="BY111" t="str">
+        <v/>
+      </c>
+      <c r="BZ111" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ111" t="str">
+        <v/>
+      </c>
+      <c r="CR111" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -5824,10 +6490,16 @@
       <c r="BN112" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO112" t="str">
-        <v/>
-      </c>
-      <c r="CP112" t="str">
+      <c r="BY112" t="str">
+        <v/>
+      </c>
+      <c r="BZ112" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ112" t="str">
+        <v/>
+      </c>
+      <c r="CR112" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -5838,10 +6510,16 @@
       <c r="BN113" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO113" t="str">
-        <v/>
-      </c>
-      <c r="CP113" t="str">
+      <c r="BY113" t="str">
+        <v/>
+      </c>
+      <c r="BZ113" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ113" t="str">
+        <v/>
+      </c>
+      <c r="CR113" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -5852,10 +6530,16 @@
       <c r="BN114" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO114" t="str">
-        <v/>
-      </c>
-      <c r="CP114" t="str">
+      <c r="BY114" t="str">
+        <v/>
+      </c>
+      <c r="BZ114" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ114" t="str">
+        <v/>
+      </c>
+      <c r="CR114" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -5866,10 +6550,16 @@
       <c r="BN115" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO115" t="str">
-        <v/>
-      </c>
-      <c r="CP115" t="str">
+      <c r="BY115" t="str">
+        <v/>
+      </c>
+      <c r="BZ115" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ115" t="str">
+        <v/>
+      </c>
+      <c r="CR115" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -5880,10 +6570,16 @@
       <c r="BN116" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO116" t="str">
-        <v/>
-      </c>
-      <c r="CP116" t="str">
+      <c r="BY116" t="str">
+        <v/>
+      </c>
+      <c r="BZ116" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ116" t="str">
+        <v/>
+      </c>
+      <c r="CR116" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -5894,10 +6590,16 @@
       <c r="BN117" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO117" t="str">
-        <v/>
-      </c>
-      <c r="CP117" t="str">
+      <c r="BY117" t="str">
+        <v/>
+      </c>
+      <c r="BZ117" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ117" t="str">
+        <v/>
+      </c>
+      <c r="CR117" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -5908,10 +6610,16 @@
       <c r="BN118" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO118" t="str">
-        <v/>
-      </c>
-      <c r="CP118" t="str">
+      <c r="BY118" t="str">
+        <v/>
+      </c>
+      <c r="BZ118" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ118" t="str">
+        <v/>
+      </c>
+      <c r="CR118" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -5922,10 +6630,16 @@
       <c r="BN119" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO119" t="str">
-        <v/>
-      </c>
-      <c r="CP119" t="str">
+      <c r="BY119" t="str">
+        <v/>
+      </c>
+      <c r="BZ119" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ119" t="str">
+        <v/>
+      </c>
+      <c r="CR119" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -5936,10 +6650,16 @@
       <c r="BN120" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO120" t="str">
-        <v/>
-      </c>
-      <c r="CP120" t="str">
+      <c r="BY120" t="str">
+        <v/>
+      </c>
+      <c r="BZ120" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ120" t="str">
+        <v/>
+      </c>
+      <c r="CR120" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -5950,10 +6670,16 @@
       <c r="BN121" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO121" t="str">
-        <v/>
-      </c>
-      <c r="CP121" t="str">
+      <c r="BY121" t="str">
+        <v/>
+      </c>
+      <c r="BZ121" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ121" t="str">
+        <v/>
+      </c>
+      <c r="CR121" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -5964,10 +6690,16 @@
       <c r="BN122" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO122" t="str">
-        <v/>
-      </c>
-      <c r="CP122" t="str">
+      <c r="BY122" t="str">
+        <v/>
+      </c>
+      <c r="BZ122" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ122" t="str">
+        <v/>
+      </c>
+      <c r="CR122" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -5978,10 +6710,16 @@
       <c r="BN123" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO123" t="str">
-        <v/>
-      </c>
-      <c r="CP123" t="str">
+      <c r="BY123" t="str">
+        <v/>
+      </c>
+      <c r="BZ123" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ123" t="str">
+        <v/>
+      </c>
+      <c r="CR123" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -5992,10 +6730,16 @@
       <c r="BN124" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO124" t="str">
-        <v/>
-      </c>
-      <c r="CP124" t="str">
+      <c r="BY124" t="str">
+        <v/>
+      </c>
+      <c r="BZ124" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ124" t="str">
+        <v/>
+      </c>
+      <c r="CR124" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -6006,10 +6750,16 @@
       <c r="BN125" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO125" t="str">
-        <v/>
-      </c>
-      <c r="CP125" t="str">
+      <c r="BY125" t="str">
+        <v/>
+      </c>
+      <c r="BZ125" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ125" t="str">
+        <v/>
+      </c>
+      <c r="CR125" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -6020,10 +6770,16 @@
       <c r="BN126" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO126" t="str">
-        <v/>
-      </c>
-      <c r="CP126" t="str">
+      <c r="BY126" t="str">
+        <v/>
+      </c>
+      <c r="BZ126" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ126" t="str">
+        <v/>
+      </c>
+      <c r="CR126" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -6034,10 +6790,16 @@
       <c r="BN127" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO127" t="str">
-        <v/>
-      </c>
-      <c r="CP127" t="str">
+      <c r="BY127" t="str">
+        <v/>
+      </c>
+      <c r="BZ127" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ127" t="str">
+        <v/>
+      </c>
+      <c r="CR127" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -6048,10 +6810,16 @@
       <c r="BN128" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO128" t="str">
-        <v/>
-      </c>
-      <c r="CP128" t="str">
+      <c r="BY128" t="str">
+        <v/>
+      </c>
+      <c r="BZ128" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ128" t="str">
+        <v/>
+      </c>
+      <c r="CR128" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -6062,10 +6830,16 @@
       <c r="BN129" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO129" t="str">
-        <v/>
-      </c>
-      <c r="CP129" t="str">
+      <c r="BY129" t="str">
+        <v/>
+      </c>
+      <c r="BZ129" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ129" t="str">
+        <v/>
+      </c>
+      <c r="CR129" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -6076,10 +6850,16 @@
       <c r="BN130" t="str">
         <v>_x000d_</v>
       </c>
-      <c r="CO130" t="str">
-        <v/>
-      </c>
-      <c r="CP130" t="str">
+      <c r="BY130" t="str">
+        <v/>
+      </c>
+      <c r="BZ130" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ130" t="str">
+        <v/>
+      </c>
+      <c r="CR130" t="str">
         <v>_x000d_</v>
       </c>
     </row>
@@ -6090,416 +6870,1122 @@
       <c r="BN131" t="str">
         <v/>
       </c>
-      <c r="CO131" t="str">
-        <v/>
-      </c>
-      <c r="CP131" t="str">
+      <c r="BY131" t="str">
+        <v/>
+      </c>
+      <c r="BZ131" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ131" t="str">
+        <v/>
+      </c>
+      <c r="CR131" t="str">
         <v>_x000d_</v>
       </c>
     </row>
     <row r="132">
-      <c r="CO132" t="str">
-        <v/>
-      </c>
-      <c r="CP132" t="str">
+      <c r="BY132" t="str">
+        <v/>
+      </c>
+      <c r="BZ132" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ132" t="str">
+        <v/>
+      </c>
+      <c r="CR132" t="str">
         <v>_x000d_</v>
       </c>
     </row>
     <row r="133">
-      <c r="CO133" t="str">
-        <v/>
-      </c>
-      <c r="CP133" t="str">
+      <c r="BY133" t="str">
+        <v/>
+      </c>
+      <c r="BZ133" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ133" t="str">
+        <v/>
+      </c>
+      <c r="CR133" t="str">
         <v>_x000d_</v>
       </c>
     </row>
     <row r="134">
-      <c r="CO134" t="str">
-        <v/>
-      </c>
-      <c r="CP134" t="str">
+      <c r="BY134" t="str">
+        <v/>
+      </c>
+      <c r="BZ134" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ134" t="str">
+        <v/>
+      </c>
+      <c r="CR134" t="str">
         <v>_x000d_</v>
       </c>
     </row>
     <row r="135">
-      <c r="CO135" t="str">
-        <v/>
-      </c>
-      <c r="CP135" t="str">
+      <c r="BY135" t="str">
+        <v/>
+      </c>
+      <c r="BZ135" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ135" t="str">
+        <v/>
+      </c>
+      <c r="CR135" t="str">
         <v>_x000d_</v>
       </c>
     </row>
     <row r="136">
-      <c r="CO136" t="str">
-        <v/>
-      </c>
-      <c r="CP136" t="str">
+      <c r="BY136" t="str">
+        <v/>
+      </c>
+      <c r="BZ136" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ136" t="str">
+        <v/>
+      </c>
+      <c r="CR136" t="str">
         <v>_x000d_</v>
       </c>
     </row>
     <row r="137">
-      <c r="CO137" t="str">
-        <v/>
-      </c>
-      <c r="CP137" t="str">
+      <c r="BY137" t="str">
+        <v/>
+      </c>
+      <c r="BZ137" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ137" t="str">
+        <v/>
+      </c>
+      <c r="CR137" t="str">
         <v>_x000d_</v>
       </c>
     </row>
     <row r="138">
-      <c r="CO138" t="str">
-        <v/>
-      </c>
-      <c r="CP138" t="str">
+      <c r="BY138" t="str">
+        <v/>
+      </c>
+      <c r="BZ138" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ138" t="str">
+        <v/>
+      </c>
+      <c r="CR138" t="str">
         <v>_x000d_</v>
       </c>
     </row>
     <row r="139">
-      <c r="CO139" t="str">
-        <v/>
-      </c>
-      <c r="CP139" t="str">
+      <c r="BY139" t="str">
+        <v/>
+      </c>
+      <c r="BZ139" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ139" t="str">
+        <v/>
+      </c>
+      <c r="CR139" t="str">
         <v>_x000d_</v>
       </c>
     </row>
     <row r="140">
-      <c r="CO140" t="str">
-        <v/>
-      </c>
-      <c r="CP140" t="str">
+      <c r="BY140" t="str">
+        <v/>
+      </c>
+      <c r="BZ140" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ140" t="str">
+        <v/>
+      </c>
+      <c r="CR140" t="str">
         <v>_x000d_</v>
       </c>
     </row>
     <row r="141">
-      <c r="CO141" t="str">
-        <v/>
-      </c>
-      <c r="CP141" t="str">
+      <c r="BY141" t="str">
+        <v/>
+      </c>
+      <c r="BZ141" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ141" t="str">
+        <v/>
+      </c>
+      <c r="CR141" t="str">
         <v>_x000d_</v>
       </c>
     </row>
     <row r="142">
-      <c r="CO142" t="str">
-        <v/>
-      </c>
-      <c r="CP142" t="str">
+      <c r="BY142" t="str">
+        <v/>
+      </c>
+      <c r="BZ142" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ142" t="str">
+        <v/>
+      </c>
+      <c r="CR142" t="str">
         <v>_x000d_</v>
       </c>
     </row>
     <row r="143">
-      <c r="CO143" t="str">
-        <v/>
-      </c>
-      <c r="CP143" t="str">
+      <c r="BY143" t="str">
+        <v/>
+      </c>
+      <c r="BZ143" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ143" t="str">
+        <v/>
+      </c>
+      <c r="CR143" t="str">
         <v>_x000d_</v>
       </c>
     </row>
     <row r="144">
-      <c r="CO144" t="str">
-        <v/>
-      </c>
-      <c r="CP144" t="str">
+      <c r="BY144" t="str">
+        <v/>
+      </c>
+      <c r="BZ144" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ144" t="str">
+        <v/>
+      </c>
+      <c r="CR144" t="str">
         <v>_x000d_</v>
       </c>
     </row>
     <row r="145">
-      <c r="CO145" t="str">
-        <v/>
-      </c>
-      <c r="CP145" t="str">
+      <c r="BY145" t="str">
+        <v/>
+      </c>
+      <c r="BZ145" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ145" t="str">
+        <v/>
+      </c>
+      <c r="CR145" t="str">
         <v>_x000d_</v>
       </c>
     </row>
     <row r="146">
-      <c r="CO146" t="str">
-        <v/>
-      </c>
-      <c r="CP146" t="str">
+      <c r="BY146" t="str">
+        <v/>
+      </c>
+      <c r="BZ146" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ146" t="str">
+        <v/>
+      </c>
+      <c r="CR146" t="str">
         <v>_x000d_</v>
       </c>
     </row>
     <row r="147">
-      <c r="CO147" t="str">
-        <v/>
-      </c>
-      <c r="CP147" t="str">
+      <c r="BY147" t="str">
+        <v/>
+      </c>
+      <c r="BZ147" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ147" t="str">
+        <v/>
+      </c>
+      <c r="CR147" t="str">
         <v>_x000d_</v>
       </c>
     </row>
     <row r="148">
-      <c r="CO148" t="str">
-        <v/>
-      </c>
-      <c r="CP148" t="str">
+      <c r="BY148" t="str">
+        <v/>
+      </c>
+      <c r="BZ148" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ148" t="str">
+        <v/>
+      </c>
+      <c r="CR148" t="str">
         <v>_x000d_</v>
       </c>
     </row>
     <row r="149">
-      <c r="CO149" t="str">
-        <v/>
-      </c>
-      <c r="CP149" t="str">
+      <c r="BY149" t="str">
+        <v/>
+      </c>
+      <c r="BZ149" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ149" t="str">
+        <v/>
+      </c>
+      <c r="CR149" t="str">
         <v>_x000d_</v>
       </c>
     </row>
     <row r="150">
-      <c r="CO150" t="str">
-        <v/>
-      </c>
-      <c r="CP150" t="str">
+      <c r="BY150" t="str">
+        <v/>
+      </c>
+      <c r="BZ150" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ150" t="str">
+        <v/>
+      </c>
+      <c r="CR150" t="str">
         <v>_x000d_</v>
       </c>
     </row>
     <row r="151">
-      <c r="CO151" t="str">
-        <v/>
-      </c>
-      <c r="CP151" t="str">
+      <c r="BY151" t="str">
+        <v/>
+      </c>
+      <c r="BZ151" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ151" t="str">
+        <v/>
+      </c>
+      <c r="CR151" t="str">
         <v>_x000d_</v>
       </c>
     </row>
     <row r="152">
-      <c r="CO152" t="str">
-        <v/>
-      </c>
-      <c r="CP152" t="str">
+      <c r="BY152" t="str">
+        <v/>
+      </c>
+      <c r="BZ152" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ152" t="str">
+        <v/>
+      </c>
+      <c r="CR152" t="str">
         <v>_x000d_</v>
       </c>
     </row>
     <row r="153">
-      <c r="CO153" t="str">
-        <v/>
-      </c>
-      <c r="CP153" t="str">
+      <c r="BY153" t="str">
+        <v/>
+      </c>
+      <c r="BZ153" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ153" t="str">
+        <v/>
+      </c>
+      <c r="CR153" t="str">
         <v>_x000d_</v>
       </c>
     </row>
     <row r="154">
-      <c r="CO154" t="str">
-        <v/>
-      </c>
-      <c r="CP154" t="str">
+      <c r="BY154" t="str">
+        <v/>
+      </c>
+      <c r="BZ154" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ154" t="str">
+        <v/>
+      </c>
+      <c r="CR154" t="str">
         <v>_x000d_</v>
       </c>
     </row>
     <row r="155">
-      <c r="CO155" t="str">
-        <v/>
-      </c>
-      <c r="CP155" t="str">
+      <c r="BY155" t="str">
+        <v/>
+      </c>
+      <c r="BZ155" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ155" t="str">
+        <v/>
+      </c>
+      <c r="CR155" t="str">
         <v>_x000d_</v>
       </c>
     </row>
     <row r="156">
-      <c r="CO156" t="str">
-        <v/>
-      </c>
-      <c r="CP156" t="str">
+      <c r="BY156" t="str">
+        <v/>
+      </c>
+      <c r="BZ156" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ156" t="str">
+        <v/>
+      </c>
+      <c r="CR156" t="str">
         <v>_x000d_</v>
       </c>
     </row>
     <row r="157">
-      <c r="CO157" t="str">
-        <v/>
-      </c>
-      <c r="CP157" t="str">
+      <c r="BY157" t="str">
+        <v/>
+      </c>
+      <c r="BZ157" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ157" t="str">
+        <v/>
+      </c>
+      <c r="CR157" t="str">
         <v>_x000d_</v>
       </c>
     </row>
     <row r="158">
-      <c r="CO158" t="str">
-        <v/>
-      </c>
-      <c r="CP158" t="str">
+      <c r="BY158" t="str">
+        <v/>
+      </c>
+      <c r="BZ158" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ158" t="str">
+        <v/>
+      </c>
+      <c r="CR158" t="str">
         <v>_x000d_</v>
       </c>
     </row>
     <row r="159">
-      <c r="CO159" t="str">
-        <v/>
-      </c>
-      <c r="CP159" t="str">
+      <c r="BY159" t="str">
+        <v/>
+      </c>
+      <c r="BZ159" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ159" t="str">
+        <v/>
+      </c>
+      <c r="CR159" t="str">
         <v>_x000d_</v>
       </c>
     </row>
     <row r="160">
-      <c r="CO160" t="str">
-        <v/>
-      </c>
-      <c r="CP160" t="str">
+      <c r="BY160" t="str">
+        <v/>
+      </c>
+      <c r="BZ160" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ160" t="str">
+        <v/>
+      </c>
+      <c r="CR160" t="str">
         <v>_x000d_</v>
       </c>
     </row>
     <row r="161">
-      <c r="CO161" t="str">
-        <v/>
-      </c>
-      <c r="CP161" t="str">
+      <c r="BY161" t="str">
+        <v/>
+      </c>
+      <c r="BZ161" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ161" t="str">
+        <v/>
+      </c>
+      <c r="CR161" t="str">
         <v>_x000d_</v>
       </c>
     </row>
     <row r="162">
-      <c r="CO162" t="str">
-        <v/>
-      </c>
-      <c r="CP162" t="str">
+      <c r="BY162" t="str">
+        <v/>
+      </c>
+      <c r="BZ162" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ162" t="str">
+        <v/>
+      </c>
+      <c r="CR162" t="str">
         <v>_x000d_</v>
       </c>
     </row>
     <row r="163">
-      <c r="CO163" t="str">
-        <v/>
-      </c>
-      <c r="CP163" t="str">
+      <c r="BY163" t="str">
+        <v/>
+      </c>
+      <c r="BZ163" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ163" t="str">
+        <v/>
+      </c>
+      <c r="CR163" t="str">
         <v>_x000d_</v>
       </c>
     </row>
     <row r="164">
-      <c r="CO164" t="str">
-        <v/>
-      </c>
-      <c r="CP164" t="str">
+      <c r="BY164" t="str">
+        <v/>
+      </c>
+      <c r="BZ164" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ164" t="str">
+        <v/>
+      </c>
+      <c r="CR164" t="str">
         <v>_x000d_</v>
       </c>
     </row>
     <row r="165">
-      <c r="CO165" t="str">
-        <v/>
-      </c>
-      <c r="CP165" t="str">
+      <c r="BY165" t="str">
+        <v/>
+      </c>
+      <c r="BZ165" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ165" t="str">
+        <v/>
+      </c>
+      <c r="CR165" t="str">
         <v>_x000d_</v>
       </c>
     </row>
     <row r="166">
-      <c r="CO166" t="str">
-        <v/>
-      </c>
-      <c r="CP166" t="str">
+      <c r="BY166" t="str">
+        <v/>
+      </c>
+      <c r="BZ166" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ166" t="str">
+        <v/>
+      </c>
+      <c r="CR166" t="str">
         <v>_x000d_</v>
       </c>
     </row>
     <row r="167">
-      <c r="CO167" t="str">
-        <v/>
-      </c>
-      <c r="CP167" t="str">
+      <c r="BY167" t="str">
+        <v/>
+      </c>
+      <c r="BZ167" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ167" t="str">
+        <v/>
+      </c>
+      <c r="CR167" t="str">
         <v>_x000d_</v>
       </c>
     </row>
     <row r="168">
-      <c r="CO168" t="str">
-        <v/>
-      </c>
-      <c r="CP168" t="str">
+      <c r="BY168" t="str">
+        <v/>
+      </c>
+      <c r="BZ168" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ168" t="str">
+        <v/>
+      </c>
+      <c r="CR168" t="str">
         <v>_x000d_</v>
       </c>
     </row>
     <row r="169">
-      <c r="CO169" t="str">
-        <v/>
-      </c>
-      <c r="CP169" t="str">
+      <c r="BY169" t="str">
+        <v/>
+      </c>
+      <c r="BZ169" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ169" t="str">
+        <v/>
+      </c>
+      <c r="CR169" t="str">
         <v>_x000d_</v>
       </c>
     </row>
     <row r="170">
-      <c r="CO170" t="str">
-        <v/>
-      </c>
-      <c r="CP170" t="str">
+      <c r="BY170" t="str">
+        <v/>
+      </c>
+      <c r="BZ170" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ170" t="str">
+        <v/>
+      </c>
+      <c r="CR170" t="str">
         <v>_x000d_</v>
       </c>
     </row>
     <row r="171">
-      <c r="CO171" t="str">
-        <v/>
-      </c>
-      <c r="CP171" t="str">
+      <c r="BY171" t="str">
+        <v/>
+      </c>
+      <c r="BZ171" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ171" t="str">
+        <v/>
+      </c>
+      <c r="CR171" t="str">
         <v>_x000d_</v>
       </c>
     </row>
     <row r="172">
-      <c r="CO172" t="str">
-        <v/>
-      </c>
-      <c r="CP172" t="str">
+      <c r="BY172" t="str">
+        <v/>
+      </c>
+      <c r="BZ172" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ172" t="str">
+        <v/>
+      </c>
+      <c r="CR172" t="str">
         <v>_x000d_</v>
       </c>
     </row>
     <row r="173">
-      <c r="CO173" t="str">
-        <v/>
-      </c>
-      <c r="CP173" t="str">
+      <c r="BY173" t="str">
+        <v/>
+      </c>
+      <c r="BZ173" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ173" t="str">
+        <v/>
+      </c>
+      <c r="CR173" t="str">
         <v>_x000d_</v>
       </c>
     </row>
     <row r="174">
-      <c r="CO174" t="str">
-        <v/>
-      </c>
-      <c r="CP174" t="str">
+      <c r="BY174" t="str">
+        <v/>
+      </c>
+      <c r="BZ174" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ174" t="str">
+        <v/>
+      </c>
+      <c r="CR174" t="str">
         <v>_x000d_</v>
       </c>
     </row>
     <row r="175">
-      <c r="CO175" t="str">
-        <v/>
-      </c>
-      <c r="CP175" t="str">
+      <c r="BY175" t="str">
+        <v/>
+      </c>
+      <c r="BZ175" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ175" t="str">
+        <v/>
+      </c>
+      <c r="CR175" t="str">
         <v>_x000d_</v>
       </c>
     </row>
     <row r="176">
-      <c r="CO176" t="str">
-        <v/>
-      </c>
-      <c r="CP176" t="str">
+      <c r="BY176" t="str">
+        <v/>
+      </c>
+      <c r="BZ176" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ176" t="str">
+        <v/>
+      </c>
+      <c r="CR176" t="str">
         <v>_x000d_</v>
       </c>
     </row>
     <row r="177">
-      <c r="CO177" t="str">
-        <v/>
-      </c>
-      <c r="CP177" t="str">
+      <c r="BY177" t="str">
+        <v/>
+      </c>
+      <c r="BZ177" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ177" t="str">
+        <v/>
+      </c>
+      <c r="CR177" t="str">
         <v>_x000d_</v>
       </c>
     </row>
     <row r="178">
-      <c r="CO178" t="str">
-        <v/>
-      </c>
-      <c r="CP178" t="str">
+      <c r="BY178" t="str">
+        <v/>
+      </c>
+      <c r="BZ178" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ178" t="str">
+        <v/>
+      </c>
+      <c r="CR178" t="str">
         <v>_x000d_</v>
       </c>
     </row>
     <row r="179">
-      <c r="CO179" t="str">
-        <v/>
-      </c>
-      <c r="CP179" t="str">
+      <c r="BY179" t="str">
+        <v/>
+      </c>
+      <c r="BZ179" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ179" t="str">
+        <v/>
+      </c>
+      <c r="CR179" t="str">
         <v>_x000d_</v>
       </c>
     </row>
     <row r="180">
-      <c r="CO180" t="str">
-        <v/>
-      </c>
-      <c r="CP180" t="str">
+      <c r="BY180" t="str">
+        <v/>
+      </c>
+      <c r="BZ180" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ180" t="str">
+        <v/>
+      </c>
+      <c r="CR180" t="str">
         <v>_x000d_</v>
       </c>
     </row>
     <row r="181">
-      <c r="CO181" t="str">
-        <v/>
-      </c>
-      <c r="CP181" t="str">
+      <c r="BY181" t="str">
+        <v/>
+      </c>
+      <c r="BZ181" t="str">
+        <v>_x000d_</v>
+      </c>
+      <c r="CQ181" t="str">
+        <v/>
+      </c>
+      <c r="CR181" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="182">
+      <c r="BY182" t="str">
+        <v/>
+      </c>
+      <c r="BZ182" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="BY183" t="str">
+        <v/>
+      </c>
+      <c r="BZ183" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="BY184" t="str">
+        <v/>
+      </c>
+      <c r="BZ184" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="BY185" t="str">
+        <v/>
+      </c>
+      <c r="BZ185" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="BY186" t="str">
+        <v/>
+      </c>
+      <c r="BZ186" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="BY187" t="str">
+        <v/>
+      </c>
+      <c r="BZ187" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="BY188" t="str">
+        <v/>
+      </c>
+      <c r="BZ188" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="BY189" t="str">
+        <v/>
+      </c>
+      <c r="BZ189" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="BY190" t="str">
+        <v/>
+      </c>
+      <c r="BZ190" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="BY191" t="str">
+        <v/>
+      </c>
+      <c r="BZ191" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="BY192" t="str">
+        <v/>
+      </c>
+      <c r="BZ192" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="BY193" t="str">
+        <v/>
+      </c>
+      <c r="BZ193" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="BY194" t="str">
+        <v/>
+      </c>
+      <c r="BZ194" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="BY195" t="str">
+        <v/>
+      </c>
+      <c r="BZ195" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="BY196" t="str">
+        <v/>
+      </c>
+      <c r="BZ196" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="BY197" t="str">
+        <v/>
+      </c>
+      <c r="BZ197" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="BY198" t="str">
+        <v/>
+      </c>
+      <c r="BZ198" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="BY199" t="str">
+        <v/>
+      </c>
+      <c r="BZ199" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="BY200" t="str">
+        <v/>
+      </c>
+      <c r="BZ200" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="BY201" t="str">
+        <v/>
+      </c>
+      <c r="BZ201" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="BY202" t="str">
+        <v/>
+      </c>
+      <c r="BZ202" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="BY203" t="str">
+        <v/>
+      </c>
+      <c r="BZ203" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="BY204" t="str">
+        <v/>
+      </c>
+      <c r="BZ204" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="BY205" t="str">
+        <v/>
+      </c>
+      <c r="BZ205" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="BY206" t="str">
+        <v/>
+      </c>
+      <c r="BZ206" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="BY207" t="str">
+        <v/>
+      </c>
+      <c r="BZ207" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="BY208" t="str">
+        <v/>
+      </c>
+      <c r="BZ208" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="BY209" t="str">
+        <v/>
+      </c>
+      <c r="BZ209" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="BY210" t="str">
+        <v/>
+      </c>
+      <c r="BZ210" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="BY211" t="str">
+        <v/>
+      </c>
+      <c r="BZ211" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="BY212" t="str">
+        <v/>
+      </c>
+      <c r="BZ212" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="BY213" t="str">
+        <v/>
+      </c>
+      <c r="BZ213" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="BY214" t="str">
+        <v/>
+      </c>
+      <c r="BZ214" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="BY215" t="str">
+        <v/>
+      </c>
+      <c r="BZ215" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="BY216" t="str">
+        <v/>
+      </c>
+      <c r="BZ216" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="BY217" t="str">
+        <v/>
+      </c>
+      <c r="BZ217" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="BY218" t="str">
+        <v/>
+      </c>
+      <c r="BZ218" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="BY219" t="str">
+        <v/>
+      </c>
+      <c r="BZ219" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="BY220" t="str">
+        <v/>
+      </c>
+      <c r="BZ220" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="BY221" t="str">
+        <v/>
+      </c>
+      <c r="BZ221" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="BY222" t="str">
+        <v/>
+      </c>
+      <c r="BZ222" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="BY223" t="str">
+        <v/>
+      </c>
+      <c r="BZ223" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="BY224" t="str">
+        <v/>
+      </c>
+      <c r="BZ224" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="BY225" t="str">
+        <v/>
+      </c>
+      <c r="BZ225" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="BY226" t="str">
+        <v/>
+      </c>
+      <c r="BZ226" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="BY227" t="str">
+        <v/>
+      </c>
+      <c r="BZ227" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="BY228" t="str">
+        <v/>
+      </c>
+      <c r="BZ228" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="BY229" t="str">
+        <v/>
+      </c>
+      <c r="BZ229" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="BY230" t="str">
+        <v/>
+      </c>
+      <c r="BZ230" t="str">
+        <v>_x000d_</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="BY231" t="str">
+        <v/>
+      </c>
+      <c r="BZ231" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:CR181"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:CT231"/>
   </ignoredErrors>
 </worksheet>
 </file>